--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Documents\siteicin-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B77A7B2-60C0-47D0-BB23-C81ACFDF20C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5060491-5F3F-466D-8161-52E0AB712DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="36" windowWidth="23040" windowHeight="12240" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="346">
   <si>
     <t>kelime_adi</t>
   </si>
@@ -63,13 +63,1027 @@
   </si>
   <si>
     <t>mustak_kelimeler</t>
+  </si>
+  <si>
+    <t>Abartmak</t>
+  </si>
+  <si>
+    <t>Acımasız</t>
+  </si>
+  <si>
+    <t>Açı</t>
+  </si>
+  <si>
+    <t>Açık artırma</t>
+  </si>
+  <si>
+    <t>Açıklamak</t>
+  </si>
+  <si>
+    <t>Açık Oturum</t>
+  </si>
+  <si>
+    <t>Açık Oy</t>
+  </si>
+  <si>
+    <t>Açılım</t>
+  </si>
+  <si>
+    <t>Açılış Töreni</t>
+  </si>
+  <si>
+    <t>Aday</t>
+  </si>
+  <si>
+    <t>Akaryakıt</t>
+  </si>
+  <si>
+    <t>Akıcı</t>
+  </si>
+  <si>
+    <t>Akım</t>
+  </si>
+  <si>
+    <t>Akışkan</t>
+  </si>
+  <si>
+    <t>Akkor</t>
+  </si>
+  <si>
+    <t>Akyuvar</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>Albay</t>
+  </si>
+  <si>
+    <t>Algı</t>
+  </si>
+  <si>
+    <t>Alımlı</t>
+  </si>
+  <si>
+    <t>Alıntı</t>
+  </si>
+  <si>
+    <t>Almaç</t>
+  </si>
+  <si>
+    <t>Amaç</t>
+  </si>
+  <si>
+    <t>Anaerkil</t>
+  </si>
+  <si>
+    <t>Anayasa</t>
+  </si>
+  <si>
+    <t>Anı</t>
+  </si>
+  <si>
+    <t>Anıt</t>
+  </si>
+  <si>
+    <t>Anlam</t>
+  </si>
+  <si>
+    <t>Anlaşmazlık</t>
+  </si>
+  <si>
+    <t>Anlatı/Anlatım</t>
+  </si>
+  <si>
+    <t>Anlayış</t>
+  </si>
+  <si>
+    <t>Anma Töreni</t>
+  </si>
+  <si>
+    <t>Aracı</t>
+  </si>
+  <si>
+    <t>Araç</t>
+  </si>
+  <si>
+    <t>Araç-gereç</t>
+  </si>
+  <si>
+    <t>Arakesit</t>
+  </si>
+  <si>
+    <t>Aralık</t>
+  </si>
+  <si>
+    <t>Arasöz</t>
+  </si>
+  <si>
+    <t>Ardıl</t>
+  </si>
+  <si>
+    <t>Ardışık</t>
+  </si>
+  <si>
+    <t>Artı</t>
+  </si>
+  <si>
+    <t>Asalak</t>
+  </si>
+  <si>
+    <t>Ast</t>
+  </si>
+  <si>
+    <t>Astsubay</t>
+  </si>
+  <si>
+    <t>Asteğmen</t>
+  </si>
+  <si>
+    <t>Aşama</t>
+  </si>
+  <si>
+    <t>Ataerkil</t>
+  </si>
+  <si>
+    <t>Atama/Atanma</t>
+  </si>
+  <si>
+    <t>Atardamar</t>
+  </si>
+  <si>
+    <t>Ateşkes</t>
+  </si>
+  <si>
+    <t>Atılım</t>
+  </si>
+  <si>
+    <t>Avuntu</t>
+  </si>
+  <si>
+    <t>Aydın</t>
+  </si>
+  <si>
+    <t>Aygıt</t>
+  </si>
+  <si>
+    <t>Ayırtman</t>
+  </si>
+  <si>
+    <t>Aymaz</t>
+  </si>
+  <si>
+    <t>Ayraç</t>
+  </si>
+  <si>
+    <t>Ayrıcalık</t>
+  </si>
+  <si>
+    <t>Ayrım</t>
+  </si>
+  <si>
+    <t>Ayrıntı</t>
+  </si>
+  <si>
+    <t>Ayrışık</t>
+  </si>
+  <si>
+    <t>Ayrışma</t>
+  </si>
+  <si>
+    <t>Azınlık</t>
+  </si>
+  <si>
+    <t>Bağıl</t>
+  </si>
+  <si>
+    <t>Bağımlı</t>
+  </si>
+  <si>
+    <t>Bağımsız</t>
+  </si>
+  <si>
+    <t>Bağıntı</t>
+  </si>
+  <si>
+    <t>Bağışık/Bağışıklık</t>
+  </si>
+  <si>
+    <t>Bağlaç</t>
+  </si>
+  <si>
+    <t>Bağlam</t>
+  </si>
+  <si>
+    <t>Bağlantı</t>
+  </si>
+  <si>
+    <t>Bağlaşık-Bağdaşık</t>
+  </si>
+  <si>
+    <t>Bağnaz</t>
+  </si>
+  <si>
+    <t>Bakan</t>
+  </si>
+  <si>
+    <t>Bakış açısı</t>
+  </si>
+  <si>
+    <t>Barınak</t>
+  </si>
+  <si>
+    <t>Barış Anlaşması</t>
+  </si>
+  <si>
+    <t>Barışçıl-Barışsever</t>
+  </si>
+  <si>
+    <t>Basın</t>
+  </si>
+  <si>
+    <t>Basınç</t>
+  </si>
+  <si>
+    <t>Başarı</t>
+  </si>
+  <si>
+    <t>Başat</t>
+  </si>
+  <si>
+    <t>Başbuğ</t>
+  </si>
+  <si>
+    <t>Başkaldırı</t>
+  </si>
+  <si>
+    <t>Başkanlık</t>
+  </si>
+  <si>
+    <t>Başkent</t>
+  </si>
+  <si>
+    <t>Başvuru</t>
+  </si>
+  <si>
+    <t>Başyapıt</t>
+  </si>
+  <si>
+    <t>Başyazar</t>
+  </si>
+  <si>
+    <t>Bay</t>
+  </si>
+  <si>
+    <t>Bayan</t>
+  </si>
+  <si>
+    <t>Bayındır/Bayındırlık</t>
+  </si>
+  <si>
+    <t>Beğeni</t>
+  </si>
+  <si>
+    <t>Belge</t>
+  </si>
+  <si>
+    <t>Belirgin</t>
+  </si>
+  <si>
+    <t>Belirlemek</t>
+  </si>
+  <si>
+    <t>Belirli</t>
+  </si>
+  <si>
+    <t>Belirteç</t>
+  </si>
+  <si>
+    <t>Belirti</t>
+  </si>
+  <si>
+    <t>Bellek</t>
+  </si>
+  <si>
+    <t>Belletici/Belletmen</t>
+  </si>
+  <si>
+    <t>Bencil</t>
+  </si>
+  <si>
+    <t>Besin</t>
+  </si>
+  <si>
+    <t>Beşgen</t>
+  </si>
+  <si>
+    <t>Betim/Betimlemek</t>
+  </si>
+  <si>
+    <t>Bildirge/Bildiri</t>
+  </si>
+  <si>
+    <t>Bileşen</t>
+  </si>
+  <si>
+    <t>Bileşik</t>
+  </si>
+  <si>
+    <t>Bileşim</t>
+  </si>
+  <si>
+    <t>Bileşke</t>
+  </si>
+  <si>
+    <t>Bilge/Bilgelik</t>
+  </si>
+  <si>
+    <t>Bilgi-Birikim</t>
+  </si>
+  <si>
+    <t>Bilgin</t>
+  </si>
+  <si>
+    <t>Bilim</t>
+  </si>
+  <si>
+    <t>Bilinç</t>
+  </si>
+  <si>
+    <t>Bilirkişi</t>
+  </si>
+  <si>
+    <t>Birey</t>
+  </si>
+  <si>
+    <t>Birikim</t>
+  </si>
+  <si>
+    <t>Birim</t>
+  </si>
+  <si>
+    <t>Birincil</t>
+  </si>
+  <si>
+    <t>Birleşik</t>
+  </si>
+  <si>
+    <t>Birleşim</t>
+  </si>
+  <si>
+    <t>Bitki</t>
+  </si>
+  <si>
+    <t>Boylam</t>
+  </si>
+  <si>
+    <t>Boyut</t>
+  </si>
+  <si>
+    <t>Bölge</t>
+  </si>
+  <si>
+    <t>Bölü</t>
+  </si>
+  <si>
+    <t>Bölüm</t>
+  </si>
+  <si>
+    <t>Bucak</t>
+  </si>
+  <si>
+    <t>Bulgu</t>
+  </si>
+  <si>
+    <t>Bunalım</t>
+  </si>
+  <si>
+    <t>Bunaltıcı</t>
+  </si>
+  <si>
+    <t>Buzul</t>
+  </si>
+  <si>
+    <t>Bütüncül/Bütünsel</t>
+  </si>
+  <si>
+    <t>Bütünleme Sınavı</t>
+  </si>
+  <si>
+    <t>Büyüteç</t>
+  </si>
+  <si>
+    <t>Coşku</t>
+  </si>
+  <si>
+    <t>Cumhurbaşkanı</t>
+  </si>
+  <si>
+    <t>Cümlecik/Yan Cümlecik</t>
+  </si>
+  <si>
+    <t>Çaba</t>
+  </si>
+  <si>
+    <t>Çağdaş</t>
+  </si>
+  <si>
+    <t>Çağdışı</t>
+  </si>
+  <si>
+    <t>Çağrı</t>
+  </si>
+  <si>
+    <t>Çağrışım/Çağrıştırma</t>
+  </si>
+  <si>
+    <t>Çarpı/Çarpım</t>
+  </si>
+  <si>
+    <t>Çarpım Tablosu/Cetveli</t>
+  </si>
+  <si>
+    <t>Çatı(Gramer)</t>
+  </si>
+  <si>
+    <t>Çekim</t>
+  </si>
+  <si>
+    <t>Çekimser</t>
+  </si>
+  <si>
+    <t>Çekince</t>
+  </si>
+  <si>
+    <t>Çelişmek</t>
+  </si>
+  <si>
+    <t>Çeviri</t>
+  </si>
+  <si>
+    <t>Çıkarım</t>
+  </si>
+  <si>
+    <t>Çıkarsama</t>
+  </si>
+  <si>
+    <t>Çizelge</t>
+  </si>
+  <si>
+    <t>Çizer</t>
+  </si>
+  <si>
+    <t>Çoğul</t>
+  </si>
+  <si>
+    <t>Çoğunluk</t>
+  </si>
+  <si>
+    <t>Çokgen</t>
+  </si>
+  <si>
+    <t>Çökelti/Çöküntü</t>
+  </si>
+  <si>
+    <t>Çözelti</t>
+  </si>
+  <si>
+    <t>Çözüm</t>
+  </si>
+  <si>
+    <t>Çözümlemek</t>
+  </si>
+  <si>
+    <t>Dağılım</t>
+  </si>
+  <si>
+    <t>Dağıtım</t>
+  </si>
+  <si>
+    <t>Damıtmak</t>
+  </si>
+  <si>
+    <t>Danışman</t>
+  </si>
+  <si>
+    <t>Danıştay</t>
+  </si>
+  <si>
+    <t>Dayanak</t>
+  </si>
+  <si>
+    <t>Dayanışma</t>
+  </si>
+  <si>
+    <t>Değerbilir</t>
+  </si>
+  <si>
+    <t>Değer Yargısı</t>
+  </si>
+  <si>
+    <t>Değin</t>
+  </si>
+  <si>
+    <t>Değinmek</t>
+  </si>
+  <si>
+    <t>Değişim</t>
+  </si>
+  <si>
+    <t>Değişken</t>
+  </si>
+  <si>
+    <t>Delgeç</t>
+  </si>
+  <si>
+    <t>Demeç</t>
+  </si>
+  <si>
+    <t>Denek</t>
+  </si>
+  <si>
+    <t>Denet</t>
+  </si>
+  <si>
+    <t>Deney</t>
+  </si>
+  <si>
+    <t>Deneyim</t>
+  </si>
+  <si>
+    <t>Denge</t>
+  </si>
+  <si>
+    <t>Denklem</t>
+  </si>
+  <si>
+    <t>Deprem</t>
+  </si>
+  <si>
+    <t>Dergi</t>
+  </si>
+  <si>
+    <t>Derslik</t>
+  </si>
+  <si>
+    <t>Devingen/Devinim</t>
+  </si>
+  <si>
+    <t>Devrim</t>
+  </si>
+  <si>
+    <t>Deyim</t>
+  </si>
+  <si>
+    <t>Dışişleri</t>
+  </si>
+  <si>
+    <t>Dışkı</t>
+  </si>
+  <si>
+    <t>Dik Açı</t>
+  </si>
+  <si>
+    <t>Dikdörtgen</t>
+  </si>
+  <si>
+    <t>Dikey</t>
+  </si>
+  <si>
+    <t>Dilekçe</t>
+  </si>
+  <si>
+    <t>Dilek Kipi</t>
+  </si>
+  <si>
+    <t>Dingin</t>
+  </si>
+  <si>
+    <t>Direnç/Direniş</t>
+  </si>
+  <si>
+    <t>Dişil</t>
+  </si>
+  <si>
+    <t>Dize</t>
+  </si>
+  <si>
+    <t>Dizgi</t>
+  </si>
+  <si>
+    <t>Dizin</t>
+  </si>
+  <si>
+    <t>Doğa</t>
+  </si>
+  <si>
+    <t>Doğaç</t>
+  </si>
+  <si>
+    <t>Doğru Orantı</t>
+  </si>
+  <si>
+    <t>Doğrulamak</t>
+  </si>
+  <si>
+    <t>Doğrultu</t>
+  </si>
+  <si>
+    <t>Doku</t>
+  </si>
+  <si>
+    <t>Dokunulmaz</t>
+  </si>
+  <si>
+    <t>Dolaşım</t>
+  </si>
+  <si>
+    <t>Donanım</t>
+  </si>
+  <si>
+    <t>Donatım</t>
+  </si>
+  <si>
+    <t>Doygun</t>
+  </si>
+  <si>
+    <t>Döllemek</t>
+  </si>
+  <si>
+    <t>Dönem</t>
+  </si>
+  <si>
+    <t>Döngü</t>
+  </si>
+  <si>
+    <t>Dönence</t>
+  </si>
+  <si>
+    <t>Dönüşmek</t>
+  </si>
+  <si>
+    <t>Dört İşlem</t>
+  </si>
+  <si>
+    <t>Durağan</t>
+  </si>
+  <si>
+    <t>Durum</t>
+  </si>
+  <si>
+    <t>Duruşma</t>
+  </si>
+  <si>
+    <t>Duyar</t>
+  </si>
+  <si>
+    <t>Duyarga</t>
+  </si>
+  <si>
+    <t>Duyguculuk</t>
+  </si>
+  <si>
+    <t>Duygudaşlık</t>
+  </si>
+  <si>
+    <t>Duygulanım</t>
+  </si>
+  <si>
+    <t>Duygusal</t>
+  </si>
+  <si>
+    <t>Duyu</t>
+  </si>
+  <si>
+    <t>Duyum</t>
+  </si>
+  <si>
+    <t>Duyuru</t>
+  </si>
+  <si>
+    <t>Dürtü</t>
+  </si>
+  <si>
+    <t>Düş</t>
+  </si>
+  <si>
+    <t>Düşey</t>
+  </si>
+  <si>
+    <t>Düşlemek</t>
+  </si>
+  <si>
+    <t>Düşünce Özgürlüğü</t>
+  </si>
+  <si>
+    <t>Düşünür</t>
+  </si>
+  <si>
+    <t>Düzelti</t>
+  </si>
+  <si>
+    <t>Düzenlemek</t>
+  </si>
+  <si>
+    <t>Düzey</t>
+  </si>
+  <si>
+    <t>Düzlem</t>
+  </si>
+  <si>
+    <t>Düzyazı</t>
+  </si>
+  <si>
+    <t>Eder</t>
+  </si>
+  <si>
+    <t>Edilgen/Edilgin</t>
+  </si>
+  <si>
+    <t>Edinim</t>
+  </si>
+  <si>
+    <t>Egemen</t>
+  </si>
+  <si>
+    <t>Eğilim</t>
+  </si>
+  <si>
+    <t>Eğim</t>
+  </si>
+  <si>
+    <t>Eğitmek</t>
+  </si>
+  <si>
+    <t>Ekim</t>
+  </si>
+  <si>
+    <t>Eklem</t>
+  </si>
+  <si>
+    <t>Eksen</t>
+  </si>
+  <si>
+    <t>Eksi</t>
+  </si>
+  <si>
+    <t>Eleştirmek</t>
+  </si>
+  <si>
+    <t>Emekli</t>
+  </si>
+  <si>
+    <t>Erdem</t>
+  </si>
+  <si>
+    <t>Erek</t>
+  </si>
+  <si>
+    <t>Eril</t>
+  </si>
+  <si>
+    <t>Erişim</t>
+  </si>
+  <si>
+    <t>Erk/Erke</t>
+  </si>
+  <si>
+    <t>Esen Kalın</t>
+  </si>
+  <si>
+    <t>Esin</t>
+  </si>
+  <si>
+    <t>Eşanlam</t>
+  </si>
+  <si>
+    <t>Eşcinsel</t>
+  </si>
+  <si>
+    <t>Eşdeğer</t>
+  </si>
+  <si>
+    <t>Eşey</t>
+  </si>
+  <si>
+    <t>Eşgüdüm</t>
+  </si>
+  <si>
+    <t>Eşit</t>
+  </si>
+  <si>
+    <t>Eşsesli</t>
+  </si>
+  <si>
+    <t>Etçil</t>
+  </si>
+  <si>
+    <t>Etken</t>
+  </si>
+  <si>
+    <t>Etki</t>
+  </si>
+  <si>
+    <t>Etmen</t>
+  </si>
+  <si>
+    <t>Evcil</t>
+  </si>
+  <si>
+    <t>Evirtik/Evirtim</t>
+  </si>
+  <si>
+    <t>Evre</t>
+  </si>
+  <si>
+    <t>Evren</t>
+  </si>
+  <si>
+    <t>Evrik</t>
+  </si>
+  <si>
+    <t>Evrim</t>
+  </si>
+  <si>
+    <t>Eylem</t>
+  </si>
+  <si>
+    <t>Fizikötesi</t>
+  </si>
+  <si>
+    <t>Geçerli</t>
+  </si>
+  <si>
+    <t>Geçerlilik</t>
+  </si>
+  <si>
+    <t>Geçersiz</t>
+  </si>
+  <si>
+    <t>Geçirgen</t>
+  </si>
+  <si>
+    <t>Geçiş Dönemi</t>
+  </si>
+  <si>
+    <t>Geçişken</t>
+  </si>
+  <si>
+    <t>Gelenek</t>
+  </si>
+  <si>
+    <t>Gelgit</t>
+  </si>
+  <si>
+    <t>Gelişim</t>
+  </si>
+  <si>
+    <t>Genel</t>
+  </si>
+  <si>
+    <t>Genleşme</t>
+  </si>
+  <si>
+    <t>Gerçekleşmek</t>
+  </si>
+  <si>
+    <t>Gereç</t>
+  </si>
+  <si>
+    <t>Gereğince</t>
+  </si>
+  <si>
+    <t>Gerekçe</t>
+  </si>
+  <si>
+    <t>Gereklilik</t>
+  </si>
+  <si>
+    <t>Gereksemek/Gereksinmek</t>
+  </si>
+  <si>
+    <t>Gerektirmek</t>
+  </si>
+  <si>
+    <t>Gerici</t>
+  </si>
+  <si>
+    <t>Gerilim</t>
+  </si>
+  <si>
+    <t>Getiri</t>
+  </si>
+  <si>
+    <t>Gezegen</t>
+  </si>
+  <si>
+    <t>Gider</t>
+  </si>
+  <si>
+    <t>Girişim</t>
+  </si>
+  <si>
+    <t>Giysi</t>
+  </si>
+  <si>
+    <t>Giz/Gizem</t>
+  </si>
+  <si>
+    <t>Gizli Ödenek</t>
+  </si>
+  <si>
+    <t>Gizli Oturum</t>
+  </si>
+  <si>
+    <t>Göçmen</t>
+  </si>
+  <si>
+    <t>Gönderi</t>
+  </si>
+  <si>
+    <t>Görece/Göreli</t>
+  </si>
+  <si>
+    <t>Görev</t>
+  </si>
+  <si>
+    <t>Görkem</t>
+  </si>
+  <si>
+    <t>Görüntü</t>
+  </si>
+  <si>
+    <t>Görünüm</t>
+  </si>
+  <si>
+    <t>Gösterge</t>
+  </si>
+  <si>
+    <t>Gösteri</t>
+  </si>
+  <si>
+    <t>Göstermelik</t>
+  </si>
+  <si>
+    <t>Gözaltı</t>
+  </si>
+  <si>
+    <t>Gözetim</t>
+  </si>
+  <si>
+    <t>Gözetmen</t>
+  </si>
+  <si>
+    <t>Gözlem</t>
+  </si>
+  <si>
+    <t>Gözlemlemek</t>
+  </si>
+  <si>
+    <t>Güç Odağı</t>
+  </si>
+  <si>
+    <t>Güdü</t>
+  </si>
+  <si>
+    <t>Güdüm</t>
+  </si>
+  <si>
+    <t>Günaydın</t>
+  </si>
+  <si>
+    <t>Günce</t>
+  </si>
+  <si>
+    <t>Güncel</t>
+  </si>
+  <si>
+    <t>Gündem</t>
+  </si>
+  <si>
+    <t>Güney</t>
+  </si>
+  <si>
+    <t>Günlük</t>
+  </si>
+  <si>
+    <t>Güven</t>
+  </si>
+  <si>
+    <t>Güvence</t>
+  </si>
+  <si>
+    <t>Güvenoyu</t>
+  </si>
+  <si>
+    <t>h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,6 +1096,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="162"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,9 +1125,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,7 +1465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{984A1489-2204-4320-8C2B-598D19BA0E68}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H338"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -480,6 +1504,1712 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Documents\siteicin-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5060491-5F3F-466D-8161-52E0AB712DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{051BDC8B-E4B1-422C-8E98-28294CF503E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
+    <workbookView xWindow="0" yWindow="384" windowWidth="23040" windowHeight="12240" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>

--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Documents\siteicin-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{051BDC8B-E4B1-422C-8E98-28294CF503E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85667E0-13C6-43B2-B093-468E802A7DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="384" windowWidth="23040" windowHeight="12240" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="351">
   <si>
     <t>kelime_adi</t>
   </si>
@@ -1077,12 +1077,32 @@
   </si>
   <si>
     <t>h</t>
+  </si>
+  <si>
+    <t>Anadolu halk ağızlarında (Konya şivesinde) tespit edilmiştir.</t>
+  </si>
+  <si>
+    <t>Tarama Dergisi (1934)</t>
+  </si>
+  <si>
+    <t>1)mübalağa/mubālaġa (ﻣﺒﺎﻟﻐﻪ)
+2)ifrat/ifrāṭ (ﺍﻓﺮﺍﻁ)
+3)izam/i‘ẓām (ﺇﻋﻈﺎﻡ)</t>
+  </si>
+  <si>
+    <t>2)ifrat/ifrāṭ (ﺍﻓﺮﺍﻁ)</t>
+  </si>
+  <si>
+    <t>3)izam/i‘ẓām (ﺇﻋﻈﺎﻡ)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode=";;;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -1125,12 +1145,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1469,13 +1494,14 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="33.88671875" customWidth="1"/>
-    <col min="4" max="4" width="35.5546875" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.21875" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="32" style="3" customWidth="1"/>
+    <col min="3" max="3" width="33.88671875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="35.5546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="16.21875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1494,7 +1520,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -1508,25 +1534,19 @@
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F2" t="s">
-        <v>345</v>
-      </c>
-      <c r="G2" t="s">
-        <v>345</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>345</v>
       </c>
     </row>
@@ -1534,10 +1554,16 @@
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="E3" s="3" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Documents\siteicin-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85667E0-13C6-43B2-B093-468E802A7DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71091E1-9863-454D-8009-57C2614183AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="348">
   <si>
     <t>kelime_adi</t>
   </si>
@@ -1074,9 +1074,6 @@
   </si>
   <si>
     <t>Güvenoyu</t>
-  </si>
-  <si>
-    <t>h</t>
   </si>
   <si>
     <t>Anadolu halk ağızlarında (Konya şivesinde) tespit edilmiştir.</t>
@@ -1088,12 +1085,6 @@
     <t>1)mübalağa/mubālaġa (ﻣﺒﺎﻟﻐﻪ)
 2)ifrat/ifrāṭ (ﺍﻓﺮﺍﻁ)
 3)izam/i‘ẓām (ﺇﻋﻈﺎﻡ)</t>
-  </si>
-  <si>
-    <t>2)ifrat/ifrāṭ (ﺍﻓﺮﺍﻁ)</t>
-  </si>
-  <si>
-    <t>3)izam/i‘ẓām (ﺇﻋﻈﺎﻡ)</t>
   </si>
 </sst>
 </file>
@@ -1535,35 +1526,23 @@
         <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>349</v>
-      </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Documents\siteicin-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71091E1-9863-454D-8009-57C2614183AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A16872-E86B-4CCE-B713-6567B8CD61E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="351">
   <si>
     <t>kelime_adi</t>
   </si>
@@ -1074,9 +1074,6 @@
   </si>
   <si>
     <t>Güvenoyu</t>
-  </si>
-  <si>
-    <t>Anadolu halk ağızlarında (Konya şivesinde) tespit edilmiştir.</t>
   </si>
   <si>
     <t>Tarama Dergisi (1934)</t>
@@ -1085,6 +1082,22 @@
     <t>1)mübalağa/mubālaġa (ﻣﺒﺎﻟﻐﻪ)
 2)ifrat/ifrāṭ (ﺍﻓﺮﺍﻁ)
 3)izam/i‘ẓām (ﺇﻋﻈﺎﻡ)</t>
+  </si>
+  <si>
+    <t>Tarama Dergisinde Konya şivesinden olduğu kaydı vardır.</t>
+  </si>
+  <si>
+    <t>Anadolu halk ağızları</t>
+  </si>
+  <si>
+    <t>Neolojizm/Kelime uydurma</t>
+  </si>
+  <si>
+    <t>1)Merhametsiz   [merhamet/merhamet (ﻣﺮﺣﻤﺖ)]
+2)İnsafsız   [insaf/inṣāf (ﺍﻧﺼﺎﻒ)]
+3)Amansız   [aman/emān (ﺍﻣﺎﻥ)]
+4)Gaddar/ġaddār (غدّار)
+5)Zalim/ẓālim (ﻇﺎﻟﻢ)</t>
   </si>
 </sst>
 </file>
@@ -1526,18 +1539,27 @@
         <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Documents\siteicin-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A16872-E86B-4CCE-B713-6567B8CD61E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C223843-B447-475E-BECC-CA0C81708159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="804">
   <si>
     <t>kelime_adi</t>
   </si>
@@ -63,1017 +63,6 @@
   </si>
   <si>
     <t>mustak_kelimeler</t>
-  </si>
-  <si>
-    <t>Abartmak</t>
-  </si>
-  <si>
-    <t>Acımasız</t>
-  </si>
-  <si>
-    <t>Açı</t>
-  </si>
-  <si>
-    <t>Açık artırma</t>
-  </si>
-  <si>
-    <t>Açıklamak</t>
-  </si>
-  <si>
-    <t>Açık Oturum</t>
-  </si>
-  <si>
-    <t>Açık Oy</t>
-  </si>
-  <si>
-    <t>Açılım</t>
-  </si>
-  <si>
-    <t>Açılış Töreni</t>
-  </si>
-  <si>
-    <t>Aday</t>
-  </si>
-  <si>
-    <t>Akaryakıt</t>
-  </si>
-  <si>
-    <t>Akıcı</t>
-  </si>
-  <si>
-    <t>Akım</t>
-  </si>
-  <si>
-    <t>Akışkan</t>
-  </si>
-  <si>
-    <t>Akkor</t>
-  </si>
-  <si>
-    <t>Akyuvar</t>
-  </si>
-  <si>
-    <t>Alan</t>
-  </si>
-  <si>
-    <t>Albay</t>
-  </si>
-  <si>
-    <t>Algı</t>
-  </si>
-  <si>
-    <t>Alımlı</t>
-  </si>
-  <si>
-    <t>Alıntı</t>
-  </si>
-  <si>
-    <t>Almaç</t>
-  </si>
-  <si>
-    <t>Amaç</t>
-  </si>
-  <si>
-    <t>Anaerkil</t>
-  </si>
-  <si>
-    <t>Anayasa</t>
-  </si>
-  <si>
-    <t>Anı</t>
-  </si>
-  <si>
-    <t>Anıt</t>
-  </si>
-  <si>
-    <t>Anlam</t>
-  </si>
-  <si>
-    <t>Anlaşmazlık</t>
-  </si>
-  <si>
-    <t>Anlatı/Anlatım</t>
-  </si>
-  <si>
-    <t>Anlayış</t>
-  </si>
-  <si>
-    <t>Anma Töreni</t>
-  </si>
-  <si>
-    <t>Aracı</t>
-  </si>
-  <si>
-    <t>Araç</t>
-  </si>
-  <si>
-    <t>Araç-gereç</t>
-  </si>
-  <si>
-    <t>Arakesit</t>
-  </si>
-  <si>
-    <t>Aralık</t>
-  </si>
-  <si>
-    <t>Arasöz</t>
-  </si>
-  <si>
-    <t>Ardıl</t>
-  </si>
-  <si>
-    <t>Ardışık</t>
-  </si>
-  <si>
-    <t>Artı</t>
-  </si>
-  <si>
-    <t>Asalak</t>
-  </si>
-  <si>
-    <t>Ast</t>
-  </si>
-  <si>
-    <t>Astsubay</t>
-  </si>
-  <si>
-    <t>Asteğmen</t>
-  </si>
-  <si>
-    <t>Aşama</t>
-  </si>
-  <si>
-    <t>Ataerkil</t>
-  </si>
-  <si>
-    <t>Atama/Atanma</t>
-  </si>
-  <si>
-    <t>Atardamar</t>
-  </si>
-  <si>
-    <t>Ateşkes</t>
-  </si>
-  <si>
-    <t>Atılım</t>
-  </si>
-  <si>
-    <t>Avuntu</t>
-  </si>
-  <si>
-    <t>Aydın</t>
-  </si>
-  <si>
-    <t>Aygıt</t>
-  </si>
-  <si>
-    <t>Ayırtman</t>
-  </si>
-  <si>
-    <t>Aymaz</t>
-  </si>
-  <si>
-    <t>Ayraç</t>
-  </si>
-  <si>
-    <t>Ayrıcalık</t>
-  </si>
-  <si>
-    <t>Ayrım</t>
-  </si>
-  <si>
-    <t>Ayrıntı</t>
-  </si>
-  <si>
-    <t>Ayrışık</t>
-  </si>
-  <si>
-    <t>Ayrışma</t>
-  </si>
-  <si>
-    <t>Azınlık</t>
-  </si>
-  <si>
-    <t>Bağıl</t>
-  </si>
-  <si>
-    <t>Bağımlı</t>
-  </si>
-  <si>
-    <t>Bağımsız</t>
-  </si>
-  <si>
-    <t>Bağıntı</t>
-  </si>
-  <si>
-    <t>Bağışık/Bağışıklık</t>
-  </si>
-  <si>
-    <t>Bağlaç</t>
-  </si>
-  <si>
-    <t>Bağlam</t>
-  </si>
-  <si>
-    <t>Bağlantı</t>
-  </si>
-  <si>
-    <t>Bağlaşık-Bağdaşık</t>
-  </si>
-  <si>
-    <t>Bağnaz</t>
-  </si>
-  <si>
-    <t>Bakan</t>
-  </si>
-  <si>
-    <t>Bakış açısı</t>
-  </si>
-  <si>
-    <t>Barınak</t>
-  </si>
-  <si>
-    <t>Barış Anlaşması</t>
-  </si>
-  <si>
-    <t>Barışçıl-Barışsever</t>
-  </si>
-  <si>
-    <t>Basın</t>
-  </si>
-  <si>
-    <t>Basınç</t>
-  </si>
-  <si>
-    <t>Başarı</t>
-  </si>
-  <si>
-    <t>Başat</t>
-  </si>
-  <si>
-    <t>Başbuğ</t>
-  </si>
-  <si>
-    <t>Başkaldırı</t>
-  </si>
-  <si>
-    <t>Başkanlık</t>
-  </si>
-  <si>
-    <t>Başkent</t>
-  </si>
-  <si>
-    <t>Başvuru</t>
-  </si>
-  <si>
-    <t>Başyapıt</t>
-  </si>
-  <si>
-    <t>Başyazar</t>
-  </si>
-  <si>
-    <t>Bay</t>
-  </si>
-  <si>
-    <t>Bayan</t>
-  </si>
-  <si>
-    <t>Bayındır/Bayındırlık</t>
-  </si>
-  <si>
-    <t>Beğeni</t>
-  </si>
-  <si>
-    <t>Belge</t>
-  </si>
-  <si>
-    <t>Belirgin</t>
-  </si>
-  <si>
-    <t>Belirlemek</t>
-  </si>
-  <si>
-    <t>Belirli</t>
-  </si>
-  <si>
-    <t>Belirteç</t>
-  </si>
-  <si>
-    <t>Belirti</t>
-  </si>
-  <si>
-    <t>Bellek</t>
-  </si>
-  <si>
-    <t>Belletici/Belletmen</t>
-  </si>
-  <si>
-    <t>Bencil</t>
-  </si>
-  <si>
-    <t>Besin</t>
-  </si>
-  <si>
-    <t>Beşgen</t>
-  </si>
-  <si>
-    <t>Betim/Betimlemek</t>
-  </si>
-  <si>
-    <t>Bildirge/Bildiri</t>
-  </si>
-  <si>
-    <t>Bileşen</t>
-  </si>
-  <si>
-    <t>Bileşik</t>
-  </si>
-  <si>
-    <t>Bileşim</t>
-  </si>
-  <si>
-    <t>Bileşke</t>
-  </si>
-  <si>
-    <t>Bilge/Bilgelik</t>
-  </si>
-  <si>
-    <t>Bilgi-Birikim</t>
-  </si>
-  <si>
-    <t>Bilgin</t>
-  </si>
-  <si>
-    <t>Bilim</t>
-  </si>
-  <si>
-    <t>Bilinç</t>
-  </si>
-  <si>
-    <t>Bilirkişi</t>
-  </si>
-  <si>
-    <t>Birey</t>
-  </si>
-  <si>
-    <t>Birikim</t>
-  </si>
-  <si>
-    <t>Birim</t>
-  </si>
-  <si>
-    <t>Birincil</t>
-  </si>
-  <si>
-    <t>Birleşik</t>
-  </si>
-  <si>
-    <t>Birleşim</t>
-  </si>
-  <si>
-    <t>Bitki</t>
-  </si>
-  <si>
-    <t>Boylam</t>
-  </si>
-  <si>
-    <t>Boyut</t>
-  </si>
-  <si>
-    <t>Bölge</t>
-  </si>
-  <si>
-    <t>Bölü</t>
-  </si>
-  <si>
-    <t>Bölüm</t>
-  </si>
-  <si>
-    <t>Bucak</t>
-  </si>
-  <si>
-    <t>Bulgu</t>
-  </si>
-  <si>
-    <t>Bunalım</t>
-  </si>
-  <si>
-    <t>Bunaltıcı</t>
-  </si>
-  <si>
-    <t>Buzul</t>
-  </si>
-  <si>
-    <t>Bütüncül/Bütünsel</t>
-  </si>
-  <si>
-    <t>Bütünleme Sınavı</t>
-  </si>
-  <si>
-    <t>Büyüteç</t>
-  </si>
-  <si>
-    <t>Coşku</t>
-  </si>
-  <si>
-    <t>Cumhurbaşkanı</t>
-  </si>
-  <si>
-    <t>Cümlecik/Yan Cümlecik</t>
-  </si>
-  <si>
-    <t>Çaba</t>
-  </si>
-  <si>
-    <t>Çağdaş</t>
-  </si>
-  <si>
-    <t>Çağdışı</t>
-  </si>
-  <si>
-    <t>Çağrı</t>
-  </si>
-  <si>
-    <t>Çağrışım/Çağrıştırma</t>
-  </si>
-  <si>
-    <t>Çarpı/Çarpım</t>
-  </si>
-  <si>
-    <t>Çarpım Tablosu/Cetveli</t>
-  </si>
-  <si>
-    <t>Çatı(Gramer)</t>
-  </si>
-  <si>
-    <t>Çekim</t>
-  </si>
-  <si>
-    <t>Çekimser</t>
-  </si>
-  <si>
-    <t>Çekince</t>
-  </si>
-  <si>
-    <t>Çelişmek</t>
-  </si>
-  <si>
-    <t>Çeviri</t>
-  </si>
-  <si>
-    <t>Çıkarım</t>
-  </si>
-  <si>
-    <t>Çıkarsama</t>
-  </si>
-  <si>
-    <t>Çizelge</t>
-  </si>
-  <si>
-    <t>Çizer</t>
-  </si>
-  <si>
-    <t>Çoğul</t>
-  </si>
-  <si>
-    <t>Çoğunluk</t>
-  </si>
-  <si>
-    <t>Çokgen</t>
-  </si>
-  <si>
-    <t>Çökelti/Çöküntü</t>
-  </si>
-  <si>
-    <t>Çözelti</t>
-  </si>
-  <si>
-    <t>Çözüm</t>
-  </si>
-  <si>
-    <t>Çözümlemek</t>
-  </si>
-  <si>
-    <t>Dağılım</t>
-  </si>
-  <si>
-    <t>Dağıtım</t>
-  </si>
-  <si>
-    <t>Damıtmak</t>
-  </si>
-  <si>
-    <t>Danışman</t>
-  </si>
-  <si>
-    <t>Danıştay</t>
-  </si>
-  <si>
-    <t>Dayanak</t>
-  </si>
-  <si>
-    <t>Dayanışma</t>
-  </si>
-  <si>
-    <t>Değerbilir</t>
-  </si>
-  <si>
-    <t>Değer Yargısı</t>
-  </si>
-  <si>
-    <t>Değin</t>
-  </si>
-  <si>
-    <t>Değinmek</t>
-  </si>
-  <si>
-    <t>Değişim</t>
-  </si>
-  <si>
-    <t>Değişken</t>
-  </si>
-  <si>
-    <t>Delgeç</t>
-  </si>
-  <si>
-    <t>Demeç</t>
-  </si>
-  <si>
-    <t>Denek</t>
-  </si>
-  <si>
-    <t>Denet</t>
-  </si>
-  <si>
-    <t>Deney</t>
-  </si>
-  <si>
-    <t>Deneyim</t>
-  </si>
-  <si>
-    <t>Denge</t>
-  </si>
-  <si>
-    <t>Denklem</t>
-  </si>
-  <si>
-    <t>Deprem</t>
-  </si>
-  <si>
-    <t>Dergi</t>
-  </si>
-  <si>
-    <t>Derslik</t>
-  </si>
-  <si>
-    <t>Devingen/Devinim</t>
-  </si>
-  <si>
-    <t>Devrim</t>
-  </si>
-  <si>
-    <t>Deyim</t>
-  </si>
-  <si>
-    <t>Dışişleri</t>
-  </si>
-  <si>
-    <t>Dışkı</t>
-  </si>
-  <si>
-    <t>Dik Açı</t>
-  </si>
-  <si>
-    <t>Dikdörtgen</t>
-  </si>
-  <si>
-    <t>Dikey</t>
-  </si>
-  <si>
-    <t>Dilekçe</t>
-  </si>
-  <si>
-    <t>Dilek Kipi</t>
-  </si>
-  <si>
-    <t>Dingin</t>
-  </si>
-  <si>
-    <t>Direnç/Direniş</t>
-  </si>
-  <si>
-    <t>Dişil</t>
-  </si>
-  <si>
-    <t>Dize</t>
-  </si>
-  <si>
-    <t>Dizgi</t>
-  </si>
-  <si>
-    <t>Dizin</t>
-  </si>
-  <si>
-    <t>Doğa</t>
-  </si>
-  <si>
-    <t>Doğaç</t>
-  </si>
-  <si>
-    <t>Doğru Orantı</t>
-  </si>
-  <si>
-    <t>Doğrulamak</t>
-  </si>
-  <si>
-    <t>Doğrultu</t>
-  </si>
-  <si>
-    <t>Doku</t>
-  </si>
-  <si>
-    <t>Dokunulmaz</t>
-  </si>
-  <si>
-    <t>Dolaşım</t>
-  </si>
-  <si>
-    <t>Donanım</t>
-  </si>
-  <si>
-    <t>Donatım</t>
-  </si>
-  <si>
-    <t>Doygun</t>
-  </si>
-  <si>
-    <t>Döllemek</t>
-  </si>
-  <si>
-    <t>Dönem</t>
-  </si>
-  <si>
-    <t>Döngü</t>
-  </si>
-  <si>
-    <t>Dönence</t>
-  </si>
-  <si>
-    <t>Dönüşmek</t>
-  </si>
-  <si>
-    <t>Dört İşlem</t>
-  </si>
-  <si>
-    <t>Durağan</t>
-  </si>
-  <si>
-    <t>Durum</t>
-  </si>
-  <si>
-    <t>Duruşma</t>
-  </si>
-  <si>
-    <t>Duyar</t>
-  </si>
-  <si>
-    <t>Duyarga</t>
-  </si>
-  <si>
-    <t>Duyguculuk</t>
-  </si>
-  <si>
-    <t>Duygudaşlık</t>
-  </si>
-  <si>
-    <t>Duygulanım</t>
-  </si>
-  <si>
-    <t>Duygusal</t>
-  </si>
-  <si>
-    <t>Duyu</t>
-  </si>
-  <si>
-    <t>Duyum</t>
-  </si>
-  <si>
-    <t>Duyuru</t>
-  </si>
-  <si>
-    <t>Dürtü</t>
-  </si>
-  <si>
-    <t>Düş</t>
-  </si>
-  <si>
-    <t>Düşey</t>
-  </si>
-  <si>
-    <t>Düşlemek</t>
-  </si>
-  <si>
-    <t>Düşünce Özgürlüğü</t>
-  </si>
-  <si>
-    <t>Düşünür</t>
-  </si>
-  <si>
-    <t>Düzelti</t>
-  </si>
-  <si>
-    <t>Düzenlemek</t>
-  </si>
-  <si>
-    <t>Düzey</t>
-  </si>
-  <si>
-    <t>Düzlem</t>
-  </si>
-  <si>
-    <t>Düzyazı</t>
-  </si>
-  <si>
-    <t>Eder</t>
-  </si>
-  <si>
-    <t>Edilgen/Edilgin</t>
-  </si>
-  <si>
-    <t>Edinim</t>
-  </si>
-  <si>
-    <t>Egemen</t>
-  </si>
-  <si>
-    <t>Eğilim</t>
-  </si>
-  <si>
-    <t>Eğim</t>
-  </si>
-  <si>
-    <t>Eğitmek</t>
-  </si>
-  <si>
-    <t>Ekim</t>
-  </si>
-  <si>
-    <t>Eklem</t>
-  </si>
-  <si>
-    <t>Eksen</t>
-  </si>
-  <si>
-    <t>Eksi</t>
-  </si>
-  <si>
-    <t>Eleştirmek</t>
-  </si>
-  <si>
-    <t>Emekli</t>
-  </si>
-  <si>
-    <t>Erdem</t>
-  </si>
-  <si>
-    <t>Erek</t>
-  </si>
-  <si>
-    <t>Eril</t>
-  </si>
-  <si>
-    <t>Erişim</t>
-  </si>
-  <si>
-    <t>Erk/Erke</t>
-  </si>
-  <si>
-    <t>Esen Kalın</t>
-  </si>
-  <si>
-    <t>Esin</t>
-  </si>
-  <si>
-    <t>Eşanlam</t>
-  </si>
-  <si>
-    <t>Eşcinsel</t>
-  </si>
-  <si>
-    <t>Eşdeğer</t>
-  </si>
-  <si>
-    <t>Eşey</t>
-  </si>
-  <si>
-    <t>Eşgüdüm</t>
-  </si>
-  <si>
-    <t>Eşit</t>
-  </si>
-  <si>
-    <t>Eşsesli</t>
-  </si>
-  <si>
-    <t>Etçil</t>
-  </si>
-  <si>
-    <t>Etken</t>
-  </si>
-  <si>
-    <t>Etki</t>
-  </si>
-  <si>
-    <t>Etmen</t>
-  </si>
-  <si>
-    <t>Evcil</t>
-  </si>
-  <si>
-    <t>Evirtik/Evirtim</t>
-  </si>
-  <si>
-    <t>Evre</t>
-  </si>
-  <si>
-    <t>Evren</t>
-  </si>
-  <si>
-    <t>Evrik</t>
-  </si>
-  <si>
-    <t>Evrim</t>
-  </si>
-  <si>
-    <t>Eylem</t>
-  </si>
-  <si>
-    <t>Fizikötesi</t>
-  </si>
-  <si>
-    <t>Geçerli</t>
-  </si>
-  <si>
-    <t>Geçerlilik</t>
-  </si>
-  <si>
-    <t>Geçersiz</t>
-  </si>
-  <si>
-    <t>Geçirgen</t>
-  </si>
-  <si>
-    <t>Geçiş Dönemi</t>
-  </si>
-  <si>
-    <t>Geçişken</t>
-  </si>
-  <si>
-    <t>Gelenek</t>
-  </si>
-  <si>
-    <t>Gelgit</t>
-  </si>
-  <si>
-    <t>Gelişim</t>
-  </si>
-  <si>
-    <t>Genel</t>
-  </si>
-  <si>
-    <t>Genleşme</t>
-  </si>
-  <si>
-    <t>Gerçekleşmek</t>
-  </si>
-  <si>
-    <t>Gereç</t>
-  </si>
-  <si>
-    <t>Gereğince</t>
-  </si>
-  <si>
-    <t>Gerekçe</t>
-  </si>
-  <si>
-    <t>Gereklilik</t>
-  </si>
-  <si>
-    <t>Gereksemek/Gereksinmek</t>
-  </si>
-  <si>
-    <t>Gerektirmek</t>
-  </si>
-  <si>
-    <t>Gerici</t>
-  </si>
-  <si>
-    <t>Gerilim</t>
-  </si>
-  <si>
-    <t>Getiri</t>
-  </si>
-  <si>
-    <t>Gezegen</t>
-  </si>
-  <si>
-    <t>Gider</t>
-  </si>
-  <si>
-    <t>Girişim</t>
-  </si>
-  <si>
-    <t>Giysi</t>
-  </si>
-  <si>
-    <t>Giz/Gizem</t>
-  </si>
-  <si>
-    <t>Gizli Ödenek</t>
-  </si>
-  <si>
-    <t>Gizli Oturum</t>
-  </si>
-  <si>
-    <t>Göçmen</t>
-  </si>
-  <si>
-    <t>Gönderi</t>
-  </si>
-  <si>
-    <t>Görece/Göreli</t>
-  </si>
-  <si>
-    <t>Görev</t>
-  </si>
-  <si>
-    <t>Görkem</t>
-  </si>
-  <si>
-    <t>Görüntü</t>
-  </si>
-  <si>
-    <t>Görünüm</t>
-  </si>
-  <si>
-    <t>Gösterge</t>
-  </si>
-  <si>
-    <t>Gösteri</t>
-  </si>
-  <si>
-    <t>Göstermelik</t>
-  </si>
-  <si>
-    <t>Gözaltı</t>
-  </si>
-  <si>
-    <t>Gözetim</t>
-  </si>
-  <si>
-    <t>Gözetmen</t>
-  </si>
-  <si>
-    <t>Gözlem</t>
-  </si>
-  <si>
-    <t>Gözlemlemek</t>
-  </si>
-  <si>
-    <t>Güç Odağı</t>
-  </si>
-  <si>
-    <t>Güdü</t>
-  </si>
-  <si>
-    <t>Güdüm</t>
-  </si>
-  <si>
-    <t>Günaydın</t>
-  </si>
-  <si>
-    <t>Günce</t>
-  </si>
-  <si>
-    <t>Güncel</t>
-  </si>
-  <si>
-    <t>Gündem</t>
-  </si>
-  <si>
-    <t>Güney</t>
-  </si>
-  <si>
-    <t>Günlük</t>
-  </si>
-  <si>
-    <t>Güven</t>
-  </si>
-  <si>
-    <t>Güvence</t>
-  </si>
-  <si>
-    <t>Güvenoyu</t>
   </si>
   <si>
     <t>Tarama Dergisi (1934)</t>
@@ -1098,6 +87,2376 @@
 3)Amansız   [aman/emān (ﺍﻣﺎﻥ)]
 4)Gaddar/ġaddār (غدّار)
 5)Zalim/ẓālim (ﻇﺎﻟﻢ)</t>
+  </si>
+  <si>
+    <t>ABARTMAK</t>
+  </si>
+  <si>
+    <t>ACIMASIZ</t>
+  </si>
+  <si>
+    <t>ACUN</t>
+  </si>
+  <si>
+    <t>AÇI</t>
+  </si>
+  <si>
+    <t>AÇIK ARTIRMA</t>
+  </si>
+  <si>
+    <t>AÇIKLAMAK</t>
+  </si>
+  <si>
+    <t>AÇIK OTURUM</t>
+  </si>
+  <si>
+    <t>AÇIK OY</t>
+  </si>
+  <si>
+    <t>AÇILIM</t>
+  </si>
+  <si>
+    <t>ADAY</t>
+  </si>
+  <si>
+    <t>AD ÇEKMEK</t>
+  </si>
+  <si>
+    <t>AHLÂKSAL</t>
+  </si>
+  <si>
+    <t>ÂİLE BİREYLERİ</t>
+  </si>
+  <si>
+    <t>AKARYAKIT</t>
+  </si>
+  <si>
+    <t>AKÇASAL</t>
+  </si>
+  <si>
+    <t>AKIM</t>
+  </si>
+  <si>
+    <t>AKKOR</t>
+  </si>
+  <si>
+    <t>AKYUVAR</t>
+  </si>
+  <si>
+    <t>ALAN</t>
+  </si>
+  <si>
+    <t>ALBAY</t>
+  </si>
+  <si>
+    <t>ALGI</t>
+  </si>
+  <si>
+    <t>ALIMLI</t>
+  </si>
+  <si>
+    <t>ALINDI</t>
+  </si>
+  <si>
+    <t>ALINTI</t>
+  </si>
+  <si>
+    <t>ALMAÇ</t>
+  </si>
+  <si>
+    <t>AMAÇ</t>
+  </si>
+  <si>
+    <t>ANAERKİ</t>
+  </si>
+  <si>
+    <t>ANA GÜNDEM MADDESİ</t>
+  </si>
+  <si>
+    <t>ANAYASA</t>
+  </si>
+  <si>
+    <t>ANI</t>
+  </si>
+  <si>
+    <t>ANIMSAMAK</t>
+  </si>
+  <si>
+    <t>ANIT</t>
+  </si>
+  <si>
+    <t>ANLAM</t>
+  </si>
+  <si>
+    <t>ANLAŞMAZLIK</t>
+  </si>
+  <si>
+    <t>ANLATI</t>
+  </si>
+  <si>
+    <t>ANLAYIŞ</t>
+  </si>
+  <si>
+    <t>ANMA TÖRENİ</t>
+  </si>
+  <si>
+    <t>ARACI</t>
+  </si>
+  <si>
+    <t>ARAÇ</t>
+  </si>
+  <si>
+    <t>ARAKESİT</t>
+  </si>
+  <si>
+    <t>ARALIK</t>
+  </si>
+  <si>
+    <t>ARASÖZ</t>
+  </si>
+  <si>
+    <t>ARAŞTIRMA KURULU</t>
+  </si>
+  <si>
+    <t>ARDIL</t>
+  </si>
+  <si>
+    <t>ARILAŞTIRMA</t>
+  </si>
+  <si>
+    <t>ARTI</t>
+  </si>
+  <si>
+    <t>ASALAK</t>
+  </si>
+  <si>
+    <t>AST</t>
+  </si>
+  <si>
+    <t>ASTSUBAY</t>
+  </si>
+  <si>
+    <t>ASTEĞMEN</t>
+  </si>
+  <si>
+    <t>AŞAMA</t>
+  </si>
+  <si>
+    <t>ATAERKİ</t>
+  </si>
+  <si>
+    <t>ATAMAK</t>
+  </si>
+  <si>
+    <t>ATARDAMAR</t>
+  </si>
+  <si>
+    <t>ATEŞKES</t>
+  </si>
+  <si>
+    <t>ATILIM</t>
+  </si>
+  <si>
+    <t>AVUNTU</t>
+  </si>
+  <si>
+    <t>AYÇA</t>
+  </si>
+  <si>
+    <t>AYDIN</t>
+  </si>
+  <si>
+    <t>AYGIT</t>
+  </si>
+  <si>
+    <t>AYIRTMAN</t>
+  </si>
+  <si>
+    <t>AYMAZ</t>
+  </si>
+  <si>
+    <t>AYRAÇ</t>
+  </si>
+  <si>
+    <t>AYRICALIK</t>
+  </si>
+  <si>
+    <t>AYRIM</t>
+  </si>
+  <si>
+    <t>AYRINTI</t>
+  </si>
+  <si>
+    <t>AYRIŞIK</t>
+  </si>
+  <si>
+    <t>AZINLIK</t>
+  </si>
+  <si>
+    <t>BAĞIL</t>
+  </si>
+  <si>
+    <t>BAĞIMLI</t>
+  </si>
+  <si>
+    <t>BAĞIMSIZ</t>
+  </si>
+  <si>
+    <t>BAĞINTI</t>
+  </si>
+  <si>
+    <t>BAĞIŞIK</t>
+  </si>
+  <si>
+    <t>BAĞIT</t>
+  </si>
+  <si>
+    <t>BAĞLAÇ</t>
+  </si>
+  <si>
+    <t>BAĞLAM</t>
+  </si>
+  <si>
+    <t>BAĞLANTI</t>
+  </si>
+  <si>
+    <t>BAĞLAŞIK</t>
+  </si>
+  <si>
+    <t>BAĞNAZ</t>
+  </si>
+  <si>
+    <t>BAKAN</t>
+  </si>
+  <si>
+    <t>BAKIŞ AÇISI</t>
+  </si>
+  <si>
+    <t>BARINAK</t>
+  </si>
+  <si>
+    <t>BARIŞÇIL</t>
+  </si>
+  <si>
+    <t>BASIN</t>
+  </si>
+  <si>
+    <t>BAŞARI</t>
+  </si>
+  <si>
+    <t>BAŞAT</t>
+  </si>
+  <si>
+    <t>BAŞBAKAN</t>
+  </si>
+  <si>
+    <t>BAŞBAYAN</t>
+  </si>
+  <si>
+    <t>BAŞBUĞ</t>
+  </si>
+  <si>
+    <t>BAŞKALDIRI</t>
+  </si>
+  <si>
+    <t>BAŞKAN</t>
+  </si>
+  <si>
+    <t>BAŞKENT</t>
+  </si>
+  <si>
+    <t>BAŞKOMUTAN</t>
+  </si>
+  <si>
+    <t>BAŞÖĞRETMEN</t>
+  </si>
+  <si>
+    <t>BAŞVURU</t>
+  </si>
+  <si>
+    <t>BAŞYAPIT</t>
+  </si>
+  <si>
+    <t>BAŞYAZAR</t>
+  </si>
+  <si>
+    <t>BAY</t>
+  </si>
+  <si>
+    <t>BAYINDIR</t>
+  </si>
+  <si>
+    <t>BEDENSEL</t>
+  </si>
+  <si>
+    <t>BEĞENİ</t>
+  </si>
+  <si>
+    <t>BELGE</t>
+  </si>
+  <si>
+    <t>BELİRGİN</t>
+  </si>
+  <si>
+    <t>BELİRLEMEK</t>
+  </si>
+  <si>
+    <t>BELİRTEÇ</t>
+  </si>
+  <si>
+    <t>BELİRTİ</t>
+  </si>
+  <si>
+    <t>BELLEK</t>
+  </si>
+  <si>
+    <t>BENCİL</t>
+  </si>
+  <si>
+    <t>BENGİ</t>
+  </si>
+  <si>
+    <t>BENZETİ</t>
+  </si>
+  <si>
+    <t>BESİN</t>
+  </si>
+  <si>
+    <t>BEŞGEN</t>
+  </si>
+  <si>
+    <t>BETİM</t>
+  </si>
+  <si>
+    <t>BIRAKIŞMA</t>
+  </si>
+  <si>
+    <t>BİLDİRİ</t>
+  </si>
+  <si>
+    <t>BİLEŞİK</t>
+  </si>
+  <si>
+    <t>BİLGE</t>
+  </si>
+  <si>
+    <t>BİLGİ</t>
+  </si>
+  <si>
+    <t>BİLİM</t>
+  </si>
+  <si>
+    <t>BİLİNÇ</t>
+  </si>
+  <si>
+    <t>BİLİRKİŞİ</t>
+  </si>
+  <si>
+    <t>BİREY</t>
+  </si>
+  <si>
+    <t>BİRİKİM</t>
+  </si>
+  <si>
+    <t>BİRİM</t>
+  </si>
+  <si>
+    <t>BİRİNCİL</t>
+  </si>
+  <si>
+    <t>BİRLEŞİK</t>
+  </si>
+  <si>
+    <t>BİR SÜRE</t>
+  </si>
+  <si>
+    <t>BİR TÜR</t>
+  </si>
+  <si>
+    <t>BİTİMLİ</t>
+  </si>
+  <si>
+    <t>BİTKİ</t>
+  </si>
+  <si>
+    <t>BOŞ İNANÇ</t>
+  </si>
+  <si>
+    <t>BOYLAM</t>
+  </si>
+  <si>
+    <t>BOYUT</t>
+  </si>
+  <si>
+    <t>BÖBREK YETMEZLİĞİ</t>
+  </si>
+  <si>
+    <t>BÖLGE</t>
+  </si>
+  <si>
+    <t>BÖLÜM</t>
+  </si>
+  <si>
+    <t>BUCAK</t>
+  </si>
+  <si>
+    <t>BUDUNBİLİM (BUDUN BİLİMİ)</t>
+  </si>
+  <si>
+    <t>BU DURUMDA</t>
+  </si>
+  <si>
+    <t>BULGU</t>
+  </si>
+  <si>
+    <t>BUNALIM</t>
+  </si>
+  <si>
+    <t>BU TÜR</t>
+  </si>
+  <si>
+    <t>BUZUL</t>
+  </si>
+  <si>
+    <t>BÜTÜNSEL</t>
+  </si>
+  <si>
+    <t>BÜYÜK ÇOĞUNLUK</t>
+  </si>
+  <si>
+    <t>BÜYÜK OLASILIKLA</t>
+  </si>
+  <si>
+    <t>BÜYÜTEÇ</t>
+  </si>
+  <si>
+    <t>CENÂZE TÖRENİ</t>
+  </si>
+  <si>
+    <t>CİNSEL</t>
+  </si>
+  <si>
+    <t>COŞKU</t>
+  </si>
+  <si>
+    <t>CUMHURBAŞKANI</t>
+  </si>
+  <si>
+    <t>CÜMLECİK</t>
+  </si>
+  <si>
+    <t>ÇABA</t>
+  </si>
+  <si>
+    <t>ÇAĞDAŞ</t>
+  </si>
+  <si>
+    <t>ÇAĞRI</t>
+  </si>
+  <si>
+    <t>ÇARPIM</t>
+  </si>
+  <si>
+    <t>ÇATI</t>
+  </si>
+  <si>
+    <t>ÇEKİM</t>
+  </si>
+  <si>
+    <t>ÇELİŞKİ</t>
+  </si>
+  <si>
+    <t>ÇELMECE</t>
+  </si>
+  <si>
+    <t>ÇEVİRİ</t>
+  </si>
+  <si>
+    <t>ÇIKARIM</t>
+  </si>
+  <si>
+    <t>ÇİZELGE</t>
+  </si>
+  <si>
+    <t>ÇOCUK ESİRGEME KURUMU</t>
+  </si>
+  <si>
+    <t>ÇOĞUL</t>
+  </si>
+  <si>
+    <t>ÇOKGEN</t>
+  </si>
+  <si>
+    <t>ÇOK ÖNEMLİ</t>
+  </si>
+  <si>
+    <t>ÇOK ÖZEL</t>
+  </si>
+  <si>
+    <t>ÇÖKELTİ</t>
+  </si>
+  <si>
+    <t>ÇÖKÜNTÜ</t>
+  </si>
+  <si>
+    <t>ÇÖZELTİ</t>
+  </si>
+  <si>
+    <t>ÇÖZÜM</t>
+  </si>
+  <si>
+    <t>DAĞILIM</t>
+  </si>
+  <si>
+    <t>DAHA ÖNEMLİ</t>
+  </si>
+  <si>
+    <t>DAİRESEL</t>
+  </si>
+  <si>
+    <t>DAMITIK</t>
+  </si>
+  <si>
+    <t>DANIŞMAN</t>
+  </si>
+  <si>
+    <t>DAYANAK</t>
+  </si>
+  <si>
+    <t>DAYANIŞMA</t>
+  </si>
+  <si>
+    <t>DEĞERBİLİR</t>
+  </si>
+  <si>
+    <t>DEĞĞİN</t>
+  </si>
+  <si>
+    <t>DEĞİNİ</t>
+  </si>
+  <si>
+    <t>DEĞİŞİM</t>
+  </si>
+  <si>
+    <t>DELGEÇ</t>
+  </si>
+  <si>
+    <t>DEMEÇ</t>
+  </si>
+  <si>
+    <t>DENEK</t>
+  </si>
+  <si>
+    <t>DENETİM</t>
+  </si>
+  <si>
+    <t>DENEY</t>
+  </si>
+  <si>
+    <t>DENGE</t>
+  </si>
+  <si>
+    <t>DENKLEM</t>
+  </si>
+  <si>
+    <t>DEPREM</t>
+  </si>
+  <si>
+    <t>DERGİ</t>
+  </si>
+  <si>
+    <t>DERSLİK</t>
+  </si>
+  <si>
+    <t>DEVİNİM</t>
+  </si>
+  <si>
+    <t>DEVLET BAŞKANI</t>
+  </si>
+  <si>
+    <t>DEVRİM</t>
+  </si>
+  <si>
+    <t>DEYİM</t>
+  </si>
+  <si>
+    <t>DIŞALIM</t>
+  </si>
+  <si>
+    <t>DIŞ İŞLERİ</t>
+  </si>
+  <si>
+    <t>DIŞKI</t>
+  </si>
+  <si>
+    <t>DIŞSATIM</t>
+  </si>
+  <si>
+    <t>DİK AÇI</t>
+  </si>
+  <si>
+    <t>DİKDÖRTGEN</t>
+  </si>
+  <si>
+    <t>DİKEY</t>
+  </si>
+  <si>
+    <t>DİLBİLİM (DİL BİLİMİ)</t>
+  </si>
+  <si>
+    <t>DİLEKÇE</t>
+  </si>
+  <si>
+    <t>DİNGİN</t>
+  </si>
+  <si>
+    <t>DİNSEL</t>
+  </si>
+  <si>
+    <t>DİRENÇ</t>
+  </si>
+  <si>
+    <t>DİŞİL</t>
+  </si>
+  <si>
+    <t>DİZE</t>
+  </si>
+  <si>
+    <t>DİZGE</t>
+  </si>
+  <si>
+    <t>DOĞA</t>
+  </si>
+  <si>
+    <t>DOĞMACA</t>
+  </si>
+  <si>
+    <t>DOĞRU ORANTILI</t>
+  </si>
+  <si>
+    <t>DOKU</t>
+  </si>
+  <si>
+    <t>DOLAŞIM</t>
+  </si>
+  <si>
+    <t>DONANIM</t>
+  </si>
+  <si>
+    <t>DOYGUN</t>
+  </si>
+  <si>
+    <t>DÖLLEME (DÖLLENME)</t>
+  </si>
+  <si>
+    <t>DÖNEM</t>
+  </si>
+  <si>
+    <t>DÖRT İŞLEM</t>
+  </si>
+  <si>
+    <t>DURAĞAN</t>
+  </si>
+  <si>
+    <t>DURUM</t>
+  </si>
+  <si>
+    <t>DUYARLI</t>
+  </si>
+  <si>
+    <t>DUYU</t>
+  </si>
+  <si>
+    <t>DÜRTÜ</t>
+  </si>
+  <si>
+    <t>DÜŞ</t>
+  </si>
+  <si>
+    <t>DÜŞÜNCE</t>
+  </si>
+  <si>
+    <t>DÜZE</t>
+  </si>
+  <si>
+    <t>DÜZELTİ</t>
+  </si>
+  <si>
+    <t>DÜZENLEMEK</t>
+  </si>
+  <si>
+    <t>DÜZEY</t>
+  </si>
+  <si>
+    <t>DÜZLEM</t>
+  </si>
+  <si>
+    <t>DÜZYAZI</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>EDİLGEN</t>
+  </si>
+  <si>
+    <t>EDİM</t>
+  </si>
+  <si>
+    <t>EGEMEN</t>
+  </si>
+  <si>
+    <t>EĞİLİM</t>
+  </si>
+  <si>
+    <t>EĞİTİM</t>
+  </si>
+  <si>
+    <t>EKİM</t>
+  </si>
+  <si>
+    <t>EKLEM</t>
+  </si>
+  <si>
+    <t>EKONOMİ BAKANI</t>
+  </si>
+  <si>
+    <t>EKSEN</t>
+  </si>
+  <si>
+    <t>EKSİ</t>
+  </si>
+  <si>
+    <t>EK SÜRE</t>
+  </si>
+  <si>
+    <t>ELEKTRİK SAYACI</t>
+  </si>
+  <si>
+    <t>ELEŞTİRİ</t>
+  </si>
+  <si>
+    <t>EMEKLİ</t>
+  </si>
+  <si>
+    <t>EMİR KOMUTA ZİNCİRİ</t>
+  </si>
+  <si>
+    <t>EMNİYET GENEL MÜDÜRLÜĞÜ</t>
+  </si>
+  <si>
+    <t>EN ÖNEMLİ</t>
+  </si>
+  <si>
+    <t>EN ÖZEL</t>
+  </si>
+  <si>
+    <t>ERDEM</t>
+  </si>
+  <si>
+    <t>EREK</t>
+  </si>
+  <si>
+    <t>ERİL</t>
+  </si>
+  <si>
+    <t>ERİŞİM</t>
+  </si>
+  <si>
+    <t>ERK</t>
+  </si>
+  <si>
+    <t>ESEN KAL (ESEN KALIN)</t>
+  </si>
+  <si>
+    <t>ESİN</t>
+  </si>
+  <si>
+    <t>EŞ ANLAM</t>
+  </si>
+  <si>
+    <t>EŞCİNSEL</t>
+  </si>
+  <si>
+    <t>EŞ DEĞER</t>
+  </si>
+  <si>
+    <t>EŞEY</t>
+  </si>
+  <si>
+    <t>EŞ GÜDÜM</t>
+  </si>
+  <si>
+    <t>EŞİT</t>
+  </si>
+  <si>
+    <t>EŞSESLİ</t>
+  </si>
+  <si>
+    <t>ETÇİL</t>
+  </si>
+  <si>
+    <t>ETKEN</t>
+  </si>
+  <si>
+    <t>ETKİ</t>
+  </si>
+  <si>
+    <t>ETMEN</t>
+  </si>
+  <si>
+    <t>EVCİL</t>
+  </si>
+  <si>
+    <t>EVİRME</t>
+  </si>
+  <si>
+    <t>EVRE</t>
+  </si>
+  <si>
+    <t>EVREN</t>
+  </si>
+  <si>
+    <t>EVRİM</t>
+  </si>
+  <si>
+    <t>EV YÖNETİMİ</t>
+  </si>
+  <si>
+    <t>EYLEM</t>
+  </si>
+  <si>
+    <t>EYTİŞİM</t>
+  </si>
+  <si>
+    <t>EZİCİ ÇOĞUNLUK</t>
+  </si>
+  <si>
+    <t>FİZİKSEL</t>
+  </si>
+  <si>
+    <t>GAZETECİ YAZAR</t>
+  </si>
+  <si>
+    <t>GEÇERLİ</t>
+  </si>
+  <si>
+    <t>GEÇİRGEN</t>
+  </si>
+  <si>
+    <t>GELECEK KUŞAKLAR</t>
+  </si>
+  <si>
+    <t>GELENEK</t>
+  </si>
+  <si>
+    <t>GELGİT</t>
+  </si>
+  <si>
+    <t>GELİR DAĞILIMI</t>
+  </si>
+  <si>
+    <t>GELİŞİM</t>
+  </si>
+  <si>
+    <t>GENEL</t>
+  </si>
+  <si>
+    <t>GENLEŞMEK</t>
+  </si>
+  <si>
+    <t>GERÇEKLEŞMEK</t>
+  </si>
+  <si>
+    <t>GEREÇ</t>
+  </si>
+  <si>
+    <t>GEREKÇE</t>
+  </si>
+  <si>
+    <t>GERİCİ</t>
+  </si>
+  <si>
+    <t>GERİLİM</t>
+  </si>
+  <si>
+    <t>GETİRİ</t>
+  </si>
+  <si>
+    <t>GEZEGEN</t>
+  </si>
+  <si>
+    <t>GİDER</t>
+  </si>
+  <si>
+    <t>GİRİŞİM</t>
+  </si>
+  <si>
+    <t>GİYSİ</t>
+  </si>
+  <si>
+    <t>GİZ</t>
+  </si>
+  <si>
+    <t>GÖÇMEN</t>
+  </si>
+  <si>
+    <t>GÖKBİLİM (GÖKBİLİMI)</t>
+  </si>
+  <si>
+    <t>GÖNDERİ</t>
+  </si>
+  <si>
+    <t>GÖNENÇ</t>
+  </si>
+  <si>
+    <t>GÖRECE</t>
+  </si>
+  <si>
+    <t>GÖREV</t>
+  </si>
+  <si>
+    <t>GÖRGÜ KURALLARI</t>
+  </si>
+  <si>
+    <t>GÖRKEM</t>
+  </si>
+  <si>
+    <t>GÖRSEL</t>
+  </si>
+  <si>
+    <t>GÖRÜNTÜ</t>
+  </si>
+  <si>
+    <t>GÖSTERGE</t>
+  </si>
+  <si>
+    <t>GÖZALTI</t>
+  </si>
+  <si>
+    <t>GÖZETİM</t>
+  </si>
+  <si>
+    <t>GÖZLEM</t>
+  </si>
+  <si>
+    <t>GÜÇ ODAĞI</t>
+  </si>
+  <si>
+    <t>GÜDÜ</t>
+  </si>
+  <si>
+    <t>GÜMRÜK VE TEKEL BAKANI</t>
+  </si>
+  <si>
+    <t>GÜNAYDIN</t>
+  </si>
+  <si>
+    <t>GÜNCE</t>
+  </si>
+  <si>
+    <t>GÜNDEM</t>
+  </si>
+  <si>
+    <t>GÜNEY</t>
+  </si>
+  <si>
+    <t>GÜNLÜK</t>
+  </si>
+  <si>
+    <t>GÜVEN</t>
+  </si>
+  <si>
+    <t>HALKOYU</t>
+  </si>
+  <si>
+    <t>HALK OZANI</t>
+  </si>
+  <si>
+    <t>HARP OKULU</t>
+  </si>
+  <si>
+    <t>HAVA AKIMI</t>
+  </si>
+  <si>
+    <t>HAYAT OKULU</t>
+  </si>
+  <si>
+    <t>HAYIR KURUMU</t>
+  </si>
+  <si>
+    <t>HAYVANSAL</t>
+  </si>
+  <si>
+    <t>HER DURUMDA</t>
+  </si>
+  <si>
+    <t>HOŞGÖRÜ</t>
+  </si>
+  <si>
+    <t>HUKUK KURALLARI</t>
+  </si>
+  <si>
+    <t>ILIMAN</t>
+  </si>
+  <si>
+    <t>IRA</t>
+  </si>
+  <si>
+    <t>ISI</t>
+  </si>
+  <si>
+    <t>İÇBÜKEY</t>
+  </si>
+  <si>
+    <t>İÇERİK</t>
+  </si>
+  <si>
+    <t>İÇGÜDÜ</t>
+  </si>
+  <si>
+    <t>İÇ İŞLERİ BAKANI</t>
+  </si>
+  <si>
+    <t>İÇSEL</t>
+  </si>
+  <si>
+    <t>İÇTEN</t>
+  </si>
+  <si>
+    <t>İÇTÜZÜK</t>
+  </si>
+  <si>
+    <t>İKİLEM</t>
+  </si>
+  <si>
+    <t>İKİNCİL</t>
+  </si>
+  <si>
+    <t>İKİRCİM</t>
+  </si>
+  <si>
+    <t>İLÇE</t>
+  </si>
+  <si>
+    <t>İLERİCİ</t>
+  </si>
+  <si>
+    <t>İLETİ</t>
+  </si>
+  <si>
+    <t>İLGİ</t>
+  </si>
+  <si>
+    <t>İLİNTİ</t>
+  </si>
+  <si>
+    <t>İLİŞKİ</t>
+  </si>
+  <si>
+    <t>İLKE</t>
+  </si>
+  <si>
+    <t>İLKOKUL</t>
+  </si>
+  <si>
+    <t>İM</t>
+  </si>
+  <si>
+    <t>İMGE</t>
+  </si>
+  <si>
+    <t>İMLEÇ</t>
+  </si>
+  <si>
+    <t>İNANÇ</t>
+  </si>
+  <si>
+    <t>İNDİRGEMEK</t>
+  </si>
+  <si>
+    <t>İNSANBİLİM</t>
+  </si>
+  <si>
+    <t>İRDELEMEK</t>
+  </si>
+  <si>
+    <t>İSTEM</t>
+  </si>
+  <si>
+    <t>İŞ BÖLÜMÜ</t>
+  </si>
+  <si>
+    <t>İŞİTME DUYUSU</t>
+  </si>
+  <si>
+    <t>İŞLEM</t>
+  </si>
+  <si>
+    <t>İŞLEV</t>
+  </si>
+  <si>
+    <t>İŞ OKULU</t>
+  </si>
+  <si>
+    <t>İVME</t>
+  </si>
+  <si>
+    <t>İYE</t>
+  </si>
+  <si>
+    <t>İYİMSER</t>
+  </si>
+  <si>
+    <t>İZDÜŞÜM</t>
+  </si>
+  <si>
+    <t>İZLEM</t>
+  </si>
+  <si>
+    <t>KALDIRAÇ</t>
+  </si>
+  <si>
+    <t>KALIT</t>
+  </si>
+  <si>
+    <t>KAMU</t>
+  </si>
+  <si>
+    <t>KANAAT ÖNDERİ</t>
+  </si>
+  <si>
+    <t>KAN DOLAŞIMI</t>
+  </si>
+  <si>
+    <t>KANI</t>
+  </si>
+  <si>
+    <t>KANIT</t>
+  </si>
+  <si>
+    <t>KANUN TASARISI</t>
+  </si>
+  <si>
+    <t>KAPALI OTURUM</t>
+  </si>
+  <si>
+    <t>KAPLAM</t>
+  </si>
+  <si>
+    <t>KAPSAM</t>
+  </si>
+  <si>
+    <t>KARAMSAR</t>
+  </si>
+  <si>
+    <t>KARASAL</t>
+  </si>
+  <si>
+    <t>KARIŞIM</t>
+  </si>
+  <si>
+    <t>KARMAŞA</t>
+  </si>
+  <si>
+    <t>KARŞILAMA TÖRENİ</t>
+  </si>
+  <si>
+    <t>KARŞIN</t>
+  </si>
+  <si>
+    <t>KARŞIT</t>
+  </si>
+  <si>
+    <t>KAS</t>
+  </si>
+  <si>
+    <t>KASIM</t>
+  </si>
+  <si>
+    <t>KATILIM</t>
+  </si>
+  <si>
+    <t>KATMAN</t>
+  </si>
+  <si>
+    <t>KATSAYI</t>
+  </si>
+  <si>
+    <t>KAVRAM</t>
+  </si>
+  <si>
+    <t>KAZI</t>
+  </si>
+  <si>
+    <t>KENT</t>
+  </si>
+  <si>
+    <t>KESENEK</t>
+  </si>
+  <si>
+    <t>KESİN</t>
+  </si>
+  <si>
+    <t>KESİNTİ</t>
+  </si>
+  <si>
+    <t>KESİT</t>
+  </si>
+  <si>
+    <t>KILCAL</t>
+  </si>
+  <si>
+    <t>KIRSAL</t>
+  </si>
+  <si>
+    <t>KISIR DÖNGÜ</t>
+  </si>
+  <si>
+    <t>KIRIM</t>
+  </si>
+  <si>
+    <t>KISINTI</t>
+  </si>
+  <si>
+    <t>KISIT</t>
+  </si>
+  <si>
+    <t>KIVANÇ</t>
+  </si>
+  <si>
+    <t>KIYIM</t>
+  </si>
+  <si>
+    <t>KİMLİK</t>
+  </si>
+  <si>
+    <t>KİMYASAL</t>
+  </si>
+  <si>
+    <t>KİP</t>
+  </si>
+  <si>
+    <t>KİŞİLİK</t>
+  </si>
+  <si>
+    <t>KİTLESEL</t>
+  </si>
+  <si>
+    <t>KOMUT</t>
+  </si>
+  <si>
+    <t>KONU</t>
+  </si>
+  <si>
+    <t>KONUK</t>
+  </si>
+  <si>
+    <t>KONUM</t>
+  </si>
+  <si>
+    <t>KONUT</t>
+  </si>
+  <si>
+    <t>KORGENERAL</t>
+  </si>
+  <si>
+    <t>KORUMACI</t>
+  </si>
+  <si>
+    <t>KORUNAK</t>
+  </si>
+  <si>
+    <t>KOŞUK</t>
+  </si>
+  <si>
+    <t>KOŞUL</t>
+  </si>
+  <si>
+    <t>KOŞUT</t>
+  </si>
+  <si>
+    <t>KOVUŞTURMA</t>
+  </si>
+  <si>
+    <t>KÖKENBİLİM (KÖKEN BİLİMİ)</t>
+  </si>
+  <si>
+    <t>KÖKTENCİ</t>
+  </si>
+  <si>
+    <t>KÖŞE YAZARI</t>
+  </si>
+  <si>
+    <t>KÖTÜCÜL</t>
+  </si>
+  <si>
+    <t>KÖTÜMSER</t>
+  </si>
+  <si>
+    <t>KULLANIM</t>
+  </si>
+  <si>
+    <t>KUMUL</t>
+  </si>
+  <si>
+    <t>KURAL</t>
+  </si>
+  <si>
+    <t>KURAM</t>
+  </si>
+  <si>
+    <t>KURGU</t>
+  </si>
+  <si>
+    <t>KURMAY</t>
+  </si>
+  <si>
+    <t>KURUCULAR KURULU</t>
+  </si>
+  <si>
+    <t>KURUL</t>
+  </si>
+  <si>
+    <t>KURULTAY</t>
+  </si>
+  <si>
+    <t>KURULUŞ</t>
+  </si>
+  <si>
+    <t>KURUM</t>
+  </si>
+  <si>
+    <t>KUŞAK</t>
+  </si>
+  <si>
+    <t>KUŞKU</t>
+  </si>
+  <si>
+    <t>KUTLAMA</t>
+  </si>
+  <si>
+    <t>KUTSAL</t>
+  </si>
+  <si>
+    <t>KUZEY</t>
+  </si>
+  <si>
+    <t>KÜLTÜR BAKANI</t>
+  </si>
+  <si>
+    <t>KÜRESEL</t>
+  </si>
+  <si>
+    <t>MADDESEL</t>
+  </si>
+  <si>
+    <t>MADENSEL</t>
+  </si>
+  <si>
+    <t>MAL BİLDİRİMİ</t>
+  </si>
+  <si>
+    <t>MANTIKSAL</t>
+  </si>
+  <si>
+    <t>MERKEZÎ YÖNETİM</t>
+  </si>
+  <si>
+    <t>MİLLÎ EĞİTİM BAKANI</t>
+  </si>
+  <si>
+    <t>MİLLÎ SAVUNMA BAKANI</t>
+  </si>
+  <si>
+    <t>MUTLU AZINLIK</t>
+  </si>
+  <si>
+    <t>MUTSUZ</t>
+  </si>
+  <si>
+    <t>NEDEN</t>
+  </si>
+  <si>
+    <t>NESNEL</t>
+  </si>
+  <si>
+    <t>NİCEL</t>
+  </si>
+  <si>
+    <t>NİTEL</t>
+  </si>
+  <si>
+    <t>OCAK</t>
+  </si>
+  <si>
+    <t>ODAK</t>
+  </si>
+  <si>
+    <t>OKUL</t>
+  </si>
+  <si>
+    <t>OKUR</t>
+  </si>
+  <si>
+    <t>OLAĞAN DIŞI</t>
+  </si>
+  <si>
+    <t>OLANAK</t>
+  </si>
+  <si>
+    <t>OLASI</t>
+  </si>
+  <si>
+    <t>OLAY</t>
+  </si>
+  <si>
+    <t>OLDUBİTTİ</t>
+  </si>
+  <si>
+    <t>OLGU</t>
+  </si>
+  <si>
+    <t>OLUMLU</t>
+  </si>
+  <si>
+    <t>OLUMSUZ</t>
+  </si>
+  <si>
+    <t>OLURLUK</t>
+  </si>
+  <si>
+    <t>OLUŞ</t>
+  </si>
+  <si>
+    <t>OMUR</t>
+  </si>
+  <si>
+    <t>ONAMA</t>
+  </si>
+  <si>
+    <t>ONARIM</t>
+  </si>
+  <si>
+    <t>ONAY</t>
+  </si>
+  <si>
+    <t>ONUR</t>
+  </si>
+  <si>
+    <t>ORAN</t>
+  </si>
+  <si>
+    <t>ORGANİK ÜRÜN</t>
+  </si>
+  <si>
+    <t>ORGENERAL</t>
+  </si>
+  <si>
+    <t>ORTA ÇAĞ</t>
+  </si>
+  <si>
+    <t>ORTAK PAYDA</t>
+  </si>
+  <si>
+    <t>ORTAM</t>
+  </si>
+  <si>
+    <t>ORTAOKUL</t>
+  </si>
+  <si>
+    <t>OTURUM</t>
+  </si>
+  <si>
+    <t>OY</t>
+  </si>
+  <si>
+    <t>OZAN</t>
+  </si>
+  <si>
+    <t>ÖDENEK</t>
+  </si>
+  <si>
+    <t>ÖDEV</t>
+  </si>
+  <si>
+    <t>ÖDÜL</t>
+  </si>
+  <si>
+    <t>ÖDÜN</t>
+  </si>
+  <si>
+    <t>ÖGE</t>
+  </si>
+  <si>
+    <t>ÖĞRENCİ</t>
+  </si>
+  <si>
+    <t>ÖĞRENİM</t>
+  </si>
+  <si>
+    <t>ÖĞRETİ</t>
+  </si>
+  <si>
+    <t>ÖĞRETMEN</t>
+  </si>
+  <si>
+    <t>ÖLÇÜN</t>
+  </si>
+  <si>
+    <t>ÖNCEL</t>
+  </si>
+  <si>
+    <t>ÖNDER</t>
+  </si>
+  <si>
+    <t>ÖNEM</t>
+  </si>
+  <si>
+    <t>ÖNERGE</t>
+  </si>
+  <si>
+    <t>ÖNERİ</t>
+  </si>
+  <si>
+    <t>ÖNGÖRÜ</t>
+  </si>
+  <si>
+    <t>ÖN KOŞUL</t>
+  </si>
+  <si>
+    <t>ÖNLEM</t>
+  </si>
+  <si>
+    <t>ÖNSEZİ</t>
+  </si>
+  <si>
+    <t>ÖNSÖZ</t>
+  </si>
+  <si>
+    <t>ÖN YARGI</t>
+  </si>
+  <si>
+    <t>ÖN YÜZBAŞI</t>
+  </si>
+  <si>
+    <t>ÖRGÜN</t>
+  </si>
+  <si>
+    <t>ÖRGÜT</t>
+  </si>
+  <si>
+    <t>ÖRNEKLEM</t>
+  </si>
+  <si>
+    <t>ÖRTMECE</t>
+  </si>
+  <si>
+    <t>ÖRTÜLÜ ÖDENEK</t>
+  </si>
+  <si>
+    <t>ÖRTÜŞMEK</t>
+  </si>
+  <si>
+    <t>ÖTELEME, ÖTELENME</t>
+  </si>
+  <si>
+    <t>ÖVGÜ</t>
+  </si>
+  <si>
+    <t>ÖVÜNÇ</t>
+  </si>
+  <si>
+    <t>ÖYKÜ</t>
+  </si>
+  <si>
+    <t>ÖZ BAĞIŞIKLIK</t>
+  </si>
+  <si>
+    <t>ÖZDEK</t>
+  </si>
+  <si>
+    <t>ÖZ DENETİM</t>
+  </si>
+  <si>
+    <t>ÖZDEŞ</t>
+  </si>
+  <si>
+    <t>ÖZDEYİŞ</t>
+  </si>
+  <si>
+    <t>ÖZ DİRENÇ</t>
+  </si>
+  <si>
+    <t>ÖZEL</t>
+  </si>
+  <si>
+    <t>ÖZERK</t>
+  </si>
+  <si>
+    <t>ÖZET</t>
+  </si>
+  <si>
+    <t>ÖZ GEÇMİŞ</t>
+  </si>
+  <si>
+    <t>ÖZGÜL</t>
+  </si>
+  <si>
+    <t>ÖZGÜN</t>
+  </si>
+  <si>
+    <t>ÖZGÜR</t>
+  </si>
+  <si>
+    <t>ÖZ GÜVEN</t>
+  </si>
+  <si>
+    <t>ÖZLEM</t>
+  </si>
+  <si>
+    <t>ÖZLEŞTİRMEK</t>
+  </si>
+  <si>
+    <t>ÖZLÜK</t>
+  </si>
+  <si>
+    <t>ÖZNE</t>
+  </si>
+  <si>
+    <t>ÖZSAYGI</t>
+  </si>
+  <si>
+    <t>ÖZSU</t>
+  </si>
+  <si>
+    <t>ÖZÜMLEMEK</t>
+  </si>
+  <si>
+    <t>ÖZÜMSEMEK</t>
+  </si>
+  <si>
+    <t>ÖZÜT</t>
+  </si>
+  <si>
+    <t>ÖZVERİ</t>
+  </si>
+  <si>
+    <t>PARASAL</t>
+  </si>
+  <si>
+    <t>PAYDA</t>
+  </si>
+  <si>
+    <t>PEK ÖNEMLİ</t>
+  </si>
+  <si>
+    <t>PEŞİN YARGI</t>
+  </si>
+  <si>
+    <t>RASTLANTI</t>
+  </si>
+  <si>
+    <t>RESMÎ GÖREV</t>
+  </si>
+  <si>
+    <t>RUHBİLİM (RUH BİLİMİ)</t>
+  </si>
+  <si>
+    <t>SAĞDUYU</t>
+  </si>
+  <si>
+    <t>SAĞLIK BAKANI</t>
+  </si>
+  <si>
+    <t>SAKINCA</t>
+  </si>
+  <si>
+    <t>SALDIRGAN</t>
+  </si>
+  <si>
+    <t>SALGI</t>
+  </si>
+  <si>
+    <t>SALINIM</t>
+  </si>
+  <si>
+    <t>SALTÇI</t>
+  </si>
+  <si>
+    <t>SANAL</t>
+  </si>
+  <si>
+    <t>SANIK</t>
+  </si>
+  <si>
+    <t>SAPLANTI</t>
+  </si>
+  <si>
+    <t>SAPTAMAK</t>
+  </si>
+  <si>
+    <t>SARKAÇ</t>
+  </si>
+  <si>
+    <t>SARMAL</t>
+  </si>
+  <si>
+    <t>SAV</t>
+  </si>
+  <si>
+    <t>SAVAŞIM</t>
+  </si>
+  <si>
+    <t>SAVCI</t>
+  </si>
+  <si>
+    <t>SAVUNMA</t>
+  </si>
+  <si>
+    <t>SAVURGAN</t>
+  </si>
+  <si>
+    <t>SAYAÇ</t>
+  </si>
+  <si>
+    <t>SAYDAM</t>
+  </si>
+  <si>
+    <t>SAYGIN</t>
+  </si>
+  <si>
+    <t>SAYISAL</t>
+  </si>
+  <si>
+    <t>SAYMAN</t>
+  </si>
+  <si>
+    <t>SAYRI</t>
+  </si>
+  <si>
+    <t>SEÇENEK</t>
+  </si>
+  <si>
+    <t>SEÇİCİ KURUL</t>
+  </si>
+  <si>
+    <t>SEÇİM BÖLGESİ</t>
+  </si>
+  <si>
+    <t>SEÇKİ</t>
+  </si>
+  <si>
+    <t>SEÇMEN</t>
+  </si>
+  <si>
+    <t>SEKİZGEN</t>
+  </si>
+  <si>
+    <t>SERÜVEN</t>
+  </si>
+  <si>
+    <t>SES BİLGİSİ</t>
+  </si>
+  <si>
+    <t>SEVECEN</t>
+  </si>
+  <si>
+    <t>SIĞINAK</t>
+  </si>
+  <si>
+    <t>SIKIYÖNETİM</t>
+  </si>
+  <si>
+    <t>SINAV</t>
+  </si>
+  <si>
+    <t>SINIRLAMA</t>
+  </si>
+  <si>
+    <t>SIVI</t>
+  </si>
+  <si>
+    <t>SİMGE</t>
+  </si>
+  <si>
+    <t>SİNDİRİM</t>
+  </si>
+  <si>
+    <t>SİNİRSEL</t>
+  </si>
+  <si>
+    <t>SİVİL SAVUNMA</t>
+  </si>
+  <si>
+    <t>SİYASA</t>
+  </si>
+  <si>
+    <t>SOLUNUM</t>
+  </si>
+  <si>
+    <t>SOMUT</t>
+  </si>
+  <si>
+    <t>SONUÇ</t>
+  </si>
+  <si>
+    <t>SORGU HÂKİMİ</t>
+  </si>
+  <si>
+    <t>SORU</t>
+  </si>
+  <si>
+    <t>SORUMLU</t>
+  </si>
+  <si>
+    <t>SORUN</t>
+  </si>
+  <si>
+    <t>SOYA ÇEKİM</t>
+  </si>
+  <si>
+    <t>SOYUT</t>
+  </si>
+  <si>
+    <t>SÖMÜRGE</t>
+  </si>
+  <si>
+    <t>SÖVGÜ</t>
+  </si>
+  <si>
+    <t>SÖYLEM</t>
+  </si>
+  <si>
+    <t>SÖYLENCE</t>
+  </si>
+  <si>
+    <t>SÖYLEŞİ</t>
+  </si>
+  <si>
+    <t>SÖYLEV</t>
+  </si>
+  <si>
+    <t>SÖZCÜK</t>
+  </si>
+  <si>
+    <t>SÖZDİZİMİ</t>
+  </si>
+  <si>
+    <t>SÖZEL</t>
+  </si>
+  <si>
+    <t>SÖZ KONUSU</t>
+  </si>
+  <si>
+    <t>SÖZLÜK</t>
+  </si>
+  <si>
+    <t>SÖZLÜ SINAV</t>
+  </si>
+  <si>
+    <t>SÖZ YAZARI</t>
+  </si>
+  <si>
+    <t>SÖZ YİTİMİ</t>
+  </si>
+  <si>
+    <t>SUBAY</t>
+  </si>
+  <si>
+    <t>SUNAK</t>
+  </si>
+  <si>
+    <t>SUNU</t>
+  </si>
+  <si>
+    <t>SU SAYACI</t>
+  </si>
+  <si>
+    <t>SU ÜRÜNLERİ</t>
+  </si>
+  <si>
+    <t>SÜRE</t>
+  </si>
+  <si>
+    <t>ŞEKİLBİLİM</t>
+  </si>
+  <si>
+    <t>ŞİİRSEL</t>
+  </si>
+  <si>
+    <t>TAKI</t>
+  </si>
+  <si>
+    <t>TAKINAK</t>
+  </si>
+  <si>
+    <t>TANI</t>
+  </si>
+  <si>
+    <t>TANIM</t>
+  </si>
+  <si>
+    <t>TANIT</t>
+  </si>
+  <si>
+    <t>TANRIBİLİM</t>
+  </si>
+  <si>
+    <t>TAPINAK</t>
+  </si>
+  <si>
+    <t>TARIM</t>
+  </si>
+  <si>
+    <t>TÂRİHSEL</t>
+  </si>
+  <si>
+    <t>TASARI</t>
+  </si>
+  <si>
+    <t>TAŞIL</t>
+  </si>
+  <si>
+    <t>TAŞIM</t>
+  </si>
+  <si>
+    <t>TAŞINMAZ</t>
+  </si>
+  <si>
+    <t>TAŞIT</t>
+  </si>
+  <si>
+    <t>TAŞLAMA</t>
+  </si>
+  <si>
+    <t>TEĞET</t>
+  </si>
+  <si>
+    <t>TEĞMEN</t>
+  </si>
+  <si>
+    <t>TEKDÜZE</t>
+  </si>
+  <si>
+    <t>TEKEL</t>
+  </si>
+  <si>
+    <t>TEKİL</t>
+  </si>
+  <si>
+    <t>TENSEL</t>
+  </si>
+  <si>
+    <t>TEPKİ</t>
+  </si>
+  <si>
+    <t>TERİM</t>
+  </si>
+  <si>
+    <t>TERS ORANTILI</t>
+  </si>
+  <si>
+    <t>TİNİ</t>
+  </si>
+  <si>
+    <t>TİKEL</t>
+  </si>
+  <si>
+    <t>TİKSİNTİ</t>
+  </si>
+  <si>
+    <t>TİTREŞİM</t>
+  </si>
+  <si>
+    <t>TOPLAM</t>
+  </si>
+  <si>
+    <t>TOPLUM</t>
+  </si>
+  <si>
+    <t>TORTUL</t>
+  </si>
+  <si>
+    <t>TÖREN</t>
+  </si>
+  <si>
+    <t>TUĞGENERAL</t>
+  </si>
+  <si>
+    <t>TUTANAK</t>
+  </si>
+  <si>
+    <t>TUTAR</t>
+  </si>
+  <si>
+    <t>TUTKU</t>
+  </si>
+  <si>
+    <t>TUTUCU</t>
+  </si>
+  <si>
+    <t>TUTUKEVİ</t>
+  </si>
+  <si>
+    <t>TUTUM</t>
+  </si>
+  <si>
+    <t>TÜKETİM</t>
+  </si>
+  <si>
+    <t>TÜM</t>
+  </si>
+  <si>
+    <t>TÜR</t>
+  </si>
+  <si>
+    <t>TÜZE</t>
+  </si>
+  <si>
+    <t>UÇAK</t>
+  </si>
+  <si>
+    <t>UĞRAŞ</t>
+  </si>
+  <si>
+    <t>ULAŞIM</t>
+  </si>
+  <si>
+    <t>ULUSAL</t>
+  </si>
+  <si>
+    <t>UTKU</t>
+  </si>
+  <si>
+    <t>UYAK</t>
+  </si>
+  <si>
+    <t>UYARI</t>
+  </si>
+  <si>
+    <t>UYDU</t>
+  </si>
+  <si>
+    <t>UYGAR</t>
+  </si>
+  <si>
+    <t>UYGULAMA</t>
+  </si>
+  <si>
+    <t>UYRUK</t>
+  </si>
+  <si>
+    <t>UYUM</t>
+  </si>
+  <si>
+    <t>UZAM</t>
+  </si>
+  <si>
+    <t>UZMAN</t>
+  </si>
+  <si>
+    <t>UZUN SÜRE</t>
+  </si>
+  <si>
+    <t>ÜÇGEN</t>
+  </si>
+  <si>
+    <t>ÜLKÜ</t>
+  </si>
+  <si>
+    <t>ÜNDEŞ</t>
+  </si>
+  <si>
+    <t>ÜNLEM</t>
+  </si>
+  <si>
+    <t>ÜNLÜ</t>
+  </si>
+  <si>
+    <t>ÜREM</t>
+  </si>
+  <si>
+    <t>ÜRETİM</t>
+  </si>
+  <si>
+    <t>ÜRKÜNÇ</t>
+  </si>
+  <si>
+    <t>ÜRÜN</t>
+  </si>
+  <si>
+    <t>ÜST DÜZEY</t>
+  </si>
+  <si>
+    <t>ÜSTEĞMEN</t>
+  </si>
+  <si>
+    <t>ÜST SUBAY</t>
+  </si>
+  <si>
+    <t>ÜYE</t>
+  </si>
+  <si>
+    <t>VARGİ</t>
+  </si>
+  <si>
+    <t>VARLIKBİLİM</t>
+  </si>
+  <si>
+    <t>VARSAYIM</t>
+  </si>
+  <si>
+    <t>VARSIL</t>
+  </si>
+  <si>
+    <t>VAROLUŞSAL</t>
+  </si>
+  <si>
+    <t>VERİ</t>
+  </si>
+  <si>
+    <t>VİCDAN ÖZGÜRLÜĞÜ</t>
+  </si>
+  <si>
+    <t>VURGUN</t>
+  </si>
+  <si>
+    <t>YABANIL</t>
+  </si>
+  <si>
+    <t>YADSIMAK</t>
+  </si>
+  <si>
+    <t>YAKIT</t>
+  </si>
+  <si>
+    <t>YAKINMA</t>
+  </si>
+  <si>
+    <t>YALITIM</t>
+  </si>
+  <si>
+    <t>YANAL</t>
+  </si>
+  <si>
+    <t>YANDAŞ</t>
+  </si>
+  <si>
+    <t>YANGI</t>
+  </si>
+  <si>
+    <t>YANILGI</t>
+  </si>
+  <si>
+    <t>YANIT</t>
+  </si>
+  <si>
+    <t>YANLI</t>
+  </si>
+  <si>
+    <t>YANSI</t>
+  </si>
+  <si>
+    <t>YAN ÜRÜN</t>
+  </si>
+  <si>
+    <t>YAPAY</t>
+  </si>
+  <si>
+    <t>YAPIM</t>
+  </si>
+  <si>
+    <t>YAPTIRIM</t>
+  </si>
+  <si>
+    <t>YARAR</t>
+  </si>
+  <si>
+    <t>YARATIK</t>
+  </si>
+  <si>
+    <t>YARBAY</t>
+  </si>
+  <si>
+    <t>YARGI</t>
+  </si>
+  <si>
+    <t>YASA</t>
+  </si>
+  <si>
+    <t>YAŞAM</t>
+  </si>
+  <si>
+    <t>YATAY</t>
+  </si>
+  <si>
+    <t>YATILI ÖĞRENCİ</t>
+  </si>
+  <si>
+    <t>YATIRIM</t>
+  </si>
+  <si>
+    <t>YATIŞTIRICI</t>
+  </si>
+  <si>
+    <t>YAYGIN</t>
+  </si>
+  <si>
+    <t>YAYIM</t>
+  </si>
+  <si>
+    <t>YAZAR</t>
+  </si>
+  <si>
+    <t>YAZGI</t>
+  </si>
+  <si>
+    <t>YAZILI SINAV</t>
+  </si>
+  <si>
+    <t>YAZIM</t>
+  </si>
+  <si>
+    <t>YEDEK SUBAY</t>
+  </si>
+  <si>
+    <t>YEĞLEMEK</t>
+  </si>
+  <si>
+    <t>YEMİN TÖRENİ</t>
+  </si>
+  <si>
+    <t>YENİ ÇAĞ</t>
+  </si>
+  <si>
+    <t>YENİLGİ</t>
+  </si>
+  <si>
+    <t>YERBİLİM</t>
+  </si>
+  <si>
+    <t>YEREL</t>
+  </si>
+  <si>
+    <t>YEREY</t>
+  </si>
+  <si>
+    <t>YERGİ</t>
+  </si>
+  <si>
+    <t>YERİNDELİK</t>
+  </si>
+  <si>
+    <t>YERKÜRE</t>
+  </si>
+  <si>
+    <t>YERLEŞİK</t>
+  </si>
+  <si>
+    <t>YETENEK</t>
+  </si>
+  <si>
+    <t>YETERLİ</t>
+  </si>
+  <si>
+    <t>YETKİ</t>
+  </si>
+  <si>
+    <t>YETKİN</t>
+  </si>
+  <si>
+    <t>YETMEZLİK</t>
+  </si>
+  <si>
+    <t>YILDIRI</t>
+  </si>
+  <si>
+    <t>YILDIZBİLİM</t>
+  </si>
+  <si>
+    <t>YILLIK</t>
+  </si>
+  <si>
+    <t>YİNELEMEK</t>
+  </si>
+  <si>
+    <t>YOĞUNLAŞMA</t>
+  </si>
+  <si>
+    <t>YOĞUŞMA</t>
+  </si>
+  <si>
+    <t>YOKSUN</t>
+  </si>
+  <si>
+    <t>YOL YÖNTEM</t>
+  </si>
+  <si>
+    <t>YONTU</t>
+  </si>
+  <si>
+    <t>YORUM</t>
+  </si>
+  <si>
+    <t>YOZLAŞMA</t>
+  </si>
+  <si>
+    <t>YÖNDEŞ</t>
+  </si>
+  <si>
+    <t>YÖNELİK</t>
+  </si>
+  <si>
+    <t>YÖNERGE</t>
+  </si>
+  <si>
+    <t>YÖNETİM</t>
+  </si>
+  <si>
+    <t>YÖNTEM</t>
+  </si>
+  <si>
+    <t>YÖRESEL</t>
+  </si>
+  <si>
+    <t>YÖRÜNGE</t>
+  </si>
+  <si>
+    <t>YURTSEVER</t>
+  </si>
+  <si>
+    <t>YURTTAŞ</t>
+  </si>
+  <si>
+    <t>YÜKSEKOKUL</t>
+  </si>
+  <si>
+    <t>YÜKSELTİ</t>
+  </si>
+  <si>
+    <t>YÜKÜM</t>
+  </si>
+  <si>
+    <t>YÜRÜRLÜK</t>
+  </si>
+  <si>
+    <t>YÜZEY</t>
+  </si>
+  <si>
+    <t>YÜZÖLÇÜMÜ (YÜZ ÖLÇÜMÜ)</t>
+  </si>
+  <si>
+    <t>ZAMAN AŞIMI</t>
+  </si>
+  <si>
+    <t>ZİHİNSEL</t>
+  </si>
+  <si>
+    <t>ZORALIM</t>
+  </si>
+  <si>
+    <t>ZORUNLU</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +2853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{984A1489-2204-4320-8C2B-598D19BA0E68}">
-  <dimension ref="A1:H338"/>
+  <dimension ref="A1:H791"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -1536,1705 +2895,3970 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>345</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>346</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>349</v>
+        <v>12</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>350</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="2" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="200" spans="1:1">
       <c r="A200" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="2" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" s="2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="321" spans="1:1">
       <c r="A321" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="323" spans="1:1">
       <c r="A323" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="326" spans="1:1">
       <c r="A326" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="327" spans="1:1">
       <c r="A327" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="329" spans="1:1">
       <c r="A329" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="330" spans="1:1">
       <c r="A330" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="331" spans="1:1">
       <c r="A331" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="332" spans="1:1">
       <c r="A332" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="333" spans="1:1">
       <c r="A333" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="334" spans="1:1">
       <c r="A334" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="335" spans="1:1">
       <c r="A335" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="336" spans="1:1">
       <c r="A336" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="338" spans="1:1">
       <c r="A338" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1">
+      <c r="A481" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1">
+      <c r="A482" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1">
+      <c r="A483" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1">
+      <c r="A484" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1">
+      <c r="A485" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1">
+      <c r="A486" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1">
+      <c r="A487" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1">
+      <c r="A488" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1">
+      <c r="A489" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1">
+      <c r="A490" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1">
+      <c r="A491" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1">
+      <c r="A492" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1">
+      <c r="A493" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1">
+      <c r="A494" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1">
+      <c r="A495" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1">
+      <c r="A496" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1">
+      <c r="A497" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1">
+      <c r="A498" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1">
+      <c r="A499" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1">
+      <c r="A500" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1">
+      <c r="A501" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1">
+      <c r="A502" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1">
+      <c r="A503" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1">
+      <c r="A504" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1">
+      <c r="A505" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1">
+      <c r="A506" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1">
+      <c r="A507" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1">
+      <c r="A508" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1">
+      <c r="A509" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1">
+      <c r="A510" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1">
+      <c r="A511" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1">
+      <c r="A512" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1">
+      <c r="A513" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1">
+      <c r="A514" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1">
+      <c r="A515" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1">
+      <c r="A516" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1">
+      <c r="A517" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1">
+      <c r="A518" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1">
+      <c r="A519" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1">
+      <c r="A520" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1">
+      <c r="A521" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1">
+      <c r="A522" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1">
+      <c r="A523" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1">
+      <c r="A524" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1">
+      <c r="A525" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1">
+      <c r="A526" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1">
+      <c r="A527" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1">
+      <c r="A528" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1">
+      <c r="A529" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1">
+      <c r="A530" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1">
+      <c r="A531" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1">
+      <c r="A532" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1">
+      <c r="A533" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1">
+      <c r="A534" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1">
+      <c r="A535" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1">
+      <c r="A536" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1">
+      <c r="A537" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1">
+      <c r="A538" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1">
+      <c r="A539" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1">
+      <c r="A540" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1">
+      <c r="A541" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1">
+      <c r="A542" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1">
+      <c r="A543" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1">
+      <c r="A544" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1">
+      <c r="A545" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1">
+      <c r="A546" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1">
+      <c r="A547" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1">
+      <c r="A548" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1">
+      <c r="A549" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1">
+      <c r="A550" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1">
+      <c r="A551" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1">
+      <c r="A552" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1">
+      <c r="A553" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1">
+      <c r="A554" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1">
+      <c r="A555" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1">
+      <c r="A556" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1">
+      <c r="A557" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1">
+      <c r="A558" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1">
+      <c r="A559" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1">
+      <c r="A560" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1">
+      <c r="A561" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1">
+      <c r="A562" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1">
+      <c r="A563" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1">
+      <c r="A564" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1">
+      <c r="A565" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1">
+      <c r="A566" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1">
+      <c r="A567" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1">
+      <c r="A568" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1">
+      <c r="A569" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1">
+      <c r="A570" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1">
+      <c r="A571" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1">
+      <c r="A572" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1">
+      <c r="A573" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1">
+      <c r="A574" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1">
+      <c r="A575" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1">
+      <c r="A576" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1">
+      <c r="A577" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1">
+      <c r="A578" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1">
+      <c r="A579" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1">
+      <c r="A580" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1">
+      <c r="A581" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1">
+      <c r="A582" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1">
+      <c r="A583" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1">
+      <c r="A584" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1">
+      <c r="A585" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1">
+      <c r="A586" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1">
+      <c r="A587" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1">
+      <c r="A588" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1">
+      <c r="A589" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1">
+      <c r="A590" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1">
+      <c r="A591" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1">
+      <c r="A592" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1">
+      <c r="A593" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1">
+      <c r="A594" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1">
+      <c r="A595" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1">
+      <c r="A596" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1">
+      <c r="A597" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1">
+      <c r="A598" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1">
+      <c r="A599" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1">
+      <c r="A600" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1">
+      <c r="A601" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1">
+      <c r="A602" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1">
+      <c r="A603" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1">
+      <c r="A604" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1">
+      <c r="A605" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1">
+      <c r="A606" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1">
+      <c r="A607" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1">
+      <c r="A608" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1">
+      <c r="A609" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1">
+      <c r="A610" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1">
+      <c r="A611" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1">
+      <c r="A612" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1">
+      <c r="A613" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1">
+      <c r="A614" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1">
+      <c r="A615" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1">
+      <c r="A616" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1">
+      <c r="A617" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1">
+      <c r="A618" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1">
+      <c r="A619" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1">
+      <c r="A620" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1">
+      <c r="A621" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1">
+      <c r="A622" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1">
+      <c r="A623" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1">
+      <c r="A624" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1">
+      <c r="A625" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1">
+      <c r="A626" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1">
+      <c r="A627" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1">
+      <c r="A628" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1">
+      <c r="A629" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1">
+      <c r="A630" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1">
+      <c r="A631" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1">
+      <c r="A632" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1">
+      <c r="A633" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1">
+      <c r="A634" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="635" spans="1:1">
+      <c r="A635" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1">
+      <c r="A636" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1">
+      <c r="A637" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1">
+      <c r="A638" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1">
+      <c r="A639" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1">
+      <c r="A640" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1">
+      <c r="A641" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1">
+      <c r="A642" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1">
+      <c r="A643" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1">
+      <c r="A644" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1">
+      <c r="A645" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1">
+      <c r="A646" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1">
+      <c r="A647" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1">
+      <c r="A648" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1">
+      <c r="A649" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1">
+      <c r="A650" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1">
+      <c r="A651" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1">
+      <c r="A652" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="653" spans="1:1">
+      <c r="A653" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1">
+      <c r="A654" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1">
+      <c r="A655" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1">
+      <c r="A656" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1">
+      <c r="A657" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1">
+      <c r="A658" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="659" spans="1:1">
+      <c r="A659" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1">
+      <c r="A660" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1">
+      <c r="A661" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1">
+      <c r="A662" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1">
+      <c r="A663" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1">
+      <c r="A664" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="665" spans="1:1">
+      <c r="A665" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1">
+      <c r="A666" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="667" spans="1:1">
+      <c r="A667" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="668" spans="1:1">
+      <c r="A668" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="669" spans="1:1">
+      <c r="A669" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="670" spans="1:1">
+      <c r="A670" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="671" spans="1:1">
+      <c r="A671" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="672" spans="1:1">
+      <c r="A672" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="673" spans="1:1">
+      <c r="A673" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="674" spans="1:1">
+      <c r="A674" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="675" spans="1:1">
+      <c r="A675" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="676" spans="1:1">
+      <c r="A676" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="677" spans="1:1">
+      <c r="A677" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="678" spans="1:1">
+      <c r="A678" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="679" spans="1:1">
+      <c r="A679" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="680" spans="1:1">
+      <c r="A680" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="681" spans="1:1">
+      <c r="A681" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="682" spans="1:1">
+      <c r="A682" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="683" spans="1:1">
+      <c r="A683" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="684" spans="1:1">
+      <c r="A684" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="685" spans="1:1">
+      <c r="A685" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="686" spans="1:1">
+      <c r="A686" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="687" spans="1:1">
+      <c r="A687" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="688" spans="1:1">
+      <c r="A688" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="689" spans="1:1">
+      <c r="A689" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="690" spans="1:1">
+      <c r="A690" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="691" spans="1:1">
+      <c r="A691" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="692" spans="1:1">
+      <c r="A692" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="693" spans="1:1">
+      <c r="A693" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="694" spans="1:1">
+      <c r="A694" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="695" spans="1:1">
+      <c r="A695" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="696" spans="1:1">
+      <c r="A696" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="697" spans="1:1">
+      <c r="A697" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="698" spans="1:1">
+      <c r="A698" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="699" spans="1:1">
+      <c r="A699" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="700" spans="1:1">
+      <c r="A700" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="701" spans="1:1">
+      <c r="A701" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="702" spans="1:1">
+      <c r="A702" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="703" spans="1:1">
+      <c r="A703" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="704" spans="1:1">
+      <c r="A704" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="705" spans="1:1">
+      <c r="A705" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="706" spans="1:1">
+      <c r="A706" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="707" spans="1:1">
+      <c r="A707" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="708" spans="1:1">
+      <c r="A708" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="709" spans="1:1">
+      <c r="A709" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="710" spans="1:1">
+      <c r="A710" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="711" spans="1:1">
+      <c r="A711" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="712" spans="1:1">
+      <c r="A712" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="713" spans="1:1">
+      <c r="A713" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="714" spans="1:1">
+      <c r="A714" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="715" spans="1:1">
+      <c r="A715" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="716" spans="1:1">
+      <c r="A716" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="717" spans="1:1">
+      <c r="A717" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="718" spans="1:1">
+      <c r="A718" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="719" spans="1:1">
+      <c r="A719" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="720" spans="1:1">
+      <c r="A720" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="721" spans="1:1">
+      <c r="A721" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="722" spans="1:1">
+      <c r="A722" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="723" spans="1:1">
+      <c r="A723" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="724" spans="1:1">
+      <c r="A724" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="725" spans="1:1">
+      <c r="A725" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="726" spans="1:1">
+      <c r="A726" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="727" spans="1:1">
+      <c r="A727" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="728" spans="1:1">
+      <c r="A728" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="729" spans="1:1">
+      <c r="A729" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="730" spans="1:1">
+      <c r="A730" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="731" spans="1:1">
+      <c r="A731" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="732" spans="1:1">
+      <c r="A732" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="733" spans="1:1">
+      <c r="A733" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="734" spans="1:1">
+      <c r="A734" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="735" spans="1:1">
+      <c r="A735" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="736" spans="1:1">
+      <c r="A736" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="737" spans="1:1">
+      <c r="A737" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="738" spans="1:1">
+      <c r="A738" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="739" spans="1:1">
+      <c r="A739" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="740" spans="1:1">
+      <c r="A740" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="741" spans="1:1">
+      <c r="A741" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="742" spans="1:1">
+      <c r="A742" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="743" spans="1:1">
+      <c r="A743" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="744" spans="1:1">
+      <c r="A744" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="745" spans="1:1">
+      <c r="A745" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="746" spans="1:1">
+      <c r="A746" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="747" spans="1:1">
+      <c r="A747" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="748" spans="1:1">
+      <c r="A748" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="749" spans="1:1">
+      <c r="A749" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="750" spans="1:1">
+      <c r="A750" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="751" spans="1:1">
+      <c r="A751" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="752" spans="1:1">
+      <c r="A752" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="753" spans="1:1">
+      <c r="A753" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="754" spans="1:1">
+      <c r="A754" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="755" spans="1:1">
+      <c r="A755" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="756" spans="1:1">
+      <c r="A756" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="757" spans="1:1">
+      <c r="A757" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="758" spans="1:1">
+      <c r="A758" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="759" spans="1:1">
+      <c r="A759" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="760" spans="1:1">
+      <c r="A760" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="761" spans="1:1">
+      <c r="A761" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="762" spans="1:1">
+      <c r="A762" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="763" spans="1:1">
+      <c r="A763" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="764" spans="1:1">
+      <c r="A764" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="765" spans="1:1">
+      <c r="A765" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="766" spans="1:1">
+      <c r="A766" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="767" spans="1:1">
+      <c r="A767" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="768" spans="1:1">
+      <c r="A768" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="769" spans="1:1">
+      <c r="A769" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="770" spans="1:1">
+      <c r="A770" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="771" spans="1:1">
+      <c r="A771" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="772" spans="1:1">
+      <c r="A772" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="773" spans="1:1">
+      <c r="A773" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="774" spans="1:1">
+      <c r="A774" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="775" spans="1:1">
+      <c r="A775" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="776" spans="1:1">
+      <c r="A776" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="777" spans="1:1">
+      <c r="A777" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="778" spans="1:1">
+      <c r="A778" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="779" spans="1:1">
+      <c r="A779" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="780" spans="1:1">
+      <c r="A780" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="781" spans="1:1">
+      <c r="A781" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="782" spans="1:1">
+      <c r="A782" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="783" spans="1:1">
+      <c r="A783" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="784" spans="1:1">
+      <c r="A784" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="785" spans="1:1">
+      <c r="A785" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="786" spans="1:1">
+      <c r="A786" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="787" spans="1:1">
+      <c r="A787" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="788" spans="1:1">
+      <c r="A788" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="789" spans="1:1">
+      <c r="A789" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="790" spans="1:1">
+      <c r="A790" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="791" spans="1:1">
+      <c r="A791" t="s">
+        <v>803</v>
       </c>
     </row>
   </sheetData>

--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Documents\siteicin-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C223843-B447-475E-BECC-CA0C81708159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5FC717-AB96-4A0A-96C1-45F39DEA4562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="807">
   <si>
     <t>kelime_adi</t>
   </si>
@@ -95,9 +95,6 @@
     <t>ACIMASIZ</t>
   </si>
   <si>
-    <t>ACUN</t>
-  </si>
-  <si>
     <t>AÇI</t>
   </si>
   <si>
@@ -2457,6 +2454,58 @@
   </si>
   <si>
     <t>ZORUNLU</t>
+  </si>
+  <si>
+    <t>Geometri, Mustafa Kemal  (1937)</t>
+  </si>
+  <si>
+    <t>1)Zaviye
+2)Cephe
+3)Veçhe
+4)Cihet
+5)Hasep
+6)Yön
+7)Pencere
+8)Bakım
+9)Nokta-i nazar
+10)İnd
+11)Ufuk</t>
+  </si>
+  <si>
+    <t>Mustafa Kemal'in icadıdır. Geometrideki zaviye kelimesinin yerine düşünülmüştü fakat sonradan görüş, perspektif vs. manalardaki birçok kelimenin yerine kullanılmaya başlandı.</t>
+  </si>
+  <si>
+    <t>1)Açı ayraç
+2)Açı ölçüm
+3)Açı parantez
+4)Açıortay
+5)Açıölçer
+6)Alt açı
+7)Bakış açısı
+8)Bütünler açı
+9)Çevre açı
+10)Dar açı
+11)Dış açı
+12)Dış ters açı
+13)Dik açı
+14)Doğru açı
+15)Geniş açı
+16)Gol açısı
+17)Görme açısı
+18)Görüş açısı
+19)İç ters açı
+20)Karşı açı
+21)Komşu açı
+22)Merkez açı
+23)Ölü açı
+24)Saat açısı
+25)Sınır açı
+26)Tam açı
+27)Tepe açısı
+28)Ters açı
+29)Tümler açı
+30)Üst açı
+31)Yöndeş açılar</t>
   </si>
 </sst>
 </file>
@@ -2508,7 +2557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2518,7 +2567,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2853,7 +2901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{984A1489-2204-4320-8C2B-598D19BA0E68}">
-  <dimension ref="A1:H791"/>
+  <dimension ref="A1:H790"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
@@ -2883,7 +2931,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -2921,9 +2969,24 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="13.8" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>806</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4592,7 +4655,7 @@
       </c>
     </row>
     <row r="338" spans="1:1">
-      <c r="A338" s="2" t="s">
+      <c r="A338" t="s">
         <v>350</v>
       </c>
     </row>
@@ -6854,11 +6917,6 @@
     <row r="790" spans="1:1">
       <c r="A790" t="s">
         <v>802</v>
-      </c>
-    </row>
-    <row r="791" spans="1:1">
-      <c r="A791" t="s">
-        <v>803</v>
       </c>
     </row>
   </sheetData>

--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Documents\siteicin-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1315E6AB-0B8E-465A-8330-F98464FFDE03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA6B938-0168-4A62-9042-33BF1B24499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>kelime_adi</t>
   </si>
@@ -95,29 +95,26 @@
     <t>AÇI</t>
   </si>
   <si>
-    <t>Geometri, Mustafa Kemal  (1937)</t>
-  </si>
-  <si>
-    <t>1)Zaviye
-2)Cephe
-3)Veçhe
-4)Cihet
-5)Hasep
-6)Yön
-7)Pencere
-8)Bakım
-9)Nokta-i nazar
-10)İnd
-11)Ufuk</t>
+    <t>Geometri, Mustafa Kemal (1937)</t>
   </si>
   <si>
     <t>Mustafa Kemal'in icadıdır. Geometrideki zaviye kelimesinin yerine düşünülmüştü fakat sonradan görüş, perspektif vs. manalardaki birçok kelimenin yerine kullanılmaya başlandı.</t>
   </si>
   <si>
-    <t>1)Abartılı: Müfrit/mufriṭ (ﻣﻔﺮﻁ)</t>
-  </si>
-  <si>
     <t>Anadolu halk şiveleri</t>
+  </si>
+  <si>
+    <t>1)Zaviye/zāviye (ﺯﺍﻭﻳﻪ)
+2)Cephe/cebhe (ﺟﺒﻬﻪ)
+3)Veçhe/veche (ﻭﺟﻬﻪ)
+4)Cihet/cihet (ﺟﻬﺖ)
+5)Hasep/ḥaseb (ﺣﺴﺐ)
+6)Nokta-i nazar/noḳṭa-i nazar (ﻧﻈﺮ ﻧﻘﻄﻪ)
+7)İnd/‘ind (ﻋﻨﺪ)
+8)Ufuk/ufḳ (ﺍﻓﻖ)
+9)Pencere (ﭘﻨﺠﺮﻩ)
+10)Yön
+11)Bakım</t>
   </si>
 </sst>
 </file>
@@ -558,7 +555,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
@@ -568,9 +565,6 @@
       </c>
       <c r="E2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -592,13 +586,13 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H4" s="4"/>
     </row>

--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Documents\siteicin-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA6B938-0168-4A62-9042-33BF1B24499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B95D452-E680-46F3-8BAD-C0D8C64BBFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
   </bookViews>
@@ -86,15 +86,6 @@
 5)Zalim/ẓālim (ﻇﺎﻟﻢ)</t>
   </si>
   <si>
-    <t>ABARTMAK</t>
-  </si>
-  <si>
-    <t>ACIMASIZ</t>
-  </si>
-  <si>
-    <t>AÇI</t>
-  </si>
-  <si>
     <t>Geometri, Mustafa Kemal (1937)</t>
   </si>
   <si>
@@ -102,6 +93,15 @@
   </si>
   <si>
     <t>Anadolu halk şiveleri</t>
+  </si>
+  <si>
+    <t>Abartmak</t>
+  </si>
+  <si>
+    <t>Acımasız</t>
+  </si>
+  <si>
+    <t>Açı</t>
   </si>
   <si>
     <t>1)Zaviye/zāviye (ﺯﺍﻭﻳﻪ)
@@ -111,10 +111,7 @@
 5)Hasep/ḥaseb (ﺣﺴﺐ)
 6)Nokta-i nazar/noḳṭa-i nazar (ﻧﻈﺮ ﻧﻘﻄﻪ)
 7)İnd/‘ind (ﻋﻨﺪ)
-8)Ufuk/ufḳ (ﺍﻓﻖ)
-9)Pencere (ﭘﻨﺠﺮﻩ)
-10)Yön
-11)Bakım</t>
+8)Ufuk/ufḳ (ﺍﻓﻖ)</t>
   </si>
 </sst>
 </file>
@@ -166,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -176,6 +173,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +515,7 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
-    <col min="2" max="2" width="32" style="3" customWidth="1"/>
+    <col min="2" max="2" width="32" style="6" customWidth="1"/>
     <col min="3" max="3" width="33.88671875" style="3" customWidth="1"/>
     <col min="4" max="4" width="35.5546875" style="3" customWidth="1"/>
     <col min="5" max="5" width="31.33203125" style="3" customWidth="1"/>
@@ -552,10 +553,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
@@ -569,9 +570,9 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -580,16 +581,16 @@
     </row>
     <row r="4" spans="1:8" ht="13.8" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>19</v>

--- a/lugat.xlsx
+++ b/lugat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ekmel\Documents\siteicin-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B95D452-E680-46F3-8BAD-C0D8C64BBFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2115BFD8-09FD-4F9D-8844-1FD91C557FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{9AC8C891-EFC2-4761-8CC2-93DDC8B0E422}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="807">
   <si>
     <t>kelime_adi</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Tarama Dergisinde Konya şivesinden olduğu kaydı vardır.</t>
-  </si>
-  <si>
-    <t>Neolojizm/Kelime uydurma</t>
   </si>
   <si>
     <t>1)Merhametsiz   [merhamet/merhamet (ﻣﺮﺣﻤﺖ)]
@@ -90,9 +87,6 @@
   </si>
   <si>
     <t>Mustafa Kemal'in icadıdır. Geometrideki zaviye kelimesinin yerine düşünülmüştü fakat sonradan görüş, perspektif vs. manalardaki birçok kelimenin yerine kullanılmaya başlandı.</t>
-  </si>
-  <si>
-    <t>Anadolu halk şiveleri</t>
   </si>
   <si>
     <t>Abartmak</t>
@@ -112,6 +106,2373 @@
 6)Nokta-i nazar/noḳṭa-i nazar (ﻧﻈﺮ ﻧﻘﻄﻪ)
 7)İnd/‘ind (ﻋﻨﺪ)
 8)Ufuk/ufḳ (ﺍﻓﻖ)</t>
+  </si>
+  <si>
+    <t>Açıklamak</t>
+  </si>
+  <si>
+    <t>Açılım</t>
+  </si>
+  <si>
+    <t>Aday</t>
+  </si>
+  <si>
+    <t>Neolojizm</t>
+  </si>
+  <si>
+    <t>Anadolu Halk Şiveleri</t>
+  </si>
+  <si>
+    <t>Acun</t>
+  </si>
+  <si>
+    <t>Açık artırma</t>
+  </si>
+  <si>
+    <t>Açık oturum</t>
+  </si>
+  <si>
+    <t>Açık oy</t>
+  </si>
+  <si>
+    <t>Ad çekmek</t>
+  </si>
+  <si>
+    <t>Ahlâksal</t>
+  </si>
+  <si>
+    <t>Akaryakıt</t>
+  </si>
+  <si>
+    <t>Akçasal</t>
+  </si>
+  <si>
+    <t>Akım</t>
+  </si>
+  <si>
+    <t>Akkor</t>
+  </si>
+  <si>
+    <t>Akyuvar</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>Albay</t>
+  </si>
+  <si>
+    <t>Algı</t>
+  </si>
+  <si>
+    <t>Alımlı</t>
+  </si>
+  <si>
+    <t>Alındı</t>
+  </si>
+  <si>
+    <t>Alıntı</t>
+  </si>
+  <si>
+    <t>Almaç</t>
+  </si>
+  <si>
+    <t>Amaç</t>
+  </si>
+  <si>
+    <t>Anaerki</t>
+  </si>
+  <si>
+    <t>Ana gündem maddesi</t>
+  </si>
+  <si>
+    <t>Anayasa</t>
+  </si>
+  <si>
+    <t>Anı</t>
+  </si>
+  <si>
+    <t>Anımsamak</t>
+  </si>
+  <si>
+    <t>Anıt</t>
+  </si>
+  <si>
+    <t>Anlam</t>
+  </si>
+  <si>
+    <t>Anlaşmazlık</t>
+  </si>
+  <si>
+    <t>Anlatı</t>
+  </si>
+  <si>
+    <t>Anlayış</t>
+  </si>
+  <si>
+    <t>Anma töreni</t>
+  </si>
+  <si>
+    <t>Aracı</t>
+  </si>
+  <si>
+    <t>Araç</t>
+  </si>
+  <si>
+    <t>Arakesit</t>
+  </si>
+  <si>
+    <t>Aralık</t>
+  </si>
+  <si>
+    <t>Arasöz</t>
+  </si>
+  <si>
+    <t>Araştırma kurulu</t>
+  </si>
+  <si>
+    <t>Ardıl</t>
+  </si>
+  <si>
+    <t>Arılaştırma</t>
+  </si>
+  <si>
+    <t>Artı</t>
+  </si>
+  <si>
+    <t>Asalak</t>
+  </si>
+  <si>
+    <t>Ast</t>
+  </si>
+  <si>
+    <t>Astsubay</t>
+  </si>
+  <si>
+    <t>Asteğmen</t>
+  </si>
+  <si>
+    <t>Aşama</t>
+  </si>
+  <si>
+    <t>Ataerki</t>
+  </si>
+  <si>
+    <t>Atamak</t>
+  </si>
+  <si>
+    <t>Atardamar</t>
+  </si>
+  <si>
+    <t>Ateşkes</t>
+  </si>
+  <si>
+    <t>Atılım</t>
+  </si>
+  <si>
+    <t>Avuntu</t>
+  </si>
+  <si>
+    <t>Ayça</t>
+  </si>
+  <si>
+    <t>Aydın</t>
+  </si>
+  <si>
+    <t>Aygıt</t>
+  </si>
+  <si>
+    <t>Ayırtman</t>
+  </si>
+  <si>
+    <t>Aymaz</t>
+  </si>
+  <si>
+    <t>Ayraç</t>
+  </si>
+  <si>
+    <t>Ayrıcalık</t>
+  </si>
+  <si>
+    <t>Ayrım</t>
+  </si>
+  <si>
+    <t>Ayrıntı</t>
+  </si>
+  <si>
+    <t>Ayrışık</t>
+  </si>
+  <si>
+    <t>Azınlık</t>
+  </si>
+  <si>
+    <t>Bağıl</t>
+  </si>
+  <si>
+    <t>Bağımlı</t>
+  </si>
+  <si>
+    <t>Bağımsız</t>
+  </si>
+  <si>
+    <t>Bağıntı</t>
+  </si>
+  <si>
+    <t>Bağışık</t>
+  </si>
+  <si>
+    <t>Bağıt</t>
+  </si>
+  <si>
+    <t>Bağlaç</t>
+  </si>
+  <si>
+    <t>Bağlam</t>
+  </si>
+  <si>
+    <t>Bağlantı</t>
+  </si>
+  <si>
+    <t>Bağlaşık</t>
+  </si>
+  <si>
+    <t>Bağnaz</t>
+  </si>
+  <si>
+    <t>Bakan</t>
+  </si>
+  <si>
+    <t>Bakış açısı</t>
+  </si>
+  <si>
+    <t>Barınak</t>
+  </si>
+  <si>
+    <t>Barışçıl</t>
+  </si>
+  <si>
+    <t>Basın</t>
+  </si>
+  <si>
+    <t>Başarı</t>
+  </si>
+  <si>
+    <t>Başat</t>
+  </si>
+  <si>
+    <t>Başbakan</t>
+  </si>
+  <si>
+    <t>Başbayan</t>
+  </si>
+  <si>
+    <t>Başbuğ</t>
+  </si>
+  <si>
+    <t>Başkaldırı</t>
+  </si>
+  <si>
+    <t>Başkan</t>
+  </si>
+  <si>
+    <t>Başkent</t>
+  </si>
+  <si>
+    <t>Başkomutan</t>
+  </si>
+  <si>
+    <t>Başöğretmen</t>
+  </si>
+  <si>
+    <t>Başvuru</t>
+  </si>
+  <si>
+    <t>Başyapıt</t>
+  </si>
+  <si>
+    <t>Başyazar</t>
+  </si>
+  <si>
+    <t>Bay</t>
+  </si>
+  <si>
+    <t>Bayındır</t>
+  </si>
+  <si>
+    <t>Bedensel</t>
+  </si>
+  <si>
+    <t>Beğeni</t>
+  </si>
+  <si>
+    <t>Belge</t>
+  </si>
+  <si>
+    <t>Belirgin</t>
+  </si>
+  <si>
+    <t>Belirlemek</t>
+  </si>
+  <si>
+    <t>Belirteç</t>
+  </si>
+  <si>
+    <t>Belirti</t>
+  </si>
+  <si>
+    <t>Bellek</t>
+  </si>
+  <si>
+    <t>Bencil</t>
+  </si>
+  <si>
+    <t>Bengi</t>
+  </si>
+  <si>
+    <t>Benzeti</t>
+  </si>
+  <si>
+    <t>Besin</t>
+  </si>
+  <si>
+    <t>Beşgen</t>
+  </si>
+  <si>
+    <t>Betim</t>
+  </si>
+  <si>
+    <t>Bırakışma</t>
+  </si>
+  <si>
+    <t>Bildiri</t>
+  </si>
+  <si>
+    <t>Bileşik</t>
+  </si>
+  <si>
+    <t>Bilge</t>
+  </si>
+  <si>
+    <t>Bilgi</t>
+  </si>
+  <si>
+    <t>Bilim</t>
+  </si>
+  <si>
+    <t>Bilinç</t>
+  </si>
+  <si>
+    <t>Bilirkişi</t>
+  </si>
+  <si>
+    <t>Birey</t>
+  </si>
+  <si>
+    <t>Birikim</t>
+  </si>
+  <si>
+    <t>Birim</t>
+  </si>
+  <si>
+    <t>Birincil</t>
+  </si>
+  <si>
+    <t>Birleşik</t>
+  </si>
+  <si>
+    <t>Bir süre</t>
+  </si>
+  <si>
+    <t>Bir tür</t>
+  </si>
+  <si>
+    <t>Bitimli</t>
+  </si>
+  <si>
+    <t>Bitki</t>
+  </si>
+  <si>
+    <t>Boş inanç</t>
+  </si>
+  <si>
+    <t>Boylam</t>
+  </si>
+  <si>
+    <t>Boyut</t>
+  </si>
+  <si>
+    <t>Böbrek yetmezliği</t>
+  </si>
+  <si>
+    <t>Bölge</t>
+  </si>
+  <si>
+    <t>Bölüm</t>
+  </si>
+  <si>
+    <t>Bucak</t>
+  </si>
+  <si>
+    <t>Budunbilim (budun bilimi)</t>
+  </si>
+  <si>
+    <t>Bu durumda</t>
+  </si>
+  <si>
+    <t>Bulgu</t>
+  </si>
+  <si>
+    <t>Bunalım</t>
+  </si>
+  <si>
+    <t>Bu tür</t>
+  </si>
+  <si>
+    <t>Buzul</t>
+  </si>
+  <si>
+    <t>Bütünsel</t>
+  </si>
+  <si>
+    <t>Büyük çoğunluk</t>
+  </si>
+  <si>
+    <t>Büyük olasılıkla</t>
+  </si>
+  <si>
+    <t>Büyüteç</t>
+  </si>
+  <si>
+    <t>Cenâze töreni</t>
+  </si>
+  <si>
+    <t>Cinsel</t>
+  </si>
+  <si>
+    <t>Coşku</t>
+  </si>
+  <si>
+    <t>Cumhurbaşkanı</t>
+  </si>
+  <si>
+    <t>Cümlecik</t>
+  </si>
+  <si>
+    <t>Çaba</t>
+  </si>
+  <si>
+    <t>Çağdaş</t>
+  </si>
+  <si>
+    <t>Çağrı</t>
+  </si>
+  <si>
+    <t>Çarpım</t>
+  </si>
+  <si>
+    <t>Çatı</t>
+  </si>
+  <si>
+    <t>Çekim</t>
+  </si>
+  <si>
+    <t>Çelişki</t>
+  </si>
+  <si>
+    <t>Çelmece</t>
+  </si>
+  <si>
+    <t>Çeviri</t>
+  </si>
+  <si>
+    <t>Çıkarım</t>
+  </si>
+  <si>
+    <t>Çizelge</t>
+  </si>
+  <si>
+    <t>Çocuk esirgeme kurumu</t>
+  </si>
+  <si>
+    <t>Çoğul</t>
+  </si>
+  <si>
+    <t>Çokgen</t>
+  </si>
+  <si>
+    <t>Çok önemli</t>
+  </si>
+  <si>
+    <t>Çok özel</t>
+  </si>
+  <si>
+    <t>Çökelti</t>
+  </si>
+  <si>
+    <t>Çöküntü</t>
+  </si>
+  <si>
+    <t>Çözelti</t>
+  </si>
+  <si>
+    <t>Çözüm</t>
+  </si>
+  <si>
+    <t>Dağılım</t>
+  </si>
+  <si>
+    <t>Daha önemli</t>
+  </si>
+  <si>
+    <t>Dairesel</t>
+  </si>
+  <si>
+    <t>Damıtık</t>
+  </si>
+  <si>
+    <t>Danışman</t>
+  </si>
+  <si>
+    <t>Dayanak</t>
+  </si>
+  <si>
+    <t>Dayanışma</t>
+  </si>
+  <si>
+    <t>Değerbilir</t>
+  </si>
+  <si>
+    <t>Değğin</t>
+  </si>
+  <si>
+    <t>Değini</t>
+  </si>
+  <si>
+    <t>Değişim</t>
+  </si>
+  <si>
+    <t>Delgeç</t>
+  </si>
+  <si>
+    <t>Demeç</t>
+  </si>
+  <si>
+    <t>Denek</t>
+  </si>
+  <si>
+    <t>Denetim</t>
+  </si>
+  <si>
+    <t>Deney</t>
+  </si>
+  <si>
+    <t>Denge</t>
+  </si>
+  <si>
+    <t>Denklem</t>
+  </si>
+  <si>
+    <t>Deprem</t>
+  </si>
+  <si>
+    <t>Dergi</t>
+  </si>
+  <si>
+    <t>Derslik</t>
+  </si>
+  <si>
+    <t>Devinim</t>
+  </si>
+  <si>
+    <t>Devlet başkanı</t>
+  </si>
+  <si>
+    <t>Devrim</t>
+  </si>
+  <si>
+    <t>Deyim</t>
+  </si>
+  <si>
+    <t>Dışalım</t>
+  </si>
+  <si>
+    <t>Dış işleri</t>
+  </si>
+  <si>
+    <t>Dışkı</t>
+  </si>
+  <si>
+    <t>Dışsatım</t>
+  </si>
+  <si>
+    <t>Dik açı</t>
+  </si>
+  <si>
+    <t>Dikdörtgen</t>
+  </si>
+  <si>
+    <t>Dikey</t>
+  </si>
+  <si>
+    <t>Dilbilim (dil bilimi)</t>
+  </si>
+  <si>
+    <t>Dilekçe</t>
+  </si>
+  <si>
+    <t>Dingin</t>
+  </si>
+  <si>
+    <t>Dinsel</t>
+  </si>
+  <si>
+    <t>Direnç</t>
+  </si>
+  <si>
+    <t>Dişil</t>
+  </si>
+  <si>
+    <t>Dize</t>
+  </si>
+  <si>
+    <t>Dizge</t>
+  </si>
+  <si>
+    <t>Doğa</t>
+  </si>
+  <si>
+    <t>Doğmaca</t>
+  </si>
+  <si>
+    <t>Doğru orantılı</t>
+  </si>
+  <si>
+    <t>Doku</t>
+  </si>
+  <si>
+    <t>Dolaşım</t>
+  </si>
+  <si>
+    <t>Donanım</t>
+  </si>
+  <si>
+    <t>Doygun</t>
+  </si>
+  <si>
+    <t>Dölleme (döllenme)</t>
+  </si>
+  <si>
+    <t>Dönem</t>
+  </si>
+  <si>
+    <t>Dört işlem</t>
+  </si>
+  <si>
+    <t>Durağan</t>
+  </si>
+  <si>
+    <t>Durum</t>
+  </si>
+  <si>
+    <t>Duyarlı</t>
+  </si>
+  <si>
+    <t>Duyu</t>
+  </si>
+  <si>
+    <t>Dürtü</t>
+  </si>
+  <si>
+    <t>Düş</t>
+  </si>
+  <si>
+    <t>Düşünce</t>
+  </si>
+  <si>
+    <t>Düze</t>
+  </si>
+  <si>
+    <t>Düzelti</t>
+  </si>
+  <si>
+    <t>Düzenlemek</t>
+  </si>
+  <si>
+    <t>Düzey</t>
+  </si>
+  <si>
+    <t>Düzlem</t>
+  </si>
+  <si>
+    <t>Düzyazı</t>
+  </si>
+  <si>
+    <t>Eder</t>
+  </si>
+  <si>
+    <t>Edilgen</t>
+  </si>
+  <si>
+    <t>Edim</t>
+  </si>
+  <si>
+    <t>Egemen</t>
+  </si>
+  <si>
+    <t>Eğilim</t>
+  </si>
+  <si>
+    <t>Eğitim</t>
+  </si>
+  <si>
+    <t>Ekim</t>
+  </si>
+  <si>
+    <t>Eklem</t>
+  </si>
+  <si>
+    <t>Ekonomi bakanı</t>
+  </si>
+  <si>
+    <t>Eksen</t>
+  </si>
+  <si>
+    <t>Eksi</t>
+  </si>
+  <si>
+    <t>Ek süre</t>
+  </si>
+  <si>
+    <t>Elektrik sayacı</t>
+  </si>
+  <si>
+    <t>Eleştiri</t>
+  </si>
+  <si>
+    <t>Emekli</t>
+  </si>
+  <si>
+    <t>Emir komuta zinciri</t>
+  </si>
+  <si>
+    <t>Emniyet genel müdürlüğü</t>
+  </si>
+  <si>
+    <t>En önemli</t>
+  </si>
+  <si>
+    <t>En özel</t>
+  </si>
+  <si>
+    <t>Erdem</t>
+  </si>
+  <si>
+    <t>Erek</t>
+  </si>
+  <si>
+    <t>Eril</t>
+  </si>
+  <si>
+    <t>Erişim</t>
+  </si>
+  <si>
+    <t>Erk</t>
+  </si>
+  <si>
+    <t>Esen kal (esen kalın)</t>
+  </si>
+  <si>
+    <t>Esin</t>
+  </si>
+  <si>
+    <t>Eş anlam</t>
+  </si>
+  <si>
+    <t>Eşcinsel</t>
+  </si>
+  <si>
+    <t>Eş değer</t>
+  </si>
+  <si>
+    <t>Eşey</t>
+  </si>
+  <si>
+    <t>Eş güdüm</t>
+  </si>
+  <si>
+    <t>Eşit</t>
+  </si>
+  <si>
+    <t>Eşsesli</t>
+  </si>
+  <si>
+    <t>Etçil</t>
+  </si>
+  <si>
+    <t>Etken</t>
+  </si>
+  <si>
+    <t>Etki</t>
+  </si>
+  <si>
+    <t>Etmen</t>
+  </si>
+  <si>
+    <t>Evcil</t>
+  </si>
+  <si>
+    <t>Evirme</t>
+  </si>
+  <si>
+    <t>Evre</t>
+  </si>
+  <si>
+    <t>Evren</t>
+  </si>
+  <si>
+    <t>Evrim</t>
+  </si>
+  <si>
+    <t>Ev yönetimi</t>
+  </si>
+  <si>
+    <t>Eylem</t>
+  </si>
+  <si>
+    <t>Eytişim</t>
+  </si>
+  <si>
+    <t>Ezici çoğunluk</t>
+  </si>
+  <si>
+    <t>Fiziksel</t>
+  </si>
+  <si>
+    <t>Gazeteci yazar</t>
+  </si>
+  <si>
+    <t>Geçerli</t>
+  </si>
+  <si>
+    <t>Geçirgen</t>
+  </si>
+  <si>
+    <t>Gelecek kuşaklar</t>
+  </si>
+  <si>
+    <t>Gelenek</t>
+  </si>
+  <si>
+    <t>Gelgit</t>
+  </si>
+  <si>
+    <t>Gelir dağılımı</t>
+  </si>
+  <si>
+    <t>Gelişim</t>
+  </si>
+  <si>
+    <t>Genel</t>
+  </si>
+  <si>
+    <t>Genleşmek</t>
+  </si>
+  <si>
+    <t>Gerçekleşmek</t>
+  </si>
+  <si>
+    <t>Gereç</t>
+  </si>
+  <si>
+    <t>Gerekçe</t>
+  </si>
+  <si>
+    <t>Gerici</t>
+  </si>
+  <si>
+    <t>Gerilim</t>
+  </si>
+  <si>
+    <t>Getiri</t>
+  </si>
+  <si>
+    <t>Gezegen</t>
+  </si>
+  <si>
+    <t>Gider</t>
+  </si>
+  <si>
+    <t>Girişim</t>
+  </si>
+  <si>
+    <t>Giysi</t>
+  </si>
+  <si>
+    <t>Giz</t>
+  </si>
+  <si>
+    <t>Göçmen</t>
+  </si>
+  <si>
+    <t>Gökbilim (gökbilimi)</t>
+  </si>
+  <si>
+    <t>Gönderi</t>
+  </si>
+  <si>
+    <t>Gönenç</t>
+  </si>
+  <si>
+    <t>Görece</t>
+  </si>
+  <si>
+    <t>Görev</t>
+  </si>
+  <si>
+    <t>Görgü kuralları</t>
+  </si>
+  <si>
+    <t>Görkem</t>
+  </si>
+  <si>
+    <t>Görsel</t>
+  </si>
+  <si>
+    <t>Görüntü</t>
+  </si>
+  <si>
+    <t>Gösterge</t>
+  </si>
+  <si>
+    <t>Gözaltı</t>
+  </si>
+  <si>
+    <t>Gözetim</t>
+  </si>
+  <si>
+    <t>Gözlem</t>
+  </si>
+  <si>
+    <t>Güç odağı</t>
+  </si>
+  <si>
+    <t>Güdü</t>
+  </si>
+  <si>
+    <t>Gümrük ve tekel bakanı</t>
+  </si>
+  <si>
+    <t>Günaydın</t>
+  </si>
+  <si>
+    <t>Günce</t>
+  </si>
+  <si>
+    <t>Gündem</t>
+  </si>
+  <si>
+    <t>Güney</t>
+  </si>
+  <si>
+    <t>Günlük</t>
+  </si>
+  <si>
+    <t>Güven</t>
+  </si>
+  <si>
+    <t>Halkoyu</t>
+  </si>
+  <si>
+    <t>Halk ozanı</t>
+  </si>
+  <si>
+    <t>Harp okulu</t>
+  </si>
+  <si>
+    <t>Hava akımı</t>
+  </si>
+  <si>
+    <t>Hayat okulu</t>
+  </si>
+  <si>
+    <t>Hayır kurumu</t>
+  </si>
+  <si>
+    <t>Hayvansal</t>
+  </si>
+  <si>
+    <t>Her durumda</t>
+  </si>
+  <si>
+    <t>Hoşgörü</t>
+  </si>
+  <si>
+    <t>Hukuk kuralları</t>
+  </si>
+  <si>
+    <t>Ilıman</t>
+  </si>
+  <si>
+    <t>Ira</t>
+  </si>
+  <si>
+    <t>Isı</t>
+  </si>
+  <si>
+    <t>İçbükey</t>
+  </si>
+  <si>
+    <t>İçerik</t>
+  </si>
+  <si>
+    <t>İçgüdü</t>
+  </si>
+  <si>
+    <t>İç işleri bakanı</t>
+  </si>
+  <si>
+    <t>İçsel</t>
+  </si>
+  <si>
+    <t>İçten</t>
+  </si>
+  <si>
+    <t>İçtüzük</t>
+  </si>
+  <si>
+    <t>İkilem</t>
+  </si>
+  <si>
+    <t>İkincil</t>
+  </si>
+  <si>
+    <t>İkircim</t>
+  </si>
+  <si>
+    <t>İlçe</t>
+  </si>
+  <si>
+    <t>İlerici</t>
+  </si>
+  <si>
+    <t>İleti</t>
+  </si>
+  <si>
+    <t>İlgi</t>
+  </si>
+  <si>
+    <t>İlinti</t>
+  </si>
+  <si>
+    <t>İlişki</t>
+  </si>
+  <si>
+    <t>İlke</t>
+  </si>
+  <si>
+    <t>İlkokul</t>
+  </si>
+  <si>
+    <t>İm</t>
+  </si>
+  <si>
+    <t>İmge</t>
+  </si>
+  <si>
+    <t>İmleç</t>
+  </si>
+  <si>
+    <t>İnanç</t>
+  </si>
+  <si>
+    <t>İndirgemek</t>
+  </si>
+  <si>
+    <t>İnsanbilim</t>
+  </si>
+  <si>
+    <t>İrdelemek</t>
+  </si>
+  <si>
+    <t>İstem</t>
+  </si>
+  <si>
+    <t>İş bölümü</t>
+  </si>
+  <si>
+    <t>İşitme duyusu</t>
+  </si>
+  <si>
+    <t>İşlem</t>
+  </si>
+  <si>
+    <t>İşlev</t>
+  </si>
+  <si>
+    <t>İş okulu</t>
+  </si>
+  <si>
+    <t>İvme</t>
+  </si>
+  <si>
+    <t>İye</t>
+  </si>
+  <si>
+    <t>İyimser</t>
+  </si>
+  <si>
+    <t>İzdüşüm</t>
+  </si>
+  <si>
+    <t>İzlem</t>
+  </si>
+  <si>
+    <t>Kaldıraç</t>
+  </si>
+  <si>
+    <t>Kalıt</t>
+  </si>
+  <si>
+    <t>Kamu</t>
+  </si>
+  <si>
+    <t>Kanaat önderi</t>
+  </si>
+  <si>
+    <t>Kan dolaşımı</t>
+  </si>
+  <si>
+    <t>Kanı</t>
+  </si>
+  <si>
+    <t>Kanıt</t>
+  </si>
+  <si>
+    <t>Kanun tasarısı</t>
+  </si>
+  <si>
+    <t>Kapalı oturum</t>
+  </si>
+  <si>
+    <t>Kaplam</t>
+  </si>
+  <si>
+    <t>Kapsam</t>
+  </si>
+  <si>
+    <t>Karamsar</t>
+  </si>
+  <si>
+    <t>Karasal</t>
+  </si>
+  <si>
+    <t>Karışım</t>
+  </si>
+  <si>
+    <t>Karmaşa</t>
+  </si>
+  <si>
+    <t>Karşılama töreni</t>
+  </si>
+  <si>
+    <t>Karşın</t>
+  </si>
+  <si>
+    <t>Karşıt</t>
+  </si>
+  <si>
+    <t>Kas</t>
+  </si>
+  <si>
+    <t>Kasım</t>
+  </si>
+  <si>
+    <t>Katılım</t>
+  </si>
+  <si>
+    <t>Katman</t>
+  </si>
+  <si>
+    <t>Katsayı</t>
+  </si>
+  <si>
+    <t>Kavram</t>
+  </si>
+  <si>
+    <t>Kazı</t>
+  </si>
+  <si>
+    <t>Kent</t>
+  </si>
+  <si>
+    <t>Kesenek</t>
+  </si>
+  <si>
+    <t>Kesin</t>
+  </si>
+  <si>
+    <t>Kesinti</t>
+  </si>
+  <si>
+    <t>Kesit</t>
+  </si>
+  <si>
+    <t>Kılcal</t>
+  </si>
+  <si>
+    <t>Kırsal</t>
+  </si>
+  <si>
+    <t>Kısır döngü</t>
+  </si>
+  <si>
+    <t>Kırım</t>
+  </si>
+  <si>
+    <t>Kısıntı</t>
+  </si>
+  <si>
+    <t>Kısıt</t>
+  </si>
+  <si>
+    <t>Kıvanç</t>
+  </si>
+  <si>
+    <t>Kıyım</t>
+  </si>
+  <si>
+    <t>Kimlik</t>
+  </si>
+  <si>
+    <t>Kimyasal</t>
+  </si>
+  <si>
+    <t>Kip</t>
+  </si>
+  <si>
+    <t>Kişilik</t>
+  </si>
+  <si>
+    <t>Kitlesel</t>
+  </si>
+  <si>
+    <t>Komut</t>
+  </si>
+  <si>
+    <t>Konu</t>
+  </si>
+  <si>
+    <t>Konuk</t>
+  </si>
+  <si>
+    <t>Konum</t>
+  </si>
+  <si>
+    <t>Konut</t>
+  </si>
+  <si>
+    <t>Korgeneral</t>
+  </si>
+  <si>
+    <t>Korumacı</t>
+  </si>
+  <si>
+    <t>Korunak</t>
+  </si>
+  <si>
+    <t>Koşuk</t>
+  </si>
+  <si>
+    <t>Koşul</t>
+  </si>
+  <si>
+    <t>Koşut</t>
+  </si>
+  <si>
+    <t>Kovuşturma</t>
+  </si>
+  <si>
+    <t>Kökenbilim (köken bilimi)</t>
+  </si>
+  <si>
+    <t>Köktenci</t>
+  </si>
+  <si>
+    <t>Köşe yazarı</t>
+  </si>
+  <si>
+    <t>Kötücül</t>
+  </si>
+  <si>
+    <t>Kötümser</t>
+  </si>
+  <si>
+    <t>Kullanım</t>
+  </si>
+  <si>
+    <t>Kumul</t>
+  </si>
+  <si>
+    <t>Kural</t>
+  </si>
+  <si>
+    <t>Kuram</t>
+  </si>
+  <si>
+    <t>Kurgu</t>
+  </si>
+  <si>
+    <t>Kurmay</t>
+  </si>
+  <si>
+    <t>Kurucular kurulu</t>
+  </si>
+  <si>
+    <t>Kurul</t>
+  </si>
+  <si>
+    <t>Kurultay</t>
+  </si>
+  <si>
+    <t>Kuruluş</t>
+  </si>
+  <si>
+    <t>Kurum</t>
+  </si>
+  <si>
+    <t>Kuşak</t>
+  </si>
+  <si>
+    <t>Kuşku</t>
+  </si>
+  <si>
+    <t>Kutlama</t>
+  </si>
+  <si>
+    <t>Kutsal</t>
+  </si>
+  <si>
+    <t>Kuzey</t>
+  </si>
+  <si>
+    <t>Kültür bakanı</t>
+  </si>
+  <si>
+    <t>Küresel</t>
+  </si>
+  <si>
+    <t>Maddesel</t>
+  </si>
+  <si>
+    <t>Madensel</t>
+  </si>
+  <si>
+    <t>Mal bildirimi</t>
+  </si>
+  <si>
+    <t>Mantıksal</t>
+  </si>
+  <si>
+    <t>Merkezî yönetim</t>
+  </si>
+  <si>
+    <t>Millî eğitim bakanı</t>
+  </si>
+  <si>
+    <t>Millî savunma bakanı</t>
+  </si>
+  <si>
+    <t>Mutlu azınlık</t>
+  </si>
+  <si>
+    <t>Mutsuz</t>
+  </si>
+  <si>
+    <t>Neden</t>
+  </si>
+  <si>
+    <t>Nesnel</t>
+  </si>
+  <si>
+    <t>Nicel</t>
+  </si>
+  <si>
+    <t>Nitel</t>
+  </si>
+  <si>
+    <t>Ocak</t>
+  </si>
+  <si>
+    <t>Odak</t>
+  </si>
+  <si>
+    <t>Okul</t>
+  </si>
+  <si>
+    <t>Okur</t>
+  </si>
+  <si>
+    <t>Olağan dışı</t>
+  </si>
+  <si>
+    <t>Olanak</t>
+  </si>
+  <si>
+    <t>Olası</t>
+  </si>
+  <si>
+    <t>Olay</t>
+  </si>
+  <si>
+    <t>Oldubitti</t>
+  </si>
+  <si>
+    <t>Olgu</t>
+  </si>
+  <si>
+    <t>Olumlu</t>
+  </si>
+  <si>
+    <t>Olumsuz</t>
+  </si>
+  <si>
+    <t>Olurluk</t>
+  </si>
+  <si>
+    <t>Oluş</t>
+  </si>
+  <si>
+    <t>Omur</t>
+  </si>
+  <si>
+    <t>Onama</t>
+  </si>
+  <si>
+    <t>Onarım</t>
+  </si>
+  <si>
+    <t>Onay</t>
+  </si>
+  <si>
+    <t>Onur</t>
+  </si>
+  <si>
+    <t>Oran</t>
+  </si>
+  <si>
+    <t>Organik ürün</t>
+  </si>
+  <si>
+    <t>Orgeneral</t>
+  </si>
+  <si>
+    <t>Orta çağ</t>
+  </si>
+  <si>
+    <t>Ortak payda</t>
+  </si>
+  <si>
+    <t>Ortam</t>
+  </si>
+  <si>
+    <t>Ortaokul</t>
+  </si>
+  <si>
+    <t>Oturum</t>
+  </si>
+  <si>
+    <t>Oy</t>
+  </si>
+  <si>
+    <t>Ozan</t>
+  </si>
+  <si>
+    <t>Ödenek</t>
+  </si>
+  <si>
+    <t>Ödev</t>
+  </si>
+  <si>
+    <t>Ödül</t>
+  </si>
+  <si>
+    <t>Ödün</t>
+  </si>
+  <si>
+    <t>Öge</t>
+  </si>
+  <si>
+    <t>Öğrenci</t>
+  </si>
+  <si>
+    <t>Öğrenim</t>
+  </si>
+  <si>
+    <t>Öğreti</t>
+  </si>
+  <si>
+    <t>Öğretmen</t>
+  </si>
+  <si>
+    <t>Ölçün</t>
+  </si>
+  <si>
+    <t>Öncel</t>
+  </si>
+  <si>
+    <t>Önder</t>
+  </si>
+  <si>
+    <t>Önem</t>
+  </si>
+  <si>
+    <t>Önerge</t>
+  </si>
+  <si>
+    <t>Öneri</t>
+  </si>
+  <si>
+    <t>Öngörü</t>
+  </si>
+  <si>
+    <t>Ön koşul</t>
+  </si>
+  <si>
+    <t>Önlem</t>
+  </si>
+  <si>
+    <t>Önsezi</t>
+  </si>
+  <si>
+    <t>Önsöz</t>
+  </si>
+  <si>
+    <t>Ön yargı</t>
+  </si>
+  <si>
+    <t>Ön yüzbaşı</t>
+  </si>
+  <si>
+    <t>Örgün</t>
+  </si>
+  <si>
+    <t>Örgüt</t>
+  </si>
+  <si>
+    <t>Örneklem</t>
+  </si>
+  <si>
+    <t>Örtmece</t>
+  </si>
+  <si>
+    <t>Örtülü ödenek</t>
+  </si>
+  <si>
+    <t>Örtüşmek</t>
+  </si>
+  <si>
+    <t>Öteleme, ötelenme</t>
+  </si>
+  <si>
+    <t>Övgü</t>
+  </si>
+  <si>
+    <t>Övünç</t>
+  </si>
+  <si>
+    <t>Öykü</t>
+  </si>
+  <si>
+    <t>Öz bağışıklık</t>
+  </si>
+  <si>
+    <t>Özdek</t>
+  </si>
+  <si>
+    <t>Öz denetim</t>
+  </si>
+  <si>
+    <t>Özdeş</t>
+  </si>
+  <si>
+    <t>Özdeyiş</t>
+  </si>
+  <si>
+    <t>Öz direnç</t>
+  </si>
+  <si>
+    <t>Özel</t>
+  </si>
+  <si>
+    <t>Özerk</t>
+  </si>
+  <si>
+    <t>Özet</t>
+  </si>
+  <si>
+    <t>Öz geçmiş</t>
+  </si>
+  <si>
+    <t>Özgül</t>
+  </si>
+  <si>
+    <t>Özgün</t>
+  </si>
+  <si>
+    <t>Özgür</t>
+  </si>
+  <si>
+    <t>Öz güven</t>
+  </si>
+  <si>
+    <t>Özlem</t>
+  </si>
+  <si>
+    <t>Özleştirmek</t>
+  </si>
+  <si>
+    <t>Özlük</t>
+  </si>
+  <si>
+    <t>Özne</t>
+  </si>
+  <si>
+    <t>Özsaygı</t>
+  </si>
+  <si>
+    <t>Özsu</t>
+  </si>
+  <si>
+    <t>Özümlemek</t>
+  </si>
+  <si>
+    <t>Özümsemek</t>
+  </si>
+  <si>
+    <t>Özüt</t>
+  </si>
+  <si>
+    <t>Özveri</t>
+  </si>
+  <si>
+    <t>Parasal</t>
+  </si>
+  <si>
+    <t>Payda</t>
+  </si>
+  <si>
+    <t>Pek önemli</t>
+  </si>
+  <si>
+    <t>Peşin yargı</t>
+  </si>
+  <si>
+    <t>Rastlantı</t>
+  </si>
+  <si>
+    <t>Resmî görev</t>
+  </si>
+  <si>
+    <t>Ruhbilim (ruh bilimi)</t>
+  </si>
+  <si>
+    <t>Sağduyu</t>
+  </si>
+  <si>
+    <t>Sağlık bakanı</t>
+  </si>
+  <si>
+    <t>Sakınca</t>
+  </si>
+  <si>
+    <t>Saldırgan</t>
+  </si>
+  <si>
+    <t>Salgı</t>
+  </si>
+  <si>
+    <t>Salınım</t>
+  </si>
+  <si>
+    <t>Saltçı</t>
+  </si>
+  <si>
+    <t>Sanal</t>
+  </si>
+  <si>
+    <t>Sanık</t>
+  </si>
+  <si>
+    <t>Saplantı</t>
+  </si>
+  <si>
+    <t>Saptamak</t>
+  </si>
+  <si>
+    <t>Sarkaç</t>
+  </si>
+  <si>
+    <t>Sarmal</t>
+  </si>
+  <si>
+    <t>Sav</t>
+  </si>
+  <si>
+    <t>Savaşım</t>
+  </si>
+  <si>
+    <t>Savcı</t>
+  </si>
+  <si>
+    <t>Savunma</t>
+  </si>
+  <si>
+    <t>Savurgan</t>
+  </si>
+  <si>
+    <t>Sayaç</t>
+  </si>
+  <si>
+    <t>Saydam</t>
+  </si>
+  <si>
+    <t>Saygın</t>
+  </si>
+  <si>
+    <t>Sayısal</t>
+  </si>
+  <si>
+    <t>Sayman</t>
+  </si>
+  <si>
+    <t>Sayrı</t>
+  </si>
+  <si>
+    <t>Seçenek</t>
+  </si>
+  <si>
+    <t>Seçici kurul</t>
+  </si>
+  <si>
+    <t>Seçim bölgesi</t>
+  </si>
+  <si>
+    <t>Seçki</t>
+  </si>
+  <si>
+    <t>Seçmen</t>
+  </si>
+  <si>
+    <t>Sekizgen</t>
+  </si>
+  <si>
+    <t>Serüven</t>
+  </si>
+  <si>
+    <t>Ses bilgisi</t>
+  </si>
+  <si>
+    <t>Sevecen</t>
+  </si>
+  <si>
+    <t>Sığınak</t>
+  </si>
+  <si>
+    <t>Sıkıyönetim</t>
+  </si>
+  <si>
+    <t>Sınav</t>
+  </si>
+  <si>
+    <t>Sınırlama</t>
+  </si>
+  <si>
+    <t>Sıvı</t>
+  </si>
+  <si>
+    <t>Simge</t>
+  </si>
+  <si>
+    <t>Sindirim</t>
+  </si>
+  <si>
+    <t>Sinirsel</t>
+  </si>
+  <si>
+    <t>Sivil savunma</t>
+  </si>
+  <si>
+    <t>Siyasa</t>
+  </si>
+  <si>
+    <t>Solunum</t>
+  </si>
+  <si>
+    <t>Somut</t>
+  </si>
+  <si>
+    <t>Sonuç</t>
+  </si>
+  <si>
+    <t>Sorgu hâkimi</t>
+  </si>
+  <si>
+    <t>Soru</t>
+  </si>
+  <si>
+    <t>Sorumlu</t>
+  </si>
+  <si>
+    <t>Sorun</t>
+  </si>
+  <si>
+    <t>Soya çekim</t>
+  </si>
+  <si>
+    <t>Soyut</t>
+  </si>
+  <si>
+    <t>Sömürge</t>
+  </si>
+  <si>
+    <t>Sövgü</t>
+  </si>
+  <si>
+    <t>Söylem</t>
+  </si>
+  <si>
+    <t>Söylence</t>
+  </si>
+  <si>
+    <t>Söyleşi</t>
+  </si>
+  <si>
+    <t>Söylev</t>
+  </si>
+  <si>
+    <t>Sözcük</t>
+  </si>
+  <si>
+    <t>Sözdizimi</t>
+  </si>
+  <si>
+    <t>Sözel</t>
+  </si>
+  <si>
+    <t>Söz konusu</t>
+  </si>
+  <si>
+    <t>Sözlük</t>
+  </si>
+  <si>
+    <t>Sözlü sınav</t>
+  </si>
+  <si>
+    <t>Söz yazarı</t>
+  </si>
+  <si>
+    <t>Söz yitimi</t>
+  </si>
+  <si>
+    <t>Subay</t>
+  </si>
+  <si>
+    <t>Sunak</t>
+  </si>
+  <si>
+    <t>Sunu</t>
+  </si>
+  <si>
+    <t>Su sayacı</t>
+  </si>
+  <si>
+    <t>Su ürünleri</t>
+  </si>
+  <si>
+    <t>Süre</t>
+  </si>
+  <si>
+    <t>Şekilbilim</t>
+  </si>
+  <si>
+    <t>Şiirsel</t>
+  </si>
+  <si>
+    <t>Takı</t>
+  </si>
+  <si>
+    <t>Takınak</t>
+  </si>
+  <si>
+    <t>Tanı</t>
+  </si>
+  <si>
+    <t>Tanım</t>
+  </si>
+  <si>
+    <t>Tanıt</t>
+  </si>
+  <si>
+    <t>Tanrıbilim</t>
+  </si>
+  <si>
+    <t>Tapınak</t>
+  </si>
+  <si>
+    <t>Tarım</t>
+  </si>
+  <si>
+    <t>Tarihsel</t>
+  </si>
+  <si>
+    <t>Tasarı</t>
+  </si>
+  <si>
+    <t>Taşıl</t>
+  </si>
+  <si>
+    <t>Taşım</t>
+  </si>
+  <si>
+    <t>Taşınmaz</t>
+  </si>
+  <si>
+    <t>Taşıt</t>
+  </si>
+  <si>
+    <t>Taşlama</t>
+  </si>
+  <si>
+    <t>Teğet</t>
+  </si>
+  <si>
+    <t>Teğmen</t>
+  </si>
+  <si>
+    <t>Tekdüze</t>
+  </si>
+  <si>
+    <t>Tekel</t>
+  </si>
+  <si>
+    <t>Tekil</t>
+  </si>
+  <si>
+    <t>Tensel</t>
+  </si>
+  <si>
+    <t>Tepki</t>
+  </si>
+  <si>
+    <t>Terim</t>
+  </si>
+  <si>
+    <t>Ters orantılı</t>
+  </si>
+  <si>
+    <t>Tini</t>
+  </si>
+  <si>
+    <t>Tikel</t>
+  </si>
+  <si>
+    <t>Tiksinti</t>
+  </si>
+  <si>
+    <t>Titreşim</t>
+  </si>
+  <si>
+    <t>Toplam</t>
+  </si>
+  <si>
+    <t>Toplum</t>
+  </si>
+  <si>
+    <t>Tortul</t>
+  </si>
+  <si>
+    <t>Tören</t>
+  </si>
+  <si>
+    <t>Tuğgeneral</t>
+  </si>
+  <si>
+    <t>Tutanak</t>
+  </si>
+  <si>
+    <t>Tutar</t>
+  </si>
+  <si>
+    <t>Tutku</t>
+  </si>
+  <si>
+    <t>Tutucu</t>
+  </si>
+  <si>
+    <t>Tutukevi</t>
+  </si>
+  <si>
+    <t>Tutum</t>
+  </si>
+  <si>
+    <t>Tüketim</t>
+  </si>
+  <si>
+    <t>Tüm</t>
+  </si>
+  <si>
+    <t>Tür</t>
+  </si>
+  <si>
+    <t>Tüze</t>
+  </si>
+  <si>
+    <t>Uçak</t>
+  </si>
+  <si>
+    <t>Uğraş</t>
+  </si>
+  <si>
+    <t>Ulaşım</t>
+  </si>
+  <si>
+    <t>Ulusal</t>
+  </si>
+  <si>
+    <t>Utku</t>
+  </si>
+  <si>
+    <t>Uyak</t>
+  </si>
+  <si>
+    <t>Uyarı</t>
+  </si>
+  <si>
+    <t>Uydu</t>
+  </si>
+  <si>
+    <t>Uygar</t>
+  </si>
+  <si>
+    <t>Uygulama</t>
+  </si>
+  <si>
+    <t>Uyruk</t>
+  </si>
+  <si>
+    <t>Uyum</t>
+  </si>
+  <si>
+    <t>Uzam</t>
+  </si>
+  <si>
+    <t>Uzman</t>
+  </si>
+  <si>
+    <t>Uzun süre</t>
+  </si>
+  <si>
+    <t>Üçgen</t>
+  </si>
+  <si>
+    <t>Ülkü</t>
+  </si>
+  <si>
+    <t>Ündeş</t>
+  </si>
+  <si>
+    <t>Ünlem</t>
+  </si>
+  <si>
+    <t>Ünlü</t>
+  </si>
+  <si>
+    <t>Ürem</t>
+  </si>
+  <si>
+    <t>Üretim</t>
+  </si>
+  <si>
+    <t>Ürkünç</t>
+  </si>
+  <si>
+    <t>Ürün</t>
+  </si>
+  <si>
+    <t>Üst düzey</t>
+  </si>
+  <si>
+    <t>Üsteğmen</t>
+  </si>
+  <si>
+    <t>Üst subay</t>
+  </si>
+  <si>
+    <t>Üye</t>
+  </si>
+  <si>
+    <t>Vargı</t>
+  </si>
+  <si>
+    <t>Varlıkbilim</t>
+  </si>
+  <si>
+    <t>Varsayım</t>
+  </si>
+  <si>
+    <t>Varsıl</t>
+  </si>
+  <si>
+    <t>Varoluşsal</t>
+  </si>
+  <si>
+    <t>Veri</t>
+  </si>
+  <si>
+    <t>Vicdan özgürlüğü</t>
+  </si>
+  <si>
+    <t>Vurgun</t>
+  </si>
+  <si>
+    <t>Yabanıl</t>
+  </si>
+  <si>
+    <t>Yadsımak</t>
+  </si>
+  <si>
+    <t>Yakıt</t>
+  </si>
+  <si>
+    <t>Yakınma</t>
+  </si>
+  <si>
+    <t>Yalıtım</t>
+  </si>
+  <si>
+    <t>Yanal</t>
+  </si>
+  <si>
+    <t>Yandaş</t>
+  </si>
+  <si>
+    <t>Yangı</t>
+  </si>
+  <si>
+    <t>Yanılgı</t>
+  </si>
+  <si>
+    <t>Yanıt</t>
+  </si>
+  <si>
+    <t>Yanlı</t>
+  </si>
+  <si>
+    <t>Yansı</t>
+  </si>
+  <si>
+    <t>Yan ürün</t>
+  </si>
+  <si>
+    <t>Yapay</t>
+  </si>
+  <si>
+    <t>Yapım</t>
+  </si>
+  <si>
+    <t>Yaptırım</t>
+  </si>
+  <si>
+    <t>Yarar</t>
+  </si>
+  <si>
+    <t>Yaratık</t>
+  </si>
+  <si>
+    <t>Yarbay</t>
+  </si>
+  <si>
+    <t>Yargı</t>
+  </si>
+  <si>
+    <t>Yasa</t>
+  </si>
+  <si>
+    <t>Yaşam</t>
+  </si>
+  <si>
+    <t>Yatay</t>
+  </si>
+  <si>
+    <t>Yatılı öğrenci</t>
+  </si>
+  <si>
+    <t>Yatırım</t>
+  </si>
+  <si>
+    <t>Yatıştırıcı</t>
+  </si>
+  <si>
+    <t>Yaygın</t>
+  </si>
+  <si>
+    <t>Yayım</t>
+  </si>
+  <si>
+    <t>Yazar</t>
+  </si>
+  <si>
+    <t>Yazgı</t>
+  </si>
+  <si>
+    <t>Yazılı sınav</t>
+  </si>
+  <si>
+    <t>Yazım</t>
+  </si>
+  <si>
+    <t>Yedek subay</t>
+  </si>
+  <si>
+    <t>Yeğlemek</t>
+  </si>
+  <si>
+    <t>Yemin töreni</t>
+  </si>
+  <si>
+    <t>Yeni çağ</t>
+  </si>
+  <si>
+    <t>Yenilgi</t>
+  </si>
+  <si>
+    <t>Yerbilim</t>
+  </si>
+  <si>
+    <t>Yerel</t>
+  </si>
+  <si>
+    <t>Yerey</t>
+  </si>
+  <si>
+    <t>Yergi</t>
+  </si>
+  <si>
+    <t>Yerindelik</t>
+  </si>
+  <si>
+    <t>Yerküre</t>
+  </si>
+  <si>
+    <t>Yerleşik</t>
+  </si>
+  <si>
+    <t>Yetenek</t>
+  </si>
+  <si>
+    <t>Yeterli</t>
+  </si>
+  <si>
+    <t>Yetki</t>
+  </si>
+  <si>
+    <t>Yetkin</t>
+  </si>
+  <si>
+    <t>Yetmezlik</t>
+  </si>
+  <si>
+    <t>Yıldırı</t>
+  </si>
+  <si>
+    <t>Yıldızbilim</t>
+  </si>
+  <si>
+    <t>Yıllık</t>
+  </si>
+  <si>
+    <t>Yinelemek</t>
+  </si>
+  <si>
+    <t>Yoğunlaşma</t>
+  </si>
+  <si>
+    <t>Yoğuşma</t>
+  </si>
+  <si>
+    <t>Yoksun</t>
+  </si>
+  <si>
+    <t>Yol yöntem</t>
+  </si>
+  <si>
+    <t>Yontu</t>
+  </si>
+  <si>
+    <t>Yorum</t>
+  </si>
+  <si>
+    <t>Yozlaşma</t>
+  </si>
+  <si>
+    <t>Yöndeş</t>
+  </si>
+  <si>
+    <t>Yönelik</t>
+  </si>
+  <si>
+    <t>Yönerge</t>
+  </si>
+  <si>
+    <t>Yönetim</t>
+  </si>
+  <si>
+    <t>Yöntem</t>
+  </si>
+  <si>
+    <t>Yöresel</t>
+  </si>
+  <si>
+    <t>Yörünge</t>
+  </si>
+  <si>
+    <t>Yurtsever</t>
+  </si>
+  <si>
+    <t>Yurttaş</t>
+  </si>
+  <si>
+    <t>Yüksekokul</t>
+  </si>
+  <si>
+    <t>Yükselti</t>
+  </si>
+  <si>
+    <t>Yüküm</t>
+  </si>
+  <si>
+    <t>Yürürlük</t>
+  </si>
+  <si>
+    <t>Yüzey</t>
+  </si>
+  <si>
+    <t>Yüzölçümü (yüz ölçümü)</t>
+  </si>
+  <si>
+    <t>Zaman aşımı</t>
+  </si>
+  <si>
+    <t>Zihinsel</t>
+  </si>
+  <si>
+    <t>Zoralım</t>
+  </si>
+  <si>
+    <t>Zorunlu</t>
+  </si>
+  <si>
+    <t>Aile bireyleri</t>
   </si>
 </sst>
 </file>
@@ -163,7 +2524,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -173,10 +2534,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,11 +2871,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{984A1489-2204-4320-8C2B-598D19BA0E68}">
-  <dimension ref="A1:H337"/>
+  <dimension ref="A1:H791"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.88671875" customWidth="1"/>
-    <col min="2" max="2" width="32" style="6" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="33.88671875" style="3" customWidth="1"/>
     <col min="4" max="4" width="35.5546875" style="3" customWidth="1"/>
     <col min="5" max="5" width="31.33203125" style="3" customWidth="1"/>
@@ -553,10 +2913,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
@@ -570,1033 +2930,3988 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="13.8" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>806</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="2"/>
+      <c r="A27" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="2"/>
+      <c r="A28" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="2"/>
+      <c r="A33" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="2"/>
+      <c r="A34" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="2"/>
+      <c r="A35" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="2"/>
+      <c r="A36" s="2" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="2"/>
+      <c r="A37" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="2"/>
+      <c r="A38" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="2"/>
+      <c r="A39" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="2"/>
+      <c r="A40" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="2"/>
+      <c r="A41" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="2"/>
+      <c r="A42" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="2"/>
+      <c r="A43" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="2"/>
+      <c r="A44" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="2"/>
+      <c r="A45" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="2"/>
+      <c r="A46" s="2" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="2"/>
+      <c r="A47" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="2"/>
+      <c r="A49" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="2"/>
+      <c r="A50" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="2"/>
+      <c r="A51" s="2" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="2"/>
+      <c r="A52" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="2"/>
+      <c r="A53" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="2"/>
+      <c r="A54" s="2" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="2"/>
+      <c r="A55" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="2"/>
+      <c r="A56" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="2"/>
+      <c r="A57" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="2"/>
+      <c r="A58" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="2"/>
+      <c r="A59" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="2"/>
+      <c r="A60" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="2"/>
+      <c r="A61" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="2"/>
+      <c r="A62" s="2" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="2"/>
+      <c r="A63" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="2"/>
+      <c r="A64" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="2"/>
+      <c r="A65" s="2" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="2"/>
+      <c r="A66" s="2" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="2"/>
+      <c r="A67" s="2" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="2"/>
+      <c r="A68" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="2"/>
+      <c r="A69" s="2" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="2"/>
+      <c r="A70" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="2"/>
+      <c r="A71" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="2"/>
+      <c r="A72" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="2"/>
+      <c r="A73" s="2" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="2"/>
+      <c r="A74" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="2"/>
+      <c r="A75" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="2"/>
+      <c r="A76" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="2"/>
+      <c r="A77" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="2"/>
+      <c r="A78" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="2"/>
+      <c r="A79" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="2"/>
+      <c r="A80" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="2"/>
+      <c r="A81" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="2"/>
+      <c r="A82" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="2"/>
+      <c r="A83" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="2"/>
+      <c r="A84" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="2"/>
+      <c r="A85" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="2"/>
+      <c r="A86" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="2"/>
+      <c r="A87" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="2"/>
+      <c r="A88" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="2"/>
+      <c r="A89" s="2" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="2"/>
+      <c r="A90" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="2"/>
+      <c r="A91" s="2" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="2"/>
+      <c r="A92" s="2" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="2"/>
+      <c r="A93" s="2" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="2"/>
+      <c r="A94" s="2" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="2"/>
+      <c r="A95" s="2" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="2"/>
+      <c r="A96" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="2"/>
+      <c r="A97" s="2" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="2"/>
+      <c r="A98" s="2" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="2"/>
+      <c r="A99" s="2" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="2"/>
+      <c r="A100" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="2"/>
+      <c r="A101" s="2" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="2"/>
+      <c r="A102" s="2" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="2"/>
+      <c r="A103" s="2" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="2"/>
+      <c r="A104" s="2" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" s="2"/>
+      <c r="A105" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="2"/>
+      <c r="A106" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="2"/>
+      <c r="A107" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" s="2"/>
+      <c r="A108" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" s="2"/>
+      <c r="A109" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" s="2"/>
+      <c r="A110" s="2" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="2"/>
+      <c r="A111" s="2" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="112" spans="1:1">
-      <c r="A112" s="2"/>
+      <c r="A112" s="2" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="2"/>
+      <c r="A113" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="114" spans="1:1">
-      <c r="A114" s="2"/>
+      <c r="A114" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="2"/>
+      <c r="A115" s="2" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="116" spans="1:1">
-      <c r="A116" s="2"/>
+      <c r="A116" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="117" spans="1:1">
-      <c r="A117" s="2"/>
+      <c r="A117" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="118" spans="1:1">
-      <c r="A118" s="2"/>
+      <c r="A118" s="2" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="119" spans="1:1">
-      <c r="A119" s="2"/>
+      <c r="A119" s="2" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="120" spans="1:1">
-      <c r="A120" s="2"/>
+      <c r="A120" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="121" spans="1:1">
-      <c r="A121" s="2"/>
+      <c r="A121" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="122" spans="1:1">
-      <c r="A122" s="2"/>
+      <c r="A122" s="2" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="123" spans="1:1">
-      <c r="A123" s="2"/>
+      <c r="A123" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="124" spans="1:1">
-      <c r="A124" s="2"/>
+      <c r="A124" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="125" spans="1:1">
-      <c r="A125" s="2"/>
+      <c r="A125" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="126" spans="1:1">
-      <c r="A126" s="2"/>
+      <c r="A126" s="2" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="2"/>
+      <c r="A127" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="128" spans="1:1">
-      <c r="A128" s="2"/>
+      <c r="A128" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="2"/>
+      <c r="A129" s="2" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="2"/>
+      <c r="A130" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="2"/>
+      <c r="A131" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="2"/>
+      <c r="A132" s="2" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="2"/>
+      <c r="A133" s="2" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="134" spans="1:1">
-      <c r="A134" s="2"/>
+      <c r="A134" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="135" spans="1:1">
-      <c r="A135" s="2"/>
+      <c r="A135" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="2"/>
+      <c r="A136" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="2"/>
+      <c r="A137" s="2" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="2"/>
+      <c r="A138" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="2"/>
+      <c r="A139" s="2" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="2"/>
+      <c r="A140" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="2"/>
+      <c r="A141" s="2" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="2"/>
+      <c r="A142" s="2" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="2"/>
+      <c r="A143" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="2"/>
+      <c r="A144" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="145" spans="1:1">
-      <c r="A145" s="2"/>
+      <c r="A145" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="146" spans="1:1">
-      <c r="A146" s="2"/>
+      <c r="A146" s="2" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="2"/>
+      <c r="A147" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="148" spans="1:1">
-      <c r="A148" s="2"/>
+      <c r="A148" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="2"/>
+      <c r="A149" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="150" spans="1:1">
-      <c r="A150" s="2"/>
+      <c r="A150" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="2"/>
+      <c r="A151" s="2" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="152" spans="1:1">
-      <c r="A152" s="2"/>
+      <c r="A152" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="2"/>
+      <c r="A153" s="2" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="154" spans="1:1">
-      <c r="A154" s="2"/>
+      <c r="A154" s="2" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="2"/>
+      <c r="A155" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="156" spans="1:1">
-      <c r="A156" s="2"/>
+      <c r="A156" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="2"/>
+      <c r="A157" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="158" spans="1:1">
-      <c r="A158" s="2"/>
+      <c r="A158" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="2"/>
+      <c r="A159" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="160" spans="1:1">
-      <c r="A160" s="2"/>
+      <c r="A160" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="161" spans="1:1">
-      <c r="A161" s="2"/>
+      <c r="A161" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="2"/>
+      <c r="A162" s="2" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="2"/>
+      <c r="A163" s="2" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="164" spans="1:1">
-      <c r="A164" s="2"/>
+      <c r="A164" s="2" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="2"/>
+      <c r="A165" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="166" spans="1:1">
-      <c r="A166" s="2"/>
+      <c r="A166" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="2"/>
+      <c r="A167" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="168" spans="1:1">
-      <c r="A168" s="2"/>
+      <c r="A168" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="2"/>
+      <c r="A169" s="2" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="170" spans="1:1">
-      <c r="A170" s="2"/>
+      <c r="A170" s="2" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="171" spans="1:1">
-      <c r="A171" s="2"/>
+      <c r="A171" s="2" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="172" spans="1:1">
-      <c r="A172" s="2"/>
+      <c r="A172" s="2" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="173" spans="1:1">
-      <c r="A173" s="2"/>
+      <c r="A173" s="2" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="174" spans="1:1">
-      <c r="A174" s="2"/>
+      <c r="A174" s="2" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="175" spans="1:1">
-      <c r="A175" s="2"/>
+      <c r="A175" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="176" spans="1:1">
-      <c r="A176" s="2"/>
+      <c r="A176" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="177" spans="1:1">
-      <c r="A177" s="2"/>
+      <c r="A177" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="178" spans="1:1">
-      <c r="A178" s="2"/>
+      <c r="A178" s="2" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="179" spans="1:1">
-      <c r="A179" s="2"/>
+      <c r="A179" s="2" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="180" spans="1:1">
-      <c r="A180" s="2"/>
+      <c r="A180" s="2" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="181" spans="1:1">
-      <c r="A181" s="2"/>
+      <c r="A181" s="2" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="182" spans="1:1">
-      <c r="A182" s="2"/>
+      <c r="A182" s="2" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="183" spans="1:1">
-      <c r="A183" s="2"/>
+      <c r="A183" s="2" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="184" spans="1:1">
-      <c r="A184" s="2"/>
+      <c r="A184" s="2" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="185" spans="1:1">
-      <c r="A185" s="2"/>
+      <c r="A185" s="2" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="186" spans="1:1">
-      <c r="A186" s="2"/>
+      <c r="A186" s="2" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="187" spans="1:1">
-      <c r="A187" s="2"/>
+      <c r="A187" s="2" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="188" spans="1:1">
-      <c r="A188" s="2"/>
+      <c r="A188" s="2" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="189" spans="1:1">
-      <c r="A189" s="2"/>
+      <c r="A189" s="2" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="190" spans="1:1">
-      <c r="A190" s="2"/>
+      <c r="A190" s="2" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="191" spans="1:1">
-      <c r="A191" s="2"/>
+      <c r="A191" s="2" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="192" spans="1:1">
-      <c r="A192" s="2"/>
+      <c r="A192" s="2" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="193" spans="1:1">
-      <c r="A193" s="2"/>
+      <c r="A193" s="2" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="194" spans="1:1">
-      <c r="A194" s="2"/>
+      <c r="A194" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="195" spans="1:1">
-      <c r="A195" s="2"/>
+      <c r="A195" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="196" spans="1:1">
-      <c r="A196" s="2"/>
+      <c r="A196" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="197" spans="1:1">
-      <c r="A197" s="2"/>
+      <c r="A197" s="2" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="198" spans="1:1">
-      <c r="A198" s="2"/>
+      <c r="A198" s="2" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="199" spans="1:1">
-      <c r="A199" s="2"/>
+      <c r="A199" s="2" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="200" spans="1:1">
-      <c r="A200" s="2"/>
+      <c r="A200" s="2" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="201" spans="1:1">
-      <c r="A201" s="2"/>
+      <c r="A201" s="2" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="202" spans="1:1">
-      <c r="A202" s="2"/>
+      <c r="A202" s="2" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="203" spans="1:1">
-      <c r="A203" s="2"/>
+      <c r="A203" s="2" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="204" spans="1:1">
-      <c r="A204" s="2"/>
+      <c r="A204" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="205" spans="1:1">
-      <c r="A205" s="2"/>
+      <c r="A205" s="2" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="206" spans="1:1">
-      <c r="A206" s="2"/>
+      <c r="A206" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="207" spans="1:1">
-      <c r="A207" s="2"/>
+      <c r="A207" s="2" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="208" spans="1:1">
-      <c r="A208" s="2"/>
+      <c r="A208" s="2" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="209" spans="1:1">
-      <c r="A209" s="2"/>
+      <c r="A209" s="2" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="210" spans="1:1">
-      <c r="A210" s="2"/>
+      <c r="A210" s="2" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="211" spans="1:1">
-      <c r="A211" s="2"/>
+      <c r="A211" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="212" spans="1:1">
-      <c r="A212" s="2"/>
+      <c r="A212" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="213" spans="1:1">
-      <c r="A213" s="2"/>
+      <c r="A213" s="2" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="214" spans="1:1">
-      <c r="A214" s="2"/>
+      <c r="A214" s="2" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="215" spans="1:1">
-      <c r="A215" s="2"/>
+      <c r="A215" s="2" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="216" spans="1:1">
-      <c r="A216" s="2"/>
+      <c r="A216" s="2" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="217" spans="1:1">
-      <c r="A217" s="2"/>
+      <c r="A217" s="2" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="218" spans="1:1">
-      <c r="A218" s="2"/>
+      <c r="A218" s="2" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="219" spans="1:1">
-      <c r="A219" s="2"/>
+      <c r="A219" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="220" spans="1:1">
-      <c r="A220" s="2"/>
+      <c r="A220" s="2" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="221" spans="1:1">
-      <c r="A221" s="2"/>
+      <c r="A221" s="2" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="222" spans="1:1">
-      <c r="A222" s="2"/>
+      <c r="A222" s="2" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="223" spans="1:1">
-      <c r="A223" s="2"/>
+      <c r="A223" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="224" spans="1:1">
-      <c r="A224" s="2"/>
+      <c r="A224" s="2" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="225" spans="1:1">
-      <c r="A225" s="2"/>
+      <c r="A225" s="2" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="226" spans="1:1">
-      <c r="A226" s="2"/>
+      <c r="A226" s="2" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="227" spans="1:1">
-      <c r="A227" s="2"/>
+      <c r="A227" s="2" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="228" spans="1:1">
-      <c r="A228" s="2"/>
+      <c r="A228" s="2" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="229" spans="1:1">
-      <c r="A229" s="2"/>
+      <c r="A229" s="2" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="230" spans="1:1">
-      <c r="A230" s="2"/>
+      <c r="A230" s="2" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="231" spans="1:1">
-      <c r="A231" s="2"/>
+      <c r="A231" s="2" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="232" spans="1:1">
-      <c r="A232" s="2"/>
+      <c r="A232" s="2" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="233" spans="1:1">
-      <c r="A233" s="2"/>
+      <c r="A233" s="2" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="234" spans="1:1">
-      <c r="A234" s="2"/>
+      <c r="A234" s="2" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="235" spans="1:1">
-      <c r="A235" s="2"/>
+      <c r="A235" s="2" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="236" spans="1:1">
-      <c r="A236" s="2"/>
+      <c r="A236" s="2" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="237" spans="1:1">
-      <c r="A237" s="2"/>
+      <c r="A237" s="2" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="238" spans="1:1">
-      <c r="A238" s="2"/>
+      <c r="A238" s="2" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="239" spans="1:1">
-      <c r="A239" s="2"/>
+      <c r="A239" s="2" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="240" spans="1:1">
-      <c r="A240" s="2"/>
+      <c r="A240" s="2" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="241" spans="1:1">
-      <c r="A241" s="2"/>
+      <c r="A241" s="2" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="242" spans="1:1">
-      <c r="A242" s="2"/>
+      <c r="A242" s="2" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="243" spans="1:1">
-      <c r="A243" s="2"/>
+      <c r="A243" s="2" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="244" spans="1:1">
-      <c r="A244" s="2"/>
+      <c r="A244" s="2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="245" spans="1:1">
-      <c r="A245" s="2"/>
+      <c r="A245" s="2" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="246" spans="1:1">
-      <c r="A246" s="2"/>
+      <c r="A246" s="2" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="247" spans="1:1">
-      <c r="A247" s="2"/>
+      <c r="A247" s="2" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="248" spans="1:1">
-      <c r="A248" s="2"/>
+      <c r="A248" s="2" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="249" spans="1:1">
-      <c r="A249" s="2"/>
+      <c r="A249" s="2" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="250" spans="1:1">
-      <c r="A250" s="2"/>
+      <c r="A250" s="2" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="251" spans="1:1">
-      <c r="A251" s="2"/>
+      <c r="A251" s="2" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="252" spans="1:1">
-      <c r="A252" s="2"/>
+      <c r="A252" s="2" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="253" spans="1:1">
-      <c r="A253" s="2"/>
+      <c r="A253" s="2" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="254" spans="1:1">
-      <c r="A254" s="2"/>
+      <c r="A254" s="2" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="255" spans="1:1">
-      <c r="A255" s="2"/>
+      <c r="A255" s="2" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="256" spans="1:1">
-      <c r="A256" s="2"/>
+      <c r="A256" s="2" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="257" spans="1:1">
-      <c r="A257" s="2"/>
+      <c r="A257" s="2" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="258" spans="1:1">
-      <c r="A258" s="2"/>
+      <c r="A258" s="2" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="259" spans="1:1">
-      <c r="A259" s="2"/>
+      <c r="A259" s="2" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="260" spans="1:1">
-      <c r="A260" s="2"/>
+      <c r="A260" s="2" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="261" spans="1:1">
-      <c r="A261" s="2"/>
+      <c r="A261" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="262" spans="1:1">
-      <c r="A262" s="2"/>
+      <c r="A262" s="2" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="263" spans="1:1">
-      <c r="A263" s="2"/>
+      <c r="A263" s="2" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="264" spans="1:1">
-      <c r="A264" s="2"/>
+      <c r="A264" s="2" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="265" spans="1:1">
-      <c r="A265" s="2"/>
+      <c r="A265" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="266" spans="1:1">
-      <c r="A266" s="2"/>
+      <c r="A266" s="2" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="267" spans="1:1">
-      <c r="A267" s="2"/>
+      <c r="A267" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="268" spans="1:1">
-      <c r="A268" s="2"/>
+      <c r="A268" s="2" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="269" spans="1:1">
-      <c r="A269" s="2"/>
+      <c r="A269" s="2" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="270" spans="1:1">
-      <c r="A270" s="2"/>
+      <c r="A270" s="2" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="271" spans="1:1">
-      <c r="A271" s="2"/>
+      <c r="A271" s="2" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="272" spans="1:1">
-      <c r="A272" s="2"/>
+      <c r="A272" s="2" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="273" spans="1:1">
-      <c r="A273" s="2"/>
+      <c r="A273" s="2" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="274" spans="1:1">
-      <c r="A274" s="2"/>
+      <c r="A274" s="2" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="275" spans="1:1">
-      <c r="A275" s="2"/>
+      <c r="A275" s="2" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="276" spans="1:1">
-      <c r="A276" s="2"/>
+      <c r="A276" s="2" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="277" spans="1:1">
-      <c r="A277" s="2"/>
+      <c r="A277" s="2" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="278" spans="1:1">
-      <c r="A278" s="2"/>
+      <c r="A278" s="2" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="279" spans="1:1">
-      <c r="A279" s="2"/>
+      <c r="A279" s="2" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="280" spans="1:1">
-      <c r="A280" s="2"/>
+      <c r="A280" s="2" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="281" spans="1:1">
-      <c r="A281" s="2"/>
+      <c r="A281" s="2" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="282" spans="1:1">
-      <c r="A282" s="2"/>
+      <c r="A282" s="2" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="283" spans="1:1">
-      <c r="A283" s="2"/>
+      <c r="A283" s="2" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="284" spans="1:1">
-      <c r="A284" s="2"/>
+      <c r="A284" s="2" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="285" spans="1:1">
-      <c r="A285" s="2"/>
+      <c r="A285" s="2" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="286" spans="1:1">
-      <c r="A286" s="2"/>
+      <c r="A286" s="2" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="287" spans="1:1">
-      <c r="A287" s="2"/>
+      <c r="A287" s="2" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="288" spans="1:1">
-      <c r="A288" s="2"/>
+      <c r="A288" s="2" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="289" spans="1:1">
-      <c r="A289" s="2"/>
+      <c r="A289" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="290" spans="1:1">
-      <c r="A290" s="2"/>
+      <c r="A290" s="2" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="291" spans="1:1">
-      <c r="A291" s="2"/>
+      <c r="A291" s="2" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="292" spans="1:1">
-      <c r="A292" s="2"/>
+      <c r="A292" s="2" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="293" spans="1:1">
-      <c r="A293" s="2"/>
+      <c r="A293" s="2" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="294" spans="1:1">
-      <c r="A294" s="2"/>
+      <c r="A294" s="2" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="295" spans="1:1">
-      <c r="A295" s="2"/>
+      <c r="A295" s="2" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="296" spans="1:1">
-      <c r="A296" s="2"/>
+      <c r="A296" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="297" spans="1:1">
-      <c r="A297" s="2"/>
+      <c r="A297" s="2" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="298" spans="1:1">
-      <c r="A298" s="2"/>
+      <c r="A298" s="2" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="299" spans="1:1">
-      <c r="A299" s="2"/>
+      <c r="A299" s="2" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="300" spans="1:1">
-      <c r="A300" s="2"/>
+      <c r="A300" s="2" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="301" spans="1:1">
-      <c r="A301" s="2"/>
+      <c r="A301" s="2" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="302" spans="1:1">
-      <c r="A302" s="2"/>
+      <c r="A302" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="303" spans="1:1">
-      <c r="A303" s="2"/>
+      <c r="A303" s="2" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="304" spans="1:1">
-      <c r="A304" s="2"/>
+      <c r="A304" s="2" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="305" spans="1:1">
-      <c r="A305" s="2"/>
+      <c r="A305" s="2" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="306" spans="1:1">
-      <c r="A306" s="2"/>
+      <c r="A306" s="2" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="307" spans="1:1">
-      <c r="A307" s="2"/>
+      <c r="A307" s="2" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="308" spans="1:1">
-      <c r="A308" s="2"/>
+      <c r="A308" s="2" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="309" spans="1:1">
-      <c r="A309" s="2"/>
+      <c r="A309" s="2" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="310" spans="1:1">
-      <c r="A310" s="2"/>
+      <c r="A310" s="2" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="311" spans="1:1">
-      <c r="A311" s="2"/>
+      <c r="A311" s="2" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="312" spans="1:1">
-      <c r="A312" s="2"/>
+      <c r="A312" s="2" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="313" spans="1:1">
-      <c r="A313" s="2"/>
+      <c r="A313" s="2" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="314" spans="1:1">
-      <c r="A314" s="2"/>
+      <c r="A314" s="2" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="315" spans="1:1">
-      <c r="A315" s="2"/>
+      <c r="A315" s="2" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="316" spans="1:1">
-      <c r="A316" s="2"/>
+      <c r="A316" s="2" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="317" spans="1:1">
-      <c r="A317" s="2"/>
+      <c r="A317" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="318" spans="1:1">
-      <c r="A318" s="2"/>
+      <c r="A318" s="2" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="319" spans="1:1">
-      <c r="A319" s="2"/>
+      <c r="A319" s="2" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="320" spans="1:1">
-      <c r="A320" s="2"/>
+      <c r="A320" s="2" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="321" spans="1:1">
-      <c r="A321" s="2"/>
+      <c r="A321" s="2" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="322" spans="1:1">
-      <c r="A322" s="2"/>
+      <c r="A322" s="2" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="323" spans="1:1">
-      <c r="A323" s="2"/>
+      <c r="A323" s="2" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="324" spans="1:1">
-      <c r="A324" s="2"/>
+      <c r="A324" s="2" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="325" spans="1:1">
-      <c r="A325" s="2"/>
+      <c r="A325" s="2" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="326" spans="1:1">
-      <c r="A326" s="2"/>
+      <c r="A326" s="2" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="327" spans="1:1">
-      <c r="A327" s="2"/>
+      <c r="A327" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="328" spans="1:1">
-      <c r="A328" s="2"/>
+      <c r="A328" s="2" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="329" spans="1:1">
-      <c r="A329" s="2"/>
+      <c r="A329" s="2" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="330" spans="1:1">
-      <c r="A330" s="2"/>
+      <c r="A330" s="2" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="331" spans="1:1">
-      <c r="A331" s="2"/>
+      <c r="A331" s="2" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="332" spans="1:1">
-      <c r="A332" s="2"/>
+      <c r="A332" s="2" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="333" spans="1:1">
-      <c r="A333" s="2"/>
+      <c r="A333" s="2" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="334" spans="1:1">
-      <c r="A334" s="2"/>
+      <c r="A334" s="2" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="335" spans="1:1">
-      <c r="A335" s="2"/>
+      <c r="A335" s="2" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="336" spans="1:1">
-      <c r="A336" s="2"/>
+      <c r="A336" s="2" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="337" spans="1:1">
-      <c r="A337" s="2"/>
+      <c r="A337" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1">
+      <c r="A481" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1">
+      <c r="A482" s="2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1">
+      <c r="A483" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1">
+      <c r="A484" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1">
+      <c r="A485" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1">
+      <c r="A486" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1">
+      <c r="A487" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1">
+      <c r="A488" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1">
+      <c r="A489" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1">
+      <c r="A490" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1">
+      <c r="A491" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1">
+      <c r="A492" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1">
+      <c r="A493" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1">
+      <c r="A494" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1">
+      <c r="A495" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="496" spans="1:1">
+      <c r="A496" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="497" spans="1:1">
+      <c r="A497" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="498" spans="1:1">
+      <c r="A498" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="499" spans="1:1">
+      <c r="A499" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="500" spans="1:1">
+      <c r="A500" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="501" spans="1:1">
+      <c r="A501" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="502" spans="1:1">
+      <c r="A502" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="503" spans="1:1">
+      <c r="A503" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="504" spans="1:1">
+      <c r="A504" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="505" spans="1:1">
+      <c r="A505" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="506" spans="1:1">
+      <c r="A506" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="507" spans="1:1">
+      <c r="A507" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="508" spans="1:1">
+      <c r="A508" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="509" spans="1:1">
+      <c r="A509" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="510" spans="1:1">
+      <c r="A510" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="511" spans="1:1">
+      <c r="A511" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1">
+      <c r="A512" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1">
+      <c r="A513" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1">
+      <c r="A514" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1">
+      <c r="A515" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1">
+      <c r="A516" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="517" spans="1:1">
+      <c r="A517" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="518" spans="1:1">
+      <c r="A518" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="519" spans="1:1">
+      <c r="A519" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1">
+      <c r="A520" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1">
+      <c r="A521" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1">
+      <c r="A522" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1">
+      <c r="A523" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1">
+      <c r="A524" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1">
+      <c r="A525" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1">
+      <c r="A526" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1">
+      <c r="A527" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1">
+      <c r="A528" s="2" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1">
+      <c r="A529" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1">
+      <c r="A530" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1">
+      <c r="A531" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1">
+      <c r="A532" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1">
+      <c r="A533" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1">
+      <c r="A534" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1">
+      <c r="A535" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1">
+      <c r="A536" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1">
+      <c r="A537" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1">
+      <c r="A538" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1">
+      <c r="A539" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1">
+      <c r="A540" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1">
+      <c r="A541" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1">
+      <c r="A542" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1">
+      <c r="A543" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1">
+      <c r="A544" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1">
+      <c r="A545" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1">
+      <c r="A546" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1">
+      <c r="A547" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1">
+      <c r="A548" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1">
+      <c r="A549" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1">
+      <c r="A550" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1">
+      <c r="A551" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1">
+      <c r="A552" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1">
+      <c r="A553" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1">
+      <c r="A554" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1">
+      <c r="A555" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1">
+      <c r="A556" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1">
+      <c r="A557" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1">
+      <c r="A558" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1">
+      <c r="A559" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1">
+      <c r="A560" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1">
+      <c r="A561" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1">
+      <c r="A562" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1">
+      <c r="A563" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1">
+      <c r="A564" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1">
+      <c r="A565" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1">
+      <c r="A566" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1">
+      <c r="A567" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1">
+      <c r="A568" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1">
+      <c r="A569" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1">
+      <c r="A570" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1">
+      <c r="A571" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1">
+      <c r="A572" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1">
+      <c r="A573" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1">
+      <c r="A574" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1">
+      <c r="A575" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1">
+      <c r="A576" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1">
+      <c r="A577" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1">
+      <c r="A578" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1">
+      <c r="A579" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1">
+      <c r="A580" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1">
+      <c r="A581" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1">
+      <c r="A582" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1">
+      <c r="A583" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1">
+      <c r="A584" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1">
+      <c r="A585" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1">
+      <c r="A586" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1">
+      <c r="A587" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1">
+      <c r="A588" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1">
+      <c r="A589" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1">
+      <c r="A590" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1">
+      <c r="A591" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1">
+      <c r="A592" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1">
+      <c r="A593" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1">
+      <c r="A594" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1">
+      <c r="A595" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1">
+      <c r="A596" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1">
+      <c r="A597" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1">
+      <c r="A598" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1">
+      <c r="A599" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1">
+      <c r="A600" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1">
+      <c r="A601" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1">
+      <c r="A602" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1">
+      <c r="A603" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1">
+      <c r="A604" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1">
+      <c r="A605" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1">
+      <c r="A606" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1">
+      <c r="A607" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1">
+      <c r="A608" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1">
+      <c r="A609" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1">
+      <c r="A610" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1">
+      <c r="A611" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1">
+      <c r="A612" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1">
+      <c r="A613" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1">
+      <c r="A614" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1">
+      <c r="A615" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1">
+      <c r="A616" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1">
+      <c r="A617" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1">
+      <c r="A618" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1">
+      <c r="A619" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1">
+      <c r="A620" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1">
+      <c r="A621" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1">
+      <c r="A622" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1">
+      <c r="A623" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1">
+      <c r="A624" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1">
+      <c r="A625" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1">
+      <c r="A626" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1">
+      <c r="A627" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1">
+      <c r="A628" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1">
+      <c r="A629" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1">
+      <c r="A630" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1">
+      <c r="A631" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1">
+      <c r="A632" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1">
+      <c r="A633" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1">
+      <c r="A634" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="635" spans="1:1">
+      <c r="A635" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1">
+      <c r="A636" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1">
+      <c r="A637" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1">
+      <c r="A638" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1">
+      <c r="A639" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1">
+      <c r="A640" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1">
+      <c r="A641" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1">
+      <c r="A642" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1">
+      <c r="A643" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1">
+      <c r="A644" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1">
+      <c r="A645" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1">
+      <c r="A646" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1">
+      <c r="A647" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1">
+      <c r="A648" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1">
+      <c r="A649" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1">
+      <c r="A650" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1">
+      <c r="A651" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1">
+      <c r="A652" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="653" spans="1:1">
+      <c r="A653" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1">
+      <c r="A654" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1">
+      <c r="A655" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1">
+      <c r="A656" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1">
+      <c r="A657" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1">
+      <c r="A658" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="659" spans="1:1">
+      <c r="A659" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1">
+      <c r="A660" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1">
+      <c r="A661" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1">
+      <c r="A662" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1">
+      <c r="A663" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1">
+      <c r="A664" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="665" spans="1:1">
+      <c r="A665" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1">
+      <c r="A666" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="667" spans="1:1">
+      <c r="A667" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="668" spans="1:1">
+      <c r="A668" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="669" spans="1:1">
+      <c r="A669" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="670" spans="1:1">
+      <c r="A670" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="671" spans="1:1">
+      <c r="A671" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="672" spans="1:1">
+      <c r="A672" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="673" spans="1:1">
+      <c r="A673" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="674" spans="1:1">
+      <c r="A674" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="675" spans="1:1">
+      <c r="A675" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="676" spans="1:1">
+      <c r="A676" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="677" spans="1:1">
+      <c r="A677" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="678" spans="1:1">
+      <c r="A678" s="2" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="679" spans="1:1">
+      <c r="A679" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="680" spans="1:1">
+      <c r="A680" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="681" spans="1:1">
+      <c r="A681" s="2" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="682" spans="1:1">
+      <c r="A682" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="683" spans="1:1">
+      <c r="A683" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="684" spans="1:1">
+      <c r="A684" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="685" spans="1:1">
+      <c r="A685" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="686" spans="1:1">
+      <c r="A686" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="687" spans="1:1">
+      <c r="A687" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="688" spans="1:1">
+      <c r="A688" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="689" spans="1:1">
+      <c r="A689" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="690" spans="1:1">
+      <c r="A690" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="691" spans="1:1">
+      <c r="A691" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="692" spans="1:1">
+      <c r="A692" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="693" spans="1:1">
+      <c r="A693" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="694" spans="1:1">
+      <c r="A694" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="695" spans="1:1">
+      <c r="A695" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="696" spans="1:1">
+      <c r="A696" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="697" spans="1:1">
+      <c r="A697" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="698" spans="1:1">
+      <c r="A698" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="699" spans="1:1">
+      <c r="A699" s="2" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="700" spans="1:1">
+      <c r="A700" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="701" spans="1:1">
+      <c r="A701" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="702" spans="1:1">
+      <c r="A702" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="703" spans="1:1">
+      <c r="A703" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="704" spans="1:1">
+      <c r="A704" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="705" spans="1:1">
+      <c r="A705" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="706" spans="1:1">
+      <c r="A706" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="707" spans="1:1">
+      <c r="A707" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="708" spans="1:1">
+      <c r="A708" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="709" spans="1:1">
+      <c r="A709" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="710" spans="1:1">
+      <c r="A710" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="711" spans="1:1">
+      <c r="A711" s="2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="712" spans="1:1">
+      <c r="A712" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="713" spans="1:1">
+      <c r="A713" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="714" spans="1:1">
+      <c r="A714" s="2" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="715" spans="1:1">
+      <c r="A715" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="716" spans="1:1">
+      <c r="A716" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="717" spans="1:1">
+      <c r="A717" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="718" spans="1:1">
+      <c r="A718" s="2" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="719" spans="1:1">
+      <c r="A719" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="720" spans="1:1">
+      <c r="A720" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="721" spans="1:1">
+      <c r="A721" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="722" spans="1:1">
+      <c r="A722" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="723" spans="1:1">
+      <c r="A723" s="2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="724" spans="1:1">
+      <c r="A724" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="725" spans="1:1">
+      <c r="A725" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="726" spans="1:1">
+      <c r="A726" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="727" spans="1:1">
+      <c r="A727" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="728" spans="1:1">
+      <c r="A728" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="729" spans="1:1">
+      <c r="A729" s="2" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="730" spans="1:1">
+      <c r="A730" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="731" spans="1:1">
+      <c r="A731" s="2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="732" spans="1:1">
+      <c r="A732" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="733" spans="1:1">
+      <c r="A733" s="2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="734" spans="1:1">
+      <c r="A734" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="735" spans="1:1">
+      <c r="A735" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="736" spans="1:1">
+      <c r="A736" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="737" spans="1:1">
+      <c r="A737" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="738" spans="1:1">
+      <c r="A738" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="739" spans="1:1">
+      <c r="A739" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="740" spans="1:1">
+      <c r="A740" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="741" spans="1:1">
+      <c r="A741" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="742" spans="1:1">
+      <c r="A742" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="743" spans="1:1">
+      <c r="A743" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="744" spans="1:1">
+      <c r="A744" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="745" spans="1:1">
+      <c r="A745" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="746" spans="1:1">
+      <c r="A746" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="747" spans="1:1">
+      <c r="A747" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="748" spans="1:1">
+      <c r="A748" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="749" spans="1:1">
+      <c r="A749" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="750" spans="1:1">
+      <c r="A750" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="751" spans="1:1">
+      <c r="A751" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="752" spans="1:1">
+      <c r="A752" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="753" spans="1:1">
+      <c r="A753" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="754" spans="1:1">
+      <c r="A754" s="2" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="755" spans="1:1">
+      <c r="A755" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="756" spans="1:1">
+      <c r="A756" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="757" spans="1:1">
+      <c r="A757" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="758" spans="1:1">
+      <c r="A758" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="759" spans="1:1">
+      <c r="A759" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="760" spans="1:1">
+      <c r="A760" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="761" spans="1:1">
+      <c r="A761" s="2" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="762" spans="1:1">
+      <c r="A762" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="763" spans="1:1">
+      <c r="A763" s="2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="764" spans="1:1">
+      <c r="A764" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="765" spans="1:1">
+      <c r="A765" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="766" spans="1:1">
+      <c r="A766" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="767" spans="1:1">
+      <c r="A767" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="768" spans="1:1">
+      <c r="A768" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="769" spans="1:1">
+      <c r="A769" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="770" spans="1:1">
+      <c r="A770" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="771" spans="1:1">
+      <c r="A771" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="772" spans="1:1">
+      <c r="A772" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="773" spans="1:1">
+      <c r="A773" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="774" spans="1:1">
+      <c r="A774" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="775" spans="1:1">
+      <c r="A775" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="776" spans="1:1">
+      <c r="A776" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="777" spans="1:1">
+      <c r="A777" s="2" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="778" spans="1:1">
+      <c r="A778" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="779" spans="1:1">
+      <c r="A779" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="780" spans="1:1">
+      <c r="A780" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="781" spans="1:1">
+      <c r="A781" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="782" spans="1:1">
+      <c r="A782" s="2" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="783" spans="1:1">
+      <c r="A783" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="784" spans="1:1">
+      <c r="A784" s="2" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="785" spans="1:1">
+      <c r="A785" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="786" spans="1:1">
+      <c r="A786" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="787" spans="1:1">
+      <c r="A787" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="788" spans="1:1">
+      <c r="A788" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="789" spans="1:1">
+      <c r="A789" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="790" spans="1:1">
+      <c r="A790" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="791" spans="1:1">
+      <c r="A791" s="2" t="s">
+        <v>805</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>